--- a/wildberries_ru/all_items.xlsx
+++ b/wildberries_ru/all_items.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,81 +503,7966 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/catalog/893553381/detail.aspx</t>
+          <t>https://www.wildberries.ru/catalog/488386749/detail.aspx</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>893553381</v>
+        <v>488386749</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Пальто шерстяное осень</t>
+          <t>Пальто длинное оверсайз весна-осень в полоску</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>26172</v>
+        <v>6537</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Чао Белла!</t>
+          <t>HANBIYKE</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.wildberries.ru/seller/415201</t>
+          <t>https://www.wildberries.ru/seller/1304162</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>L, XL</t>
+          <t>S, M, L, XL</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Шерстяное пальто ниже колена с поясом и декором из стекляруса, пайеток и шелковых нитей от белорусского премиум-бренда L E U S H I N A. Прямой крой, натуральный состав и много внимания. Наш бренд за вашу уникальность! Все вещи бренда выполнены из качественных материалов и декорированы с применением ручного труда. Что делает каждую вещь особенной. Сиять каждый день легко, если вы в L E U S H I N A.</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>беларусь</t>
-        </is>
-      </c>
+          <t>Женское пальто из натуральной шерсти — идеальный выбор для холодного сезона. Длинная модель в модном оверсайз-крое сочетает стиль и комфорт, подойдёт для осени, зимы и ранней весны. Тёплое пальто мягкое и приятное на ощупь, отлично сохраняет тепло и защищает от ветра. Универсальный свободный фасон легко комбинируется с платьями, юбками, брюками и джинсами. Пальто женское макси длины визуально вытягивает силуэт и подходит для повседневных прогулок, деловых встреч и вечерних выходов. Классическое пальто на пуговицах станет базовым элементом гардероба, прослужит не один сезон и подчеркнёт ваш утончённый стиль.</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Состав:  шерсть-30%; Хлопок-60%; эластан-10%
-Цвет:  розовый; бежевый; пудровый
-Пол:  Женский
+          <t>Состав:  шерсть 30% полиэстер 60% вискоза 10%
+Цвет:  черный
 Сезон:  демисезон
 Вид застежки:  пуговицы
-Рост модели на фото:  167 см
-Параметры модели на фото (ОГ-ОТ-ОБ):  90-63-93
-Размер на модели:  М (44-46)
+Покрой:  оверсайз
+Тип карманов:  накладные
+Тип рукава:  длинные
+Опции капюшона:  без капюшона
+Опции опушки:  без опушки
+Декоративные элементы:  пояс
+Особенности модели:  Теплостойкость
+Пол:  Женский
+Уход за вещами:  ручная стирка
+Комплектация:  пальто 1шт; пояс 1 шт</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>https://basket-27.wbbasket.ru/vol4883/part488386/488386749/images/big/1.webp, https://basket-27.wbbasket.ru/vol4883/part488386/488386749/images/big/2.webp, https://basket-27.wbbasket.ru/vol4883/part488386/488386749/images/big/3.webp, https://basket-27.wbbasket.ru/vol4883/part488386/488386749/images/big/4.webp, https://basket-27.wbbasket.ru/vol4883/part488386/488386749/images/big/5.webp, https://basket-27.wbbasket.ru/vol4883/part488386/488386749/images/big/6.webp, https://basket-27.wbbasket.ru/vol4883/part488386/488386749/images/big/7.webp, https://basket-27.wbbasket.ru/vol4883/part488386/488386749/images/big/8.webp, https://basket-27.wbbasket.ru/vol4883/part488386/488386749/images/big/9.webp, https://basket-27.wbbasket.ru/vol4883/part488386/488386749/images/big/10.webp, https://basket-27.wbbasket.ru/vol4883/part488386/488386749/images/big/11.webp, https://basket-27.wbbasket.ru/vol4883/part488386/488386749/images/big/12.webp, https://basket-27.wbbasket.ru/vol4883/part488386/488386749/images/big/13.webp, https://basket-27.wbbasket.ru/vol4883/part488386/488386749/images/big/14.webp, https://basket-27.wbbasket.ru/vol4883/part488386/488386749/images/big/15.webp, https://basket-27.wbbasket.ru/vol4883/part488386/488386749/images/big/16.webp, https://basket-27.wbbasket.ru/vol4883/part488386/488386749/images/big/17.webp, https://basket-27.wbbasket.ru/vol4883/part488386/488386749/images/big/18.webp, https://basket-27.wbbasket.ru/vol4883/part488386/488386749/images/big/19.webp, https://basket-27.wbbasket.ru/vol4883/part488386/488386749/images/big/20.webp, https://basket-27.wbbasket.ru/vol4883/part488386/488386749/images/big/21.webp, https://basket-27.wbbasket.ru/vol4883/part488386/488386749/images/big/22.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/447770823/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>447770823</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Пальто длинное демисезонное</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>17479</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>thecash</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/377770</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>48, 50, 52, 54, 56, 58, 60, 46</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>573</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Мужское пальто весна-осень оверсайз – идеальный выбор для прохладных осенних дней, тренд 2026 года. Базовое пальто выполнено из плотной теплой ткани, в составе которого 70% шерсти. Отложной английский воротник и длинный прямой крой ниже колена обеспечит дополнительный уют и защиту от ветра.  Пальто дополнено глубокими карманами, которые не только украшают его, но и позволяют удобно хранить мелочи. Шлица на спинке добавляет удобства при носке и подчеркивает классический стиль. 
+Утепленное шерстяное пальто станет вашим надежным спутником на осень и весну.  Этот драповый вариант прекрасно подходит как для работы в офисе, так и для учебы или прогулок по городу. Сочетая современный дизайн с функциональностью, модель в пол подойдет для теплой зимы. 
+Классическое двубортное длинное мужское пальто подходит как для молодежного, так и для более зрелого возраста.  
+Драповое широкое пальто оверсайз великолепно смотрится на низких и высоких мужчинах, идеально сочетая практичность и элегантность. 
+В коллекции TheCaSH представлены модели разных фасонов - Вы обязательно найдете свою идеальную длину и цвет, который подчеркнет вашу индивидуальность.</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Состав:  шерсть - 70%; Эластан - 5%; Полиамид - 25%
+Цвет:  серый; серый графит; графит
+Пол:  Мужской
+Сезон:  Демисезон
+Вид застежки:  пуговицы
+Рост модели на фото:  182 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  112-90-110
+Размер на модели:  54
 Утеплитель:  без утеплителя
-Материал подкладки:  Вискоза - 100 %
+Температурный режим:  от -5 °C до +10 °C
+Материал подкладки:  вискоза
+Покрой:  прямой
+Тип карманов:  с клапаном
+Тип рукава:  длинные
+Опции капюшона:  без капюшона
+Опции опушки:  без опушки
+Декоративные элементы:  пуговицы
+Особенности модели:  мужское пальто длинное; двубортная
+Уход за вещами:  стирка запрещена; отбеливание запрещено; деликатная химическая чистка
+Комплектация:  Мужское пальто длинное - 1 шт; вешалка -1шт; Упаковочная сумка - 1 шт
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>https://basket-25.wbbasket.ru/vol4477/part447770/447770823/images/big/1.webp, https://basket-25.wbbasket.ru/vol4477/part447770/447770823/images/big/2.webp, https://basket-25.wbbasket.ru/vol4477/part447770/447770823/images/big/3.webp, https://basket-25.wbbasket.ru/vol4477/part447770/447770823/images/big/4.webp, https://basket-25.wbbasket.ru/vol4477/part447770/447770823/images/big/5.webp, https://basket-25.wbbasket.ru/vol4477/part447770/447770823/images/big/6.webp, https://basket-25.wbbasket.ru/vol4477/part447770/447770823/images/big/7.webp, https://basket-25.wbbasket.ru/vol4477/part447770/447770823/images/big/8.webp, https://basket-25.wbbasket.ru/vol4477/part447770/447770823/images/big/9.webp, https://basket-25.wbbasket.ru/vol4477/part447770/447770823/images/big/10.webp, https://basket-25.wbbasket.ru/vol4477/part447770/447770823/images/big/11.webp, https://basket-25.wbbasket.ru/vol4477/part447770/447770823/images/big/12.webp, https://basket-25.wbbasket.ru/vol4477/part447770/447770823/images/big/13.webp, https://basket-25.wbbasket.ru/vol4477/part447770/447770823/images/big/14.webp, https://basket-25.wbbasket.ru/vol4477/part447770/447770823/images/big/15.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/669906162/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>669906162</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Пальто длинное весна большие размеры оверсайз с поясом</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>4061</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>the nana</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/236134</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>64, 66, 68, 70, 36, 38, 40, 42, 44, 46, 48, 50, 52, 54, 56, 58, 60, 62</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>32</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Длинное оверсайз пальто с поясом в елочку рубчик от бренда the nana - идеальный выбор для демисезонного периода осень весна. Пальто на высокий рост является воплощением стиля, комфорта и качества. Базовое классическое пальто изготовлено из высококачественных материалов: 40% шерсть, 30% вискоза и 30% полиэстер. Такой состав обеспечивает тепло и комфорт в температурном режиме от -5°C до +15°C. Подкладка из полиэстера придает дополнительный уровень уюта и защиты от холода и ветра. Это стильное и модное пальто имеет классический черный цвет, который легко сочетается с любым образом. Особенности модели - наличие отложного английского воротника и длинный крой, который создает оверсайз эффект. Длина изделия макси, что делает его идеальным выбором как для повседневного ношения, так и для особых случаев, также по боковым швам на уровне талии обработаны шлевки. Прорезные карманы и длинные рукава, которые можно закатывать, делают это пальто универсальным и практичным. Покрой свободный, подчеркивающий стиль oversize и создающий модное и трендовое сочетание. Брендовое пальто отлично подойдет для любого типа фигуры - оно представлено в больших размерах, от 36 до 80 размера. Подойдет как для полных, так и для худых девушек. Натуральные нити и премиум качество материалов делают его долговечным и изысканным предметом гардероба. Спинка со средним швом и шлицей добавляет утонченности и стиля этой модели. Длинное пальто с поясом уместно как для офисного официального стиля, так и для повседневного образа. Обладая классическим и современным видом, это пальто прекрасно сочетается с любой обувью и аксессуарами. Пальто нашего бренда создано для тех, кто ценит качество и стиль. Независимо от вашего роста (высокий или невысокий) или типа фигуры (худые или полные), это пальто подчеркнет ваш индивидуальный стиль и придаст образу элегантности и изысканности</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>киргизия</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Состав:  шерсть 40%; вискоза 30%; полиэстер 30%
+Цвет:  черный
+Пол:  Женский
+Сезон:  Демисезон
+Вид застежки:  внутренний пояс
+Утеплитель:  без утеплителя
+Температурный режим:  от -5°C до +15°С
+Материал подкладки:  полиэстер
 Покрой:  прямой
 Тип карманов:  прорезные
 Тип рукава:  длинные
 Опции капюшона:  без капюшона
 Опции опушки:  без опушки
-Декоративные элементы:  пальто женское с пайетками и вышивкой
-Особенности модели:  ручная вышивка пайетки
+Декоративные элементы:  пояс
+Особенности модели:  рукав реглан
+Уход за вещами:  деликатная химическая чистка
+Комплектация:  Пальто с поясом 1шт.
+Страна производства:  Киргизия</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>https://basket-32.wbbasket.ru/vol6699/part669906/669906162/images/big/1.webp, https://basket-32.wbbasket.ru/vol6699/part669906/669906162/images/big/2.webp, https://basket-32.wbbasket.ru/vol6699/part669906/669906162/images/big/3.webp, https://basket-32.wbbasket.ru/vol6699/part669906/669906162/images/big/4.webp, https://basket-32.wbbasket.ru/vol6699/part669906/669906162/images/big/5.webp, https://basket-32.wbbasket.ru/vol6699/part669906/669906162/images/big/6.webp, https://basket-32.wbbasket.ru/vol6699/part669906/669906162/images/big/7.webp, https://basket-32.wbbasket.ru/vol6699/part669906/669906162/images/big/8.webp, https://basket-32.wbbasket.ru/vol6699/part669906/669906162/images/big/9.webp, https://basket-32.wbbasket.ru/vol6699/part669906/669906162/images/big/10.webp, https://basket-32.wbbasket.ru/vol6699/part669906/669906162/images/big/11.webp, https://basket-32.wbbasket.ru/vol6699/part669906/669906162/images/big/12.webp, https://basket-32.wbbasket.ru/vol6699/part669906/669906162/images/big/13.webp, https://basket-32.wbbasket.ru/vol6699/part669906/669906162/images/big/14.webp, https://basket-32.wbbasket.ru/vol6699/part669906/669906162/images/big/15.webp, https://basket-32.wbbasket.ru/vol6699/part669906/669906162/images/big/16.webp, https://basket-32.wbbasket.ru/vol6699/part669906/669906162/images/big/17.webp, https://basket-32.wbbasket.ru/vol6699/part669906/669906162/images/big/18.webp, https://basket-32.wbbasket.ru/vol6699/part669906/669906162/images/big/19.webp, https://basket-32.wbbasket.ru/vol6699/part669906/669906162/images/big/20.webp, https://basket-32.wbbasket.ru/vol6699/part669906/669906162/images/big/21.webp, https://basket-32.wbbasket.ru/vol6699/part669906/669906162/images/big/22.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/317997588/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>317997588</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Пальто оверсайз длинное весеннее</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>5415</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>the nana</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/236134</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>38, 40, 42, 44, 46, 48, 50, 52, 54, 56, 58, 60, 62, 64, 66, 68, 70, 36</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>264</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Бренд the nana более 10 лет радует представительниц прекрасного пола своими стильными моделями, сохраняя высокий уровень премиум качества всех изделий, совершенствуя пошив и качество благодаря нашим прекрасным покупателям. Наш бренд разработал новую классическую модель демисезонного пальто Lotus. Такое базовое серое пальто должно быть в гардеробе у каждой стильной женщины в этом сезоне весна – осень 2026. Длинное пальто станет приятным приобретением для девушек в весеннем и осеннем сезоне. За счет своей длины макси и натурального состава – шерсть 40%, вискоза 30% и 30% полиэстер, пальто будет защищать от ветра и холода в любую погоду, и даже зимой. Такой состав обеспечивает тепло и комфорт в температурном режиме от -5°C до +15°C, а подкладка из полиэстера и вискозы придает дополнительный уровень уюта и защиты. Особенности модели включают двубортную застежку на пуговицы, наличие отложного английского воротника и длинный крой умеренного объема. Застежка на потайные кнопки делает пальто идеальным выбором для повседневного ношения и особых случаев, также у пальто есть внешние пуговицы и пояс. Тип карманов – прорезные с клапаном, и длинный двухшовный втачной рукав с пуговицами, что делает это пальто практичным. Покрой свободный, подчеркивающий стиль оверсайз и создающий модное и трендовое сочетание. Брендовое пальто отлично подойдет для любого типа фигуры - оно представлено в больших размерах, подойдет для полных и для худых, а также для беременных девушек. Натуральные нити и премиум качество материалов делают его долговечным. Спинка со средним швом и отлетной шлицей добавляет утонченности и стиля этой модели. Длинное модное пальто уместно как для офисного официального стиля, так и для повседневного образа. Обладая классическим и современным видом, это пальто прекрасно сочетается с любой обувью и аксессуарами. Шерстяное пальто создано для тех, кто ценит качество и стиль, которое придаст образу элегантности и изысканности.</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>киргизия</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Состав:  шерсть 40%; вискоза 30%; полиэстер 30%
+Цвет:  серый; светло-серый
+Пол:  Женский
+Сезон:  Демисезон
+Вид застежки:  пуговицы
+Рост модели на фото:  171 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  83-65-92
+Утеплитель:  без утеплителя
+Температурный режим:  от -5°C до +15°С
+Материал подкладки:  полиэстер 50%; вискоза 30%
+Покрой:  приталенный
+Тип карманов:  с клапаном
+Тип рукава:  длинные
+Опции капюшона:  без капюшона
+Опции опушки:  без опушки
+Декоративные элементы:  без элементов
+Особенности модели:  двубортная
+Уход за вещами:  деликатная химическая чистка
+Комплектация:  Пальто со шлицей 1шт.
+Страна производства:  Киргизия</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>https://basket-19.wbbasket.ru/vol3179/part317997/317997588/images/big/1.webp, https://basket-19.wbbasket.ru/vol3179/part317997/317997588/images/big/2.webp, https://basket-19.wbbasket.ru/vol3179/part317997/317997588/images/big/3.webp, https://basket-19.wbbasket.ru/vol3179/part317997/317997588/images/big/4.webp, https://basket-19.wbbasket.ru/vol3179/part317997/317997588/images/big/5.webp, https://basket-19.wbbasket.ru/vol3179/part317997/317997588/images/big/6.webp, https://basket-19.wbbasket.ru/vol3179/part317997/317997588/images/big/7.webp, https://basket-19.wbbasket.ru/vol3179/part317997/317997588/images/big/8.webp, https://basket-19.wbbasket.ru/vol3179/part317997/317997588/images/big/9.webp, https://basket-19.wbbasket.ru/vol3179/part317997/317997588/images/big/10.webp, https://basket-19.wbbasket.ru/vol3179/part317997/317997588/images/big/11.webp, https://basket-19.wbbasket.ru/vol3179/part317997/317997588/images/big/12.webp, https://basket-19.wbbasket.ru/vol3179/part317997/317997588/images/big/13.webp, https://basket-19.wbbasket.ru/vol3179/part317997/317997588/images/big/14.webp, https://basket-19.wbbasket.ru/vol3179/part317997/317997588/images/big/15.webp, https://basket-19.wbbasket.ru/vol3179/part317997/317997588/images/big/16.webp, https://basket-19.wbbasket.ru/vol3179/part317997/317997588/images/big/17.webp, https://basket-19.wbbasket.ru/vol3179/part317997/317997588/images/big/18.webp, https://basket-19.wbbasket.ru/vol3179/part317997/317997588/images/big/19.webp, https://basket-19.wbbasket.ru/vol3179/part317997/317997588/images/big/20.webp, https://basket-19.wbbasket.ru/vol3179/part317997/317997588/images/big/21.webp, https://basket-19.wbbasket.ru/vol3179/part317997/317997588/images/big/22.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/578880573/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>578880573</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Пальто утепленное шерстяное длинное</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>15158</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>CORESSI</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/26796</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>42, 44, 46, 48, 50, 52, 54</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>434</v>
+      </c>
+      <c r="J6" t="n">
+        <v>5</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Пальто женское длинное утеплённое шерстяное демисезонное CORESSI (КОРЕССИ) — элегантная модель для ранней весны и сезона весна–осень 2026. Стильное двубортное пальто прямого кроя с поясом сочетает комфорт, практичность и дизайн, оставаясь удобным для повседневной носки и делового гардероба.
+Состав изделия: шерсть — 57%, вискоза — 36%, полиэстер — 7%. Длина по спинке — 124 см, длина рукава — 64 см. Удлинённое женское пальто визуально вытягивает силуэт и формирует аккуратную посадку.
+Изделие выполнено из натуральной шерсти с добавлением кашемира, что делает ткань мягкой и приятной к телу. Плотная твидовая фактура придаёт пальто благородный внешний вид и подчёркивает классический стиль. Шерстяное пальто сохраняет тепло и комфорт в прохладную погоду.
+Двубортное длинное пальто прямого кроя дополнено английским воротником и шлицей по спинке. Пояс из основной ткани позволяет носить модель как приталенное пальто или в более свободном оверсайз-силуэте. Застёжка на пуговицах сохраняет аккуратный и классический вид.
+Цвет — бежевый: элегантный оттенок, который сочетается с базовым гардеробом. Бежевое пальто подходит для городского и делового стиля.
+Твидовая ворсистая фактура ткани придаёт изделию выразительную текстуру. Для ухода рекомендуется использовать велюровую щётку и ролик.
+Пальто женское утеплённое демисезонное CORESSI производится в России на современном оборудовании и проходит строгий контроль качества.
+Внутри используется современный утеплитель TermoFinn Micro (термофин) из ультратонкого микроволокна. Он формирует лёгкий и равномерный теплоизолирующий слой, сохраняет естественное тепло тела и обеспечивает воздухообмен. Благодаря этому пальто комфортно носить в температурном диапазоне примерно от +15°C до –10°C — подходит для весны, осени и еврозимы. Модель можно рассматривать как пальто зимнее женское для мягкой зимы при разной активности.
+Тёплое длинное пальто — практичный и универсальный выбор для повседневной носки на весну и осень.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Состав:  шерсть; вискоза; полиэстер
+Цвет:  светло-коричневый; бежевый
+Пол:  Женский
+Сезон:  демисезон
+Вид застежки:  пуговицы
+Рост модели на фото:  175 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  87-60-90
+Размер на модели:  44
+Утеплитель:  термофин
+Плотность синтетического утеплителя:  100 г/кв.м
+Температурный режим:  от +10°С до -10°С
+Материал подкладки:  полиэстер
+Покрой:  прямой
+Тип карманов:  прорезные
+Опции капюшона:  без капюшона
+Опции опушки:  без опушки
+Декоративные элементы:  пуговицы; пояс; декоративная отстрочка
+Особенности модели:  ветрозащита; оверсайз; двубортная
+Уход за вещами:  деликатная химическая чистка; допускается отпаривание
+Комплектация:  Пальто - 1 шт; Упаковочная сумка-чемодан
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>https://basket-29.wbbasket.ru/vol5788/part578880/578880573/images/big/1.webp, https://basket-29.wbbasket.ru/vol5788/part578880/578880573/images/big/2.webp, https://basket-29.wbbasket.ru/vol5788/part578880/578880573/images/big/3.webp, https://basket-29.wbbasket.ru/vol5788/part578880/578880573/images/big/4.webp, https://basket-29.wbbasket.ru/vol5788/part578880/578880573/images/big/5.webp, https://basket-29.wbbasket.ru/vol5788/part578880/578880573/images/big/6.webp, https://basket-29.wbbasket.ru/vol5788/part578880/578880573/images/big/7.webp, https://basket-29.wbbasket.ru/vol5788/part578880/578880573/images/big/8.webp, https://basket-29.wbbasket.ru/vol5788/part578880/578880573/images/big/9.webp, https://basket-29.wbbasket.ru/vol5788/part578880/578880573/images/big/10.webp, https://basket-29.wbbasket.ru/vol5788/part578880/578880573/images/big/11.webp, https://basket-29.wbbasket.ru/vol5788/part578880/578880573/images/big/12.webp, https://basket-29.wbbasket.ru/vol5788/part578880/578880573/images/big/13.webp, https://basket-29.wbbasket.ru/vol5788/part578880/578880573/images/big/14.webp, https://basket-29.wbbasket.ru/vol5788/part578880/578880573/images/big/15.webp, https://basket-29.wbbasket.ru/vol5788/part578880/578880573/images/big/16.webp, https://basket-29.wbbasket.ru/vol5788/part578880/578880573/images/big/17.webp, https://basket-29.wbbasket.ru/vol5788/part578880/578880573/images/big/18.webp, https://basket-29.wbbasket.ru/vol5788/part578880/578880573/images/big/19.webp, https://basket-29.wbbasket.ru/vol5788/part578880/578880573/images/big/20.webp, https://basket-29.wbbasket.ru/vol5788/part578880/578880573/images/big/21.webp, https://basket-29.wbbasket.ru/vol5788/part578880/578880573/images/big/22.webp, https://basket-29.wbbasket.ru/vol5788/part578880/578880573/images/big/23.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/303239532/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>303239532</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Пальто без подклада</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>9999</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Магазин одежды бохо</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/61696</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>oversize 50-54, oversize 56-60, oversize 62-66, oversize 46-48</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>209</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Демисезонное женское пальто без подклада от milidi – идеальный выбор для создания стильных образов весна-осень 2026. Модель выполнена из высококачественной вареной и валяной шерсти, благодаря чему изделие обладает отличными тепловыми свойствами и сохраняет внешний вид на протяжении долгого времени. Дизайнерская модель легкого женского пальто без подклада подчеркивается английским воротником и универсальным синим цветом, что делает это женское пальто из лодена не только практичным, но и невероятно модным решением для любого случая.
+Кардиган женский удлиненный представлен в размере оверсайз, что позволяет носить его девушкам и женщинам plus size, а также беременным – изделие не сковывает движений и подходит для больших размеров и полных. Летнее модное пальто milidi гармонично сочетается с вещами в стиле бохо, классика и премиум.
+Полупальто milidi – это базовая вещь для гардероба, подходящая для создания уютного и теплого образа. Преимущества: натуральная шерсть, современный дизайн с накладными карманами, универсальность (весна-осень). 
+Бренд MILIDI имеет свое производство в России,  что позволяет нам контролировать высокое качество одежды больших размеров!</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Состав:  шерсть 80%; Вискоза 20%
+Цвет:  темно-синий; синий; синий космос; черно-синий; ночной синий
+Пол:  Женский
+Сезон:  Демисезон
+Вид застежки:  пуговицы; без пояса
+Рост модели на фото:  173 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  90-63-93
+Размер на модели:  50-54
+Утеплитель:  без утеплителя
+Температурный режим:  от +5 °C до +15 °C
+Материал подкладки:  без подкладки
+Покрой:  прямой
+Тип карманов:  накладные
+Тип рукава:  длинные
+Опции капюшона:  без капюшона
+Опции опушки:  без опушки
+Мех опушки/отделки:  без меха
+Декоративные элементы:  без элементов; однотонное; для полных
+Особенности модели:  тонкое; легкое; Кардиган пальто женский больших размеров
+Уход за вещами:  деликатная стирка в режиме "шерсть" при температуре не выше 30 градусов; без отжима; сушка только в горизонтальном положении при естественных условиях
+Комплектация:  Пальто демисезонное длинное - 1 шт
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>https://basket-18.wbbasket.ru/vol3032/part303239/303239532/images/big/1.webp, https://basket-18.wbbasket.ru/vol3032/part303239/303239532/images/big/2.webp, https://basket-18.wbbasket.ru/vol3032/part303239/303239532/images/big/3.webp, https://basket-18.wbbasket.ru/vol3032/part303239/303239532/images/big/4.webp, https://basket-18.wbbasket.ru/vol3032/part303239/303239532/images/big/5.webp, https://basket-18.wbbasket.ru/vol3032/part303239/303239532/images/big/6.webp, https://basket-18.wbbasket.ru/vol3032/part303239/303239532/images/big/7.webp, https://basket-18.wbbasket.ru/vol3032/part303239/303239532/images/big/8.webp, https://basket-18.wbbasket.ru/vol3032/part303239/303239532/images/big/9.webp, https://basket-18.wbbasket.ru/vol3032/part303239/303239532/images/big/10.webp, https://basket-18.wbbasket.ru/vol3032/part303239/303239532/images/big/11.webp, https://basket-18.wbbasket.ru/vol3032/part303239/303239532/images/big/12.webp, https://basket-18.wbbasket.ru/vol3032/part303239/303239532/images/big/13.webp, https://basket-18.wbbasket.ru/vol3032/part303239/303239532/images/big/14.webp, https://basket-18.wbbasket.ru/vol3032/part303239/303239532/images/big/15.webp, https://basket-18.wbbasket.ru/vol3032/part303239/303239532/images/big/16.webp, https://basket-18.wbbasket.ru/vol3032/part303239/303239532/images/big/17.webp, https://basket-18.wbbasket.ru/vol3032/part303239/303239532/images/big/18.webp, https://basket-18.wbbasket.ru/vol3032/part303239/303239532/images/big/19.webp, https://basket-18.wbbasket.ru/vol3032/part303239/303239532/images/big/20.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/474328452/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>474328452</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Пальто длинное демисезонное оверсайз</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>6048</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>КазРусТекстиль</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/321797</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>42, 44, 46, 48, 50, 52, 54, 56, 58, 60, 62, 64, 66</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>46</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Пальто женское - идеальный выбор для модных женщин, желающих подчеркнуть свой стиль в любое время года. Весеннее пальто - это легкое и яркое решение для прохладных дней. У нас есть осенние модели, выполненные из шерсти и драпа, которые дарят уют и тепло. Демисезонное пальто - незаменимый элемент гардероба для межсезонья: весна-осень и осень-зима, что позволяет подобрать подходящую модель для любого сезона. Осенние модели отличаются стильным дизайном и практичностью. Теплое, утепленное изделие согреет в холодную погоду, ткань из шерсти с натуральным утеплителем идеально подходят для зимних морозных дней. Однобортное пальто с поясом и пуговицей создают максимальный комфорт и элегантность. Модели оверсайз и плюс сайз подойдут для полных женщин и беременных, обеспечивая свободу движений. Для подростков и молодых девушек мы предлагаем молодежные и стильные модели пальто пинтерест, которые подчеркивают индивидуальность и актуальность модных тенденций. Пальто с английским воротником подчеркнут вашу индивидуальность и хороший вкус. Драповое пальто - это классика, проверенная временем, обладают высоким качеством и долговечностью. У нас есть пальто на запах, которые прекрасно подходят для еврозимы. Эти изделия легкие и уютные, обеспечивающие комфорт при любой погоде. В нашем ассортименте представлены как длинные, так и макси модели. Длинное пальто - элегантное и утонченное, удлиненное пальто миди - это стильный выбор для тех, кто ценит моду и комфорт. Прямое и приталенное пальто идеально подчеркивает фигуру, создавая женственный силуэт. Каждое изделие имеет удобные глубокие карманы, что делает их функциональными и практичными, а рукава со спущенными оверсайз плечами обеспечивают свободу движений. Универсальная модель поможет создать образы кэжуал, винтаж и элегантные классические стили. Дизайнерская верхняя одежда больших размеров и для невысоких женщин - у нас найдутся модели для всех кто ищет что-то необычное.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>казахстан</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Состав:  шерсть; акрил
+Цвет:  бежевый
+Сезон:  демисезон
+Вид застежки:  пуговицы пояс
+Рост модели на фото:  167 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  83-57-87
+Размер на модели:  46
+Утеплитель:  полиэстер
+Температурный режим:  от -5С до + 15С
+Материал подкладки:  полиэстер
+Покрой:  прямой
+Тип карманов:  накладные
+Тип рукава:  длинные
+Опции капюшона:  без капюшона
+Опции опушки:  без опушки
+Декоративные элементы:  паты
+Особенности модели:  с подкладкой
+Конструктивные элементы:  карман
+Пол:  Женский
+Уход за вещами:  Машинная стирка; отбеливание запрещено
+Комплектация:  женское пальто; пояс
+Страна производства:  Казахстан</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>https://basket-26.wbbasket.ru/vol4743/part474328/474328452/images/big/1.webp, https://basket-26.wbbasket.ru/vol4743/part474328/474328452/images/big/2.webp, https://basket-26.wbbasket.ru/vol4743/part474328/474328452/images/big/3.webp, https://basket-26.wbbasket.ru/vol4743/part474328/474328452/images/big/4.webp, https://basket-26.wbbasket.ru/vol4743/part474328/474328452/images/big/5.webp, https://basket-26.wbbasket.ru/vol4743/part474328/474328452/images/big/6.webp, https://basket-26.wbbasket.ru/vol4743/part474328/474328452/images/big/7.webp, https://basket-26.wbbasket.ru/vol4743/part474328/474328452/images/big/8.webp, https://basket-26.wbbasket.ru/vol4743/part474328/474328452/images/big/9.webp, https://basket-26.wbbasket.ru/vol4743/part474328/474328452/images/big/10.webp, https://basket-26.wbbasket.ru/vol4743/part474328/474328452/images/big/11.webp, https://basket-26.wbbasket.ru/vol4743/part474328/474328452/images/big/12.webp, https://basket-26.wbbasket.ru/vol4743/part474328/474328452/images/big/13.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/197268380/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>197268380</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Пальто зимнее длинное теплое</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>8002</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Eurydike</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/3971567</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>46, 48, 50, 52, 54, 44, 56, 58</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>66</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Данное пальто представляет собой модный и практичный вариант для осеннего и зимнего сезонов, идеально подходящий для девушек с фигурами размером 48-58. Высококачественная мягкая ткань, использованная при его выполнении, обеспечивает комфорт и уют в прохладные дни. Этот дизайнерский предмет одежды с удлиненным прямым фасоном подчеркивает индивидуальность, а его серый цвет и классический дизайн добавляют вещи актуальности в любой коллекции.
+Модель оснащена английским воротником,  закрывающимся и защищающим от холодного воздуха, и прорезными накладными скошенными карманами, добавляющими функциональность. Многослойные элементы конструкции делают его особенно удобным для носки, позволяя использовать его как в деловом, так и в повседневном стиле. В сочетании с высокими сапогами или кроссовками, этот вариант станет отличным решением для прогулок и активного отдыха.
+В процессе создания этого изделия присутствуют натуральные материалы, которые обеспечивают должный уход и долговечность. Пальто имеет утеплитель,в составе которого - 100% шерсть, он защищает от низких температур, что делает его идеальным для межсезонья, позволяя  его носить в еврозиму. Данная верхняя одежда выделяется на фоне других благодаря своему уникальному дизайну и трендовому виду. 
+С таким базовым изделием легко комбинировать другие элементы гардероба, создавая завершенный образ актуальный в течение всего зимнего сезона.  Эта модель станет незаменимой частью вашего гардероба, добавляя в него стиль и уют. Подчеркните свою женственность с этой модной вещью,  соответствующей самым последним трендам и требованиям.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Состав:  50% шерсть, 30% вискоза, 20% поливискоза
+Цвет:  серо-бежевый; серый; серый меланж; бежевый; серо-бежевый светлый
+Сезон:  зима
+Вид застежки:  пуговицы
+Рост модели на фото:  175 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  84-64-93
+Размер на модели:  46
+Утеплитель:  шерсть
+Плотность синтетического утеплителя:  180 г/кв.м
+Температурный режим:  от -10 до +5
+Материал подкладки:  полиэстер; шерстепон
+Покрой:  свободный
+Тип карманов:  накладные
+Тип рукава:  длинные
+Опции капюшона:  без капюшона
+Опции опушки:  без опушки
+Мех опушки/отделки:  без меха
+Декоративные элементы:  без элементов
+Особенности модели:  ветрозащита; дышащий материал; теплое
+Конструктивные элементы:  свободный крой
+Пол:  Женский
+Уход за вещами:  допускается отпаривание; деликатная химическая чистка
+Комплектация:  пояс; пальто
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>https://basket-13.wbbasket.ru/vol1972/part197268/197268380/images/big/1.webp, https://basket-13.wbbasket.ru/vol1972/part197268/197268380/images/big/2.webp, https://basket-13.wbbasket.ru/vol1972/part197268/197268380/images/big/3.webp, https://basket-13.wbbasket.ru/vol1972/part197268/197268380/images/big/4.webp, https://basket-13.wbbasket.ru/vol1972/part197268/197268380/images/big/5.webp, https://basket-13.wbbasket.ru/vol1972/part197268/197268380/images/big/6.webp, https://basket-13.wbbasket.ru/vol1972/part197268/197268380/images/big/7.webp, https://basket-13.wbbasket.ru/vol1972/part197268/197268380/images/big/8.webp, https://basket-13.wbbasket.ru/vol1972/part197268/197268380/images/big/9.webp, https://basket-13.wbbasket.ru/vol1972/part197268/197268380/images/big/10.webp, https://basket-13.wbbasket.ru/vol1972/part197268/197268380/images/big/11.webp, https://basket-13.wbbasket.ru/vol1972/part197268/197268380/images/big/12.webp, https://basket-13.wbbasket.ru/vol1972/part197268/197268380/images/big/13.webp, https://basket-13.wbbasket.ru/vol1972/part197268/197268380/images/big/14.webp, https://basket-13.wbbasket.ru/vol1972/part197268/197268380/images/big/15.webp, https://basket-13.wbbasket.ru/vol1972/part197268/197268380/images/big/16.webp, https://basket-13.wbbasket.ru/vol1972/part197268/197268380/images/big/17.webp, https://basket-13.wbbasket.ru/vol1972/part197268/197268380/images/big/18.webp, https://basket-13.wbbasket.ru/vol1972/part197268/197268380/images/big/19.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/446834586/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>446834586</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Пальто шерстяное демисезонное оверсайз короткое</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>9303</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>CORESSI</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/26796</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>42, 44, 46, 48, 50, 52, 54</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>291</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Окунитесь в стиль и комфорт, выбирая женское пальто для сезона весна–осень. Это короткое демисезонное пальто станет практичным и стильным решением для повседневной носки в прохладную погоду. Модель сочетает актуальный дизайн и функциональность, позволяя чувствовать себя уютно и уверенно каждый день.
+Двубортное твидовое пальто прямого кроя выполнено с английским воротником, декоративными погонами и патами на рукавах. Застёжка на пуговицах формирует аккуратный силуэт и подчёркивает классические линии. Длина изделия по спинке — 63,5 см, длина рукава от линии втачивания воротника — 75 см, что делает модель удобной и универсальной.
+Тёплое укороченное пальто создаёт ощущение уюта и защищает от прохлады в межсезонье. Натуральная ворсовая ткань с высоким содержанием шерсти помогает сохранять комфортное тепло, а кашемировое ощущение мягкости делает изделие особенно приятным в носке. Такое шерстяное полупальто подойдёт для весенних и осенних дней.
+Модель гармонично вписывается как в кэжуал-образы, так и в офисную классику. Коричневый цвет легко сочетается с базовым гардеробом. Это пальто универсальный выбор для автоледи,оптимальная длина не сковывает движения и обеспечивает комфорт за рулём.
+Изделие привлекает внимание винтажным настроением, которое создаётся за счёт прямого кроя, выразительных деталей и благородного оттенка. Стиль подчёркивает индивидуальность и соответствует модным тенденциям 2026 года. Размерный ряд делает модель подходящей как для женщин, так и для подростков.
+Ткань имеет ворсистую фактуру благодаря большому проценту шерсти, поэтому возможно прилипание волокон, шерсти животных и пыли. Материал не скатывается, сохраняет форму и цвет. В процессе носки ворс может подниматься — рекомендуется очищать поверхность липким роликом и велюровой щёткой по направлению ворса.
+Вся продукция бренда CORESSI производится в России, отшивается на современном швейном оборудовании и проходит строгий контроль качества. Будем признательны за оставленный отзыв. Приятных покупок!
+</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Состав:  шерсть 57%; вискоза 36%; полиэстер 7%
+Цвет:  коричневый
+Пол:  Женский
+Сезон:  Демисезон
+Вид застежки:  пуговицы
+Рост модели на фото:  167 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  89-66-96
+Размер на модели:  44
+Утеплитель:  без утеплителя
+Температурный режим:  от 0 °C до +15 °C
+Материал подкладки:  полиэстер
+Покрой:  прямой
+Тип карманов:  прорезные
+Опции капюшона:  без капюшона
+Опции опушки:  без опушки
+Декоративные элементы:  декоративная отстрочка; погоны; пуговицы
+Особенности модели:  ветрозащита; оверсайз; двубортная
+Уход за вещами:  деликатная химическая чистка; допускается отпаривание
+Комплектация:  Пальто - 1 шт; Упаковочная сумка-чемодан
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>https://basket-25.wbbasket.ru/vol4468/part446834/446834586/images/big/1.webp, https://basket-25.wbbasket.ru/vol4468/part446834/446834586/images/big/2.webp, https://basket-25.wbbasket.ru/vol4468/part446834/446834586/images/big/3.webp, https://basket-25.wbbasket.ru/vol4468/part446834/446834586/images/big/4.webp, https://basket-25.wbbasket.ru/vol4468/part446834/446834586/images/big/5.webp, https://basket-25.wbbasket.ru/vol4468/part446834/446834586/images/big/6.webp, https://basket-25.wbbasket.ru/vol4468/part446834/446834586/images/big/7.webp, https://basket-25.wbbasket.ru/vol4468/part446834/446834586/images/big/8.webp, https://basket-25.wbbasket.ru/vol4468/part446834/446834586/images/big/9.webp, https://basket-25.wbbasket.ru/vol4468/part446834/446834586/images/big/10.webp, https://basket-25.wbbasket.ru/vol4468/part446834/446834586/images/big/11.webp, https://basket-25.wbbasket.ru/vol4468/part446834/446834586/images/big/12.webp, https://basket-25.wbbasket.ru/vol4468/part446834/446834586/images/big/13.webp, https://basket-25.wbbasket.ru/vol4468/part446834/446834586/images/big/14.webp, https://basket-25.wbbasket.ru/vol4468/part446834/446834586/images/big/15.webp, https://basket-25.wbbasket.ru/vol4468/part446834/446834586/images/big/16.webp, https://basket-25.wbbasket.ru/vol4468/part446834/446834586/images/big/17.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/680696689/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>680696689</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Пальто весна-осень длинное шерстяное</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11934</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Overcast</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/80300</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>S, M</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Женское шерстяное пальто с поясом в пол весна-осень на больших пуговицах. Представляет собой стильную модель верхней одежды из премиальных материалов, как кашемир. Выполнено из натуральной шерсти — плотной и мягкой, дает тепло даже в холодные дни. Длинное роскошное макси — тренд и универсальное решение для демисезонного и весеннего периодов, идеально подходящее как для официального делового образа, так и для повседневного носки в стиле casual. Весеннее свободное полупальто с лацканами и шлицей имеет деловой, но элегантный дизайн с двубортной застежкой на пуговицы, что подчеркивает комфортный крой. Приталенный силуэт с поясом акцентирует талию, создавая женственный и современный образ для подростков, а широкие свободные рукава и отложной английский воротник с отворотами дополняют композицию, придавая изделию винтажную нотку. Сбоку расположены удобные накладные карманы с боковыми разрезами, которые обеспечивают свободу движений и защищают от ветра. Тренч изготовлен из драпа с качественной подкладкой, которая предотвращает проникновение холодного воздуха. Цветовая гамма базовая и универсальная — классическое черное изделие легко впишется в любой гардероб, особенно большие размеры для беременных. Теплая однотонная модель является базой, сочетающей в себе комфорт, стиль и элегантность. Утепленное с приталенной линией кроя — наряд для женщин, ценящих функциональность в сочетании с офис дизайном на весна осень 2026. Высокое качество тканей подтверждает премиум сегмент, гарантирующий долговечность и сохранение внешнего вида на протяжении многих сезонов. Плащ олд мани, как в пинтерест отлично подойдет тем, кто ищет драповое решение для любого сезона, предпочитая строгую классику.</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Состав:  шерсть 30%; полиэстер 35%; Вискоза 35%
+Цвет:  черный
+Сезон:  демисезон
+Вид застежки:  пуговицы
+Рост модели на фото:  173 см
+Утеплитель:  без утеплителя
+Температурный режим:  от 0 °C до +10 °C
+Материал подкладки:  полиэстер
+Покрой:  прямой
+Тип карманов:  прорезные; с клапаном
+Тип рукава:  длинные
+Опции капюшона:  без капюшона
+Опции опушки:  без опушки
+Мех опушки/отделки:  без меха
+Декоративные элементы:  лацканы; пуговицы
+Особенности модели:  ветрозащита; водоотталкивающий материал; с разрезом
+Конструктивные элементы:  шлица
+Пол:  Женский
+Уход за вещами:  сухая чистка
+Комплектация:  пальто 1 шт, пояс 1 шт
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>https://basket-33.wbbasket.ru/vol6806/part680696/680696689/images/big/1.webp, https://basket-33.wbbasket.ru/vol6806/part680696/680696689/images/big/2.webp, https://basket-33.wbbasket.ru/vol6806/part680696/680696689/images/big/3.webp, https://basket-33.wbbasket.ru/vol6806/part680696/680696689/images/big/4.webp, https://basket-33.wbbasket.ru/vol6806/part680696/680696689/images/big/5.webp, https://basket-33.wbbasket.ru/vol6806/part680696/680696689/images/big/6.webp, https://basket-33.wbbasket.ru/vol6806/part680696/680696689/images/big/7.webp, https://basket-33.wbbasket.ru/vol6806/part680696/680696689/images/big/8.webp, https://basket-33.wbbasket.ru/vol6806/part680696/680696689/images/big/9.webp, https://basket-33.wbbasket.ru/vol6806/part680696/680696689/images/big/10.webp, https://basket-33.wbbasket.ru/vol6806/part680696/680696689/images/big/11.webp, https://basket-33.wbbasket.ru/vol6806/part680696/680696689/images/big/12.webp, https://basket-33.wbbasket.ru/vol6806/part680696/680696689/images/big/13.webp, https://basket-33.wbbasket.ru/vol6806/part680696/680696689/images/big/14.webp, https://basket-33.wbbasket.ru/vol6806/part680696/680696689/images/big/15.webp, https://basket-33.wbbasket.ru/vol6806/part680696/680696689/images/big/16.webp, https://basket-33.wbbasket.ru/vol6806/part680696/680696689/images/big/17.webp, https://basket-33.wbbasket.ru/vol6806/part680696/680696689/images/big/18.webp, https://basket-33.wbbasket.ru/vol6806/part680696/680696689/images/big/19.webp, https://basket-33.wbbasket.ru/vol6806/part680696/680696689/images/big/20.webp, https://basket-33.wbbasket.ru/vol6806/part680696/680696689/images/big/21.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/324425182/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>324425182</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Пальто шерстяное натуральное</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>13042</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Rendez-Vous</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/528630</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>S, L, XS, M, XL, XXL</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>8</v>
+      </c>
+      <c r="J12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Черное пальто женское французского бренда Maison David. Состав: 100% шерсть натуральная. Шерсть отлично согревает, при этом позволяет телу дышать, не создавая парникового эффекта. В шерстяных вещах тепло, но не жарко. Одежда из шерсти — идеальный выбор для зимы и холодного демисезона. Состав подкладки: полиэстер, вискоза.
+Верхняя одежда имеет силуэт оверсайз. Модель отличает отложной воротник и наличие прорезных карманов. Температурный режим от плюс 10 до минус 5.
+Ухаживайте за вещью правильно, чтобы она дольше служила и радовала вас. Правила по уходу указаны на вшивном ярлычке изделия. Разрешено: химчистка. Запрещено: стирка, отбеливание, глажка, барабанная сушка.
+Пальто в элегантном стиле BCBG — превосходный выбор для рабочих или повседневных образов. Одежда в стиле BCBG (bon chic bon genre) станет хорошей инвестицией в базовый гардероб. Maison David — дом современной элегантности. Бренд отражает идею французского bon chic, bon genre: искусство быть безупречным без усилий, сочетая гармонию интеллекта и формы, а качество становится главным языком красоты. Бренд соединяет современные тенденции с классическими формами, сохраняя баланс между актуальностью и вечностью. Каждая вещь Maison David создается, чтобы жить долго — сопровождать своего владельца в реальной, настоящей жизни: в работе, в путешествиях, в личных историях. Это не просто гардероб, а состояние уравновешенности и эстетического покоя.</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Состав:  шерсть натуральная 100%
+Цвет:  черный
+Пол:  Женский
+Сезон:  демисезон
+Рост модели на фото:  175 см
+Температурный режим:  от -5 °C до +10 °C
+Покрой:  оверсайз
+Тип карманов:  прорезные
+Тип рукава:  длинные
+Особенности модели:  Без капюшона, теплый
+Уход за вещами:  Химическая стирка; стирка запрещена; отбеливание запрещено
+Комплектация:  1 шт
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>https://basket-19.wbbasket.ru/vol3244/part324425/324425182/images/big/1.webp, https://basket-19.wbbasket.ru/vol3244/part324425/324425182/images/big/2.webp, https://basket-19.wbbasket.ru/vol3244/part324425/324425182/images/big/3.webp, https://basket-19.wbbasket.ru/vol3244/part324425/324425182/images/big/4.webp, https://basket-19.wbbasket.ru/vol3244/part324425/324425182/images/big/5.webp, https://basket-19.wbbasket.ru/vol3244/part324425/324425182/images/big/6.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/26800702/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>26800702</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Пальто демисезонное большие размеры</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>8002</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Primadonna</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/47927</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>48, 50, 52, 54, 60</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>5</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Женское пальто бренда PDONNA выполнено из натуральной шерсти, свободного кроя. Модель имеет застёжку -пуговицы, воротник- стойка, карманы прорезные с листочкой. Эта модель подчеркнёт Вашу фигуру и создаст элегантный образ. Пальто прекрасно сочетается как с классическими брюками и юбкой, так и с вечернем платьем. При заказе обязательно сверьтесь с нашей таблицей размеров.</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Состав:  полиэстер; шерсть; текстиль
+Цвет:  коралловый
+Сезон:  демисезон
+Вид застежки:  пуговицы; кнопки
+Утеплитель:  полиэстер
+Температурный режим:  +5 до +15
+Материал подкладки:  полиэстер
+Покрой:  свободный
+Тип карманов:  прорезные
+Тип рукава:  длинные
+Опции капюшона:  без капюшона
+Опции опушки:  без опушки
+Декоративные элементы:  без элементов
+Особенности модели:  износостойкость
+Конструктивные элементы:  воротник
+Пол:  Женский
+Уход за вещами:  деликатная химическая чистка
+Комплектация:  пальто женское демисезонное -1 шт
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>https://basket-02.wbbasket.ru/vol268/part26800/26800702/images/big/1.webp, https://basket-02.wbbasket.ru/vol268/part26800/26800702/images/big/2.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/500685157/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>500685157</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Пальто укороченное шерстяное прямое</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11276</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Rendez-Vous</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/528630</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>S, M, XS, L, XL</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Бежевое полупальто женское французского бренда Maison David. Состав: 100% шерсть натуральная. Шерсть отлично согревает, при этом позволяет телу дышать, не создавая парникового эффекта. В шерстяных вещах тепло, но не жарко. Одежда из шерсти — идеальный выбор для зимы и холодного демисезона. Состав подкладки: полиэстер, вискоза.
+Верхняя одежда имеет прямой силуэт. Модель отличает отложной воротник и наличие прорезных карманов. Температурный режим от плюс 10 до минус 5.
+Ухаживайте за вещью правильно, чтобы она дольше служила и радовала вас. Правила по уходу указаны на вшивном ярлычке изделия. Разрешено: химчистка. Запрещено: стирка, отбеливание, глажка, барабанная сушка.
+Полупальто в элегантном стиле BCBG — превосходный выбор для рабочих или повседневных образов. Одежда в стиле BCBG (bon chic bon genre) станет хорошей инвестицией в базовый гардероб. Maison David — дом современной элегантности. Бренд отражает идею французского bon chic, bon genre: искусство быть безупречным без усилий, сочетая гармонию интеллекта и формы, а качество становится главным языком красоты. Бренд соединяет современные тенденции с классическими формами, сохраняя баланс между актуальностью и вечностью. Каждая вещь Maison David создается, чтобы жить долго — сопровождать своего владельца в реальной, настоящей жизни: в работе, в путешествиях, в личных историях. Это не просто гардероб, а состояние уравновешенности и эстетического покоя.</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Состав:  шерсть натуральная 100%
+Цвет:  темно-бежевый
+Сезон:  демисезон
+Рост модели на фото:  175 см
+Температурный режим:  от -5 °C до +10 °C
+Покрой:  прямой
+Воротник:  отложной
+Тип карманов:  прорезные
+Особенности модели:  Без капюшона, теплый
+Пол:  Женский
+Уход за вещами:  Химическая стирка; стирка запрещена; отбеливание запрещено
+Комплектация:  1 шт
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>https://basket-27.wbbasket.ru/vol5006/part500685/500685157/images/big/1.webp, https://basket-27.wbbasket.ru/vol5006/part500685/500685157/images/big/2.webp, https://basket-27.wbbasket.ru/vol5006/part500685/500685157/images/big/3.webp, https://basket-27.wbbasket.ru/vol5006/part500685/500685157/images/big/4.webp, https://basket-27.wbbasket.ru/vol5006/part500685/500685157/images/big/5.webp, https://basket-27.wbbasket.ru/vol5006/part500685/500685157/images/big/6.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/710155258/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>710155258</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Пальто шерстяное весна-осень</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>4812</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>GUANGUANGUAN</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/250083754</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>L, M, S, XS</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>10</v>
+      </c>
+      <c r="I15" t="n">
+        <v>5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Женское пальто из шерсти — ваша идеальная пара на осень и зиму!
+Этот элегантный фасон выполнен из премиальной шерстяной ткани (70% шерсть). Натуральный состав не только обеспечивает исключительную теплоизоляцию и комфорт даже в холодную погоду, но и отличается долговечностью.
+Современный дизайн соответствует последним трендам и делает пальто универсальным предметом гардероба. Оно идеально подойдет для повседневной носки, прогулок и деловых встреч.
+Благодаря лаконичному стилю, пальто легко сочетается с любой обувью и аксессуарами, позволяя создавать безупречные образы для любого случая.
+Подарите себе уверенность в стиле и тепло!</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Состав:  70% шерсть
+Цвет:  зеленый
+Сезон:  демисезон
+Рост модели на фото:  168 см
+Температурный режим:  от -5 °C до +10 °C
+Материал подкладки:  без подклада
+Покрой:  прямой
+Тип рукава:  длинные
+Опции капюшона:  без капюшона
+Пол:  Женский</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>https://basket-34.wbbasket.ru/vol7101/part710155/710155258/images/big/1.webp, https://basket-34.wbbasket.ru/vol7101/part710155/710155258/images/big/2.webp, https://basket-34.wbbasket.ru/vol7101/part710155/710155258/images/big/3.webp, https://basket-34.wbbasket.ru/vol7101/part710155/710155258/images/big/4.webp, https://basket-34.wbbasket.ru/vol7101/part710155/710155258/images/big/5.webp, https://basket-34.wbbasket.ru/vol7101/part710155/710155258/images/big/6.webp, https://basket-34.wbbasket.ru/vol7101/part710155/710155258/images/big/7.webp, https://basket-34.wbbasket.ru/vol7101/part710155/710155258/images/big/8.webp, https://basket-34.wbbasket.ru/vol7101/part710155/710155258/images/big/9.webp, https://basket-34.wbbasket.ru/vol7101/part710155/710155258/images/big/10.webp, https://basket-34.wbbasket.ru/vol7101/part710155/710155258/images/big/11.webp, https://basket-34.wbbasket.ru/vol7101/part710155/710155258/images/big/12.webp, https://basket-34.wbbasket.ru/vol7101/part710155/710155258/images/big/13.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/246885839/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>246885839</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Пальто</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>24570</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Швейная фабрика Bella</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/47543</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>50, 52, 54, 56</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>18</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Демисезонная одежда нашей фабрики  станет любимым предметом гардероба, благодаря премиальному качеству и практичности.  Пальто женское - идеальный выбор для модных женщин, желающих подчеркнуть свой стиль в любое время года. У нас есть осенние модели, выполненные из шерсти и драпа, которые дарят уют и тепло. Демисезонное пальто - незаменимый элемент гардероба для межсезонья, что позволяет подобрать подходящую модель для любого сезона. Осенние модели отличаются стильным дизайном и практичностью. Теплое, утепленное изделие согреет в холодную погоду, ткань из шерсти с натуральным утеплителем идеально подходят для зимних морозных дней. Однобортное пальто халат с поясом и пуговицей создают максимальный комфорт и элегантность. Модели оверсайз и плюс сайз подойдут для полных женщин и беременных, обеспечивая свободу движений. Для подростков и молодых девушек мы предлагаем молодежные и стильные модели, которые подчеркивают индивидуальность и актуальность модных тенденций. Пальто с английским воротником, с качественной подкладкой и шерстяным утеплителем подчеркнут вашу индивидуальность и хороший вкус. Драповое пальто - это классика, проверенная временем, обладают высоким качеством и долговечностью. У нас есть пальто на запах, которые прекрасно подходят для еврозимы. Эти изделия больших размеров легкие и уютные, обеспечивающие комфорт при любой погоде. В нашем ассортименте представлены как длинные, так и макси модели. Длинное пальто - элегантное и утонченное, удлиненное пальто миди - это стильный выбор для тех, кто ценит моду и комфорт. Прямое и приталенное пальто идеально подчеркивает фигуру, создавая женственный силуэт. Каждое изделие имеет удобные глубокие карманы, что делает их функциональными и практичными, а рукава со спущенными реглан плечами обеспечивают свободу движений.</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Состав:  вирджинская шерсть 60%; мохер 18 %; полиамид 22%
+Цвет:  мокко
+Сезон:  демисезон
+Вид застежки:  кнопки
+Утеплитель:  нет
+Температурный режим:  до 0°С
+Материал подкладки:  вискоза 45%; полиэстер 55%
+Покрой:  прямой
+Тип карманов:  прорезные
+Тип рукава:  цельнокроенный
+Опции капюшона:  без капюшона
+Декоративные элементы:  пуговицы
+Особенности модели:  однобортная
+Пол:  Женский
 Уход за вещами:  химическая чистка
-Комплектация:  Пальто -1шт, пояс -1 шт.
-Страна производства:  Беларусь</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>https://basket-39.wbbasket.ru/vol8935/part893553/893553381/images/big/1.webp, https://basket-39.wbbasket.ru/vol8935/part893553/893553381/images/big/2.webp, https://basket-39.wbbasket.ru/vol8935/part893553/893553381/images/big/3.webp, https://basket-39.wbbasket.ru/vol8935/part893553/893553381/images/big/4.webp, https://basket-39.wbbasket.ru/vol8935/part893553/893553381/images/big/5.webp, https://basket-39.wbbasket.ru/vol8935/part893553/893553381/images/big/6.webp, https://basket-39.wbbasket.ru/vol8935/part893553/893553381/images/big/7.webp, https://basket-39.wbbasket.ru/vol8935/part893553/893553381/images/big/8.webp, https://basket-39.wbbasket.ru/vol8935/part893553/893553381/images/big/9.webp, https://basket-39.wbbasket.ru/vol8935/part893553/893553381/images/big/10.webp, https://basket-39.wbbasket.ru/vol8935/part893553/893553381/images/big/11.webp, https://basket-39.wbbasket.ru/vol8935/part893553/893553381/images/big/12.webp, https://basket-39.wbbasket.ru/vol8935/part893553/893553381/images/big/13.webp, https://basket-39.wbbasket.ru/vol8935/part893553/893553381/images/big/14.webp, https://basket-39.wbbasket.ru/vol8935/part893553/893553381/images/big/15.webp, https://basket-39.wbbasket.ru/vol8935/part893553/893553381/images/big/16.webp</t>
+Комплектация:  пальто
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>https://basket-16.wbbasket.ru/vol2468/part246885/246885839/images/big/1.webp, https://basket-16.wbbasket.ru/vol2468/part246885/246885839/images/big/2.webp, https://basket-16.wbbasket.ru/vol2468/part246885/246885839/images/big/3.webp, https://basket-16.wbbasket.ru/vol2468/part246885/246885839/images/big/4.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/505463412/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>505463412</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Пальто длинное макси</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>14215</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>МАГАЗИН</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/28213</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>42/164, 44/164, 46/164, 48/164, 50/164, 52/164, 54/164</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Роскошное женское пальто макси из натуральной шерсти — тренд осени!
+Элегантное длинное пальто в пол из натуральной шерсти (50%) — это безупречный выбор для тех, кто ценит стиль, комфорт и качество. Классический, но модный фасон с отложным воротником, длинным рукавом и застёжкой на пуговицах подчеркнёт вашу утончённость. Удобная шлица добавляет свободу движений, а свободный крой oversize делает пальто идеальным даже для беременных.
+Объёмное пальто согреет вас в осенние холода и мягкую еврозиму. В наличии большие размеры — каждая женщина найдёт свой идеальный вариант.
+Сочетайте с чем угодно: пальто макси легко впишется в любой образ, добавляя ему лаконичность и выразительность. Подарите себе стиль и уют этой осенью!</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Состав:  50% шерсть 33% акрил 17% спандекс
+Цвет:  инжирный; фиолетово-баклажанный; сине-фиолетовый; сиреневый
+Сезон:  демисезон
+Вид застежки:  пуговицы
+Рост модели на фото:  169 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  78-60-88
+Размер на модели:  42/164
+Утеплитель:  без утеплителя
+Температурный режим:  от +5 °C до +20 °C
+Материал подкладки:  Вискоза 55% Полиэстер 45%
+Покрой:  оверсайз
+Тип карманов:  с клапаном; прорезные
+Тип рукава:  длинные
+Опции капюшона:  Без капюшона пальто демисезонное
+Опции опушки:  Без опушки и меха
+Декоративные элементы:  пуговицы
+Особенности модели:  ветрозащита
+Конструктивные элементы:  оверсайз посадка большие размеры
+Пол:  Женский
+Уход за вещами:  деликатная химическая чистка
+Комплектация:  пальто оверсайз; пакет; пальто женское осеннее; пояс; шуба женская; для будущих мам; большие размеры; пальто длинное; верхняя одежда для женщин
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>https://basket-27.wbbasket.ru/vol5054/part505463/505463412/images/big/1.webp, https://basket-27.wbbasket.ru/vol5054/part505463/505463412/images/big/2.webp, https://basket-27.wbbasket.ru/vol5054/part505463/505463412/images/big/3.webp, https://basket-27.wbbasket.ru/vol5054/part505463/505463412/images/big/4.webp, https://basket-27.wbbasket.ru/vol5054/part505463/505463412/images/big/5.webp, https://basket-27.wbbasket.ru/vol5054/part505463/505463412/images/big/6.webp, https://basket-27.wbbasket.ru/vol5054/part505463/505463412/images/big/7.webp, https://basket-27.wbbasket.ru/vol5054/part505463/505463412/images/big/8.webp, https://basket-27.wbbasket.ru/vol5054/part505463/505463412/images/big/9.webp, https://basket-27.wbbasket.ru/vol5054/part505463/505463412/images/big/10.webp, https://basket-27.wbbasket.ru/vol5054/part505463/505463412/images/big/11.webp, https://basket-27.wbbasket.ru/vol5054/part505463/505463412/images/big/12.webp, https://basket-27.wbbasket.ru/vol5054/part505463/505463412/images/big/13.webp, https://basket-27.wbbasket.ru/vol5054/part505463/505463412/images/big/14.webp, https://basket-27.wbbasket.ru/vol5054/part505463/505463412/images/big/15.webp, https://basket-27.wbbasket.ru/vol5054/part505463/505463412/images/big/16.webp, https://basket-27.wbbasket.ru/vol5054/part505463/505463412/images/big/17.webp, https://basket-27.wbbasket.ru/vol5054/part505463/505463412/images/big/18.webp, https://basket-27.wbbasket.ru/vol5054/part505463/505463412/images/big/19.webp, https://basket-27.wbbasket.ru/vol5054/part505463/505463412/images/big/20.webp, https://basket-27.wbbasket.ru/vol5054/part505463/505463412/images/big/21.webp, https://basket-27.wbbasket.ru/vol5054/part505463/505463412/images/big/22.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/246400178/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>246400178</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Пальто с капюшоном демисезонное</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>18252</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Швейная фабрика Bella</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/47543</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>42, 44, 46, 48</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4</v>
+      </c>
+      <c r="J18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Демисезонная одежда нашей фабрики  станет любимым предметом гардероба, благодаря премиальному качеству и практичности.  Пальто женское - идеальный выбор для модных женщин, желающих подчеркнуть свой стиль в любое время года. У нас есть осенние модели, выполненные из шерсти и драпа, которые дарят уют и тепло. Демисезонное пальто - незаменимый элемент гардероба для межсезонья, что позволяет подобрать подходящую модель для любого сезона. Осенние модели отличаются стильным дизайном и практичностью. Теплое, утепленное изделие согреет в холодную погоду, ткань из шерсти с натуральным утеплителем идеально подходят для зимних морозных дней. Однобортное пальто халат с поясом и пуговицей создают максимальный комфорт и элегантность. Модели оверсайз и плюс сайз подойдут для полных женщин и беременных, обеспечивая свободу движений. Для подростков и молодых девушек мы предлагаем молодежные и стильные модели, которые подчеркивают индивидуальность и актуальность модных тенденций. Пальто с английским воротником, с качественной подкладкой и шерстяным утеплителем подчеркнут вашу индивидуальность и хороший вкус. Драповое пальто - это классика, проверенная временем, обладают высоким качеством и долговечностью. У нас есть пальто на запах, которые прекрасно подходят для еврозимы. Эти изделия больших размеров легкие и уютные, обеспечивающие комфорт при любой погоде. В нашем ассортименте представлены как длинные, так и макси модели. Длинное пальто - элегантное и утонченное, удлиненное пальто миди - это стильный выбор для тех, кто ценит моду и комфорт. Прямое и приталенное пальто идеально подчеркивает фигуру, создавая женственный силуэт. Каждое изделие имеет удобные глубокие карманы, что делает их функциональными и практичными, а рукава со спущенными реглан плечами обеспечивают свободу движений.</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Состав:  шерсть 70%; полиэстер 20%; нейлон 10%
+Цвет:  мокко
+Пол:  Женский
+Сезон:  Демисезон
+Вид застежки:  кнопки; 1 навесная петля + пуговица
+Температурный режим:  от +5 °C до +10 °C
+Материал подкладки:  вискоза 45%; полиэстер 55%
+Покрой:  прямой
+Тип карманов:  Прорезной в листочку
+Тип рукава:  Втачные
+Опции капюшона:  несъемный капюшон
+Опции опушки:  без опушки
+Декоративные элементы:  пуговицы
+Уход за вещами:  химическая чистка
+Комплектация:  пальто; пояс
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>https://basket-16.wbbasket.ru/vol2464/part246400/246400178/images/big/1.webp, https://basket-16.wbbasket.ru/vol2464/part246400/246400178/images/big/2.webp, https://basket-16.wbbasket.ru/vol2464/part246400/246400178/images/big/3.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/581396639/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>581396639</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>пальто шерстяное длинное с жилеткой</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>5624</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Aura</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/250060379</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>M, S</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" t="n">
+        <v>9</v>
+      </c>
+      <c r="J19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>женское шерстяное пальто — ваш идеальный спутник осенью и зимой!
+эта модель создана из высококачественной шерстяной ткани (70,8% овечья шерсть). натуральные волокна не только обеспечивают превосходную теплоизоляцию и комфорт даже в холодную погоду, но и отличаются долговечностью. искусная работа мастеров воплощает безупречное качество, обеспечивающее комфорт при носке.
+современный дизайн соответствует актуальным трендам, создавая универсальную вещь для разных ситуаций. будь то повседневная носка, прогулки или деловые встречи — пальто безупречно выполнит свою роль. даже в зимних многослойных образах вы легко создадите изысканный силуэт.
+лаконичный стиль легко комбинируется с любой обувью и аксессуарами, помогая создавать утонченные образы для любых сценариев.
+подарите себе не только теплую защиту, но и непревзойденное чувство стиля!</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Состав:  70.8% шерсти
+Цвет:  серый
+Пол:  Женский
+Сезон:  демисезон
+Рост модели на фото:  168 см
+Температурный режим:  от -5 °C до +10 °C
+Покрой:  прямой
+Тип рукава:  длинные
+Опции капюшона:  без капюшона
+Декоративные элементы:  жилет</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>https://basket-29.wbbasket.ru/vol5813/part581396/581396639/images/big/1.webp, https://basket-29.wbbasket.ru/vol5813/part581396/581396639/images/big/2.webp, https://basket-29.wbbasket.ru/vol5813/part581396/581396639/images/big/3.webp, https://basket-29.wbbasket.ru/vol5813/part581396/581396639/images/big/4.webp, https://basket-29.wbbasket.ru/vol5813/part581396/581396639/images/big/5.webp, https://basket-29.wbbasket.ru/vol5813/part581396/581396639/images/big/6.webp, https://basket-29.wbbasket.ru/vol5813/part581396/581396639/images/big/7.webp, https://basket-29.wbbasket.ru/vol5813/part581396/581396639/images/big/8.webp, https://basket-29.wbbasket.ru/vol5813/part581396/581396639/images/big/9.webp, https://basket-29.wbbasket.ru/vol5813/part581396/581396639/images/big/10.webp, https://basket-29.wbbasket.ru/vol5813/part581396/581396639/images/big/11.webp, https://basket-29.wbbasket.ru/vol5813/part581396/581396639/images/big/12.webp, https://basket-29.wbbasket.ru/vol5813/part581396/581396639/images/big/13.webp, https://basket-29.wbbasket.ru/vol5813/part581396/581396639/images/big/14.webp, https://basket-29.wbbasket.ru/vol5813/part581396/581396639/images/big/15.webp, https://basket-29.wbbasket.ru/vol5813/part581396/581396639/images/big/16.webp, https://basket-29.wbbasket.ru/vol5813/part581396/581396639/images/big/17.webp, https://basket-29.wbbasket.ru/vol5813/part581396/581396639/images/big/18.webp, https://basket-29.wbbasket.ru/vol5813/part581396/581396639/images/big/19.webp, https://basket-29.wbbasket.ru/vol5813/part581396/581396639/images/big/20.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/175466058/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>175466058</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Пальто демисезонное длинное с капюшоном из шерсти еврозима</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>30515</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>KROYYORK</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/25326</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>40, 42, 44, 46</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>5</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Элегантное пальто женское демисезонное с капюшоном, от российского бренда KROYYORK.  
+Благодаря ворсистой структуре ткани оно смотрится как натуральная шуба из стриженной норки или пальто из кашемира. Верхняя одежда из шерсти альпака с добавлением натуральной овечьей шерсти оверсайз с подкладкой из вискозы, которая не электризуется и приятна к телу. Пальто женское модное из материала premium качества не мнется.
+Пальто весеннее для женщин больших размеров с цельнокроеным рукавом,  выверенным кроем и превосходным качеством швов дополняют  удобные прорезные карманы с листочкой, застежка на кнопки и внутреннюю пуговицу и пояс в тон.  
+Однобортное легкое осеннее пальто длинной 112 см.
+Оно хорошо сохраняет тепло, при этом на ощупь пальто довольно мягкое, материал износостойкий надолго сохраняет форму и безупречный вид. </t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Состав:  шерсть альпака 70%; шерсть овечья 20%; Шерсть 10%
+Цвет:  черно-синий; темно-синий
+Сезон:  демисезон
+Вид застежки:  кнопки; пояс
+Утеплитель:  без утеплителя
+Температурный режим:  от +10 °C до -5 °C
+Материал подкладки:  вискоза
+Покрой:  прямой
+Тип карманов:  прорезные
+Тип рукава:  длинные
+Опции капюшона:  несъемный капюшон
+Опции опушки:  без опушки
+Декоративные элементы:  отделочные строчки
+Особенности модели:  с подкладкой
+Конструктивные элементы:  капюшон
+Пол:  Женский
+Уход за вещами:  деликатная химическая чистка; допускается отпаривание
+Комплектация:  пальто женское; пояс
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>https://basket-12.wbbasket.ru/vol1754/part175466/175466058/images/big/1.webp, https://basket-12.wbbasket.ru/vol1754/part175466/175466058/images/big/2.webp, https://basket-12.wbbasket.ru/vol1754/part175466/175466058/images/big/3.webp, https://basket-12.wbbasket.ru/vol1754/part175466/175466058/images/big/4.webp, https://basket-12.wbbasket.ru/vol1754/part175466/175466058/images/big/5.webp, https://basket-12.wbbasket.ru/vol1754/part175466/175466058/images/big/6.webp, https://basket-12.wbbasket.ru/vol1754/part175466/175466058/images/big/7.webp, https://basket-12.wbbasket.ru/vol1754/part175466/175466058/images/big/8.webp, https://basket-12.wbbasket.ru/vol1754/part175466/175466058/images/big/9.webp, https://basket-12.wbbasket.ru/vol1754/part175466/175466058/images/big/10.webp, https://basket-12.wbbasket.ru/vol1754/part175466/175466058/images/big/11.webp, https://basket-12.wbbasket.ru/vol1754/part175466/175466058/images/big/12.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/846347977/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>846347977</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Демисезонное полупальто короткое для невысокого роста</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>25264</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>INICO</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/1165152</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>M/L, XS</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Модель разработана для миниатюрных девушек и женщин с учетом роста до 164 см.
+Демисезонное полупальто получилось легким, но исключительно теплым. Изделие выполнено из ворсистого материала с высоким содержанием натуральной шерсти, которая согревает, а искусственные волокна придают износоустойчивости. Изделие выполнено по технологии двусторонняя ткань, поэтому выглядит также безупречно с изнанки. Дополнительную защиту от холода и ветра создаст объемный капюшон, а талию можно подчеркнуть поясом из комплекта или оставить образ расслабленным.
+Рекомендованный температурный режим от 0°C до +10°C.
+•    Свободный крой
+•    Длина до середины бедра
+•    Модель без застежки
+•    Боковые карманы 
+•    Рукава-реглан
+•    В комплекте пояс из аналогичного материала 
+•    Изделие без подкладки
+Пальто женское весна-осень станет безупречным дополнением вашего гардероба, предлагая идеальный баланс между уютным теплом и современной городской эстетикой. Данное полупальто женское демисезонное выполнено из премиального ворсистого материала с высоким содержанием натуральной шерсти, которая превосходно согревает. Уникальная технология двусторонней ткани позволяет модели выглядеть роскошно даже с изнанки, подчеркивая высокий статус вещи и ваше внимание к деталям. Если вы ищете универсальный вариант для активных будней, то это пальто женское весна-осень короткое длиной до середины бедра обеспечит вам полную свободу движений благодаря свободному крою и мягким рукавам-реглан. Объемный капюшон послужит надежной защитой от капризного ветра, делая это пальто короткое женское максимально функциональным в период межсезонья. При составлении образов рекомендуем сочетать это пальто весеннее женское с классическими брюками и ботильонами для строгого офисного стиля или с широкими джинсами и ботинками. Пальто халат женское весна-осень, которое выгодно акцентирует талию и добавляет образу женственности. Это укороченное пальто женское станет незаменимым спутником для прогулок или деловых встреч. </t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>китай</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Состав:  50% шерсть,50% полиэстер
+Цвет:  бежевый
+Пол:  Женский
+Сезон:  демисезон
+Вид застежки:  без застежки
+Рост модели на фото:  175 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  91-60-93
+Размер на модели:  42
+Утеплитель:  без утеплителя
+Температурный режим:  от 0°C до +10°C
+Материал подкладки:  без подкладки
+Покрой:  укороченный
+Тип карманов:  прорезные
+Тип рукава:  длинные
+Опции капюшона:  несъемный капюшон
+Опции опушки:  без опушки
+Мех опушки/отделки:  без меха
+Декоративные элементы:  без элементов
+Особенности модели:  дышащий материал
+Уход за вещами:  Рекомендуем придерживаться информации со вшивной этикетки при уходе за изделием
+Комплектация:  пальто 1 шт
+Страна производства:  Китай</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>https://basket-38.wbbasket.ru/vol8463/part846347/846347977/images/big/1.webp, https://basket-38.wbbasket.ru/vol8463/part846347/846347977/images/big/2.webp, https://basket-38.wbbasket.ru/vol8463/part846347/846347977/images/big/3.webp, https://basket-38.wbbasket.ru/vol8463/part846347/846347977/images/big/4.webp, https://basket-38.wbbasket.ru/vol8463/part846347/846347977/images/big/5.webp, https://basket-38.wbbasket.ru/vol8463/part846347/846347977/images/big/6.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/307618866/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>307618866</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Пальто весна-осень длинное</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>14826</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Mmoda</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/37302</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>38, 40, 42, 44, 46, 48</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>5</v>
+      </c>
+      <c r="J22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Представляем вашему вниманию элегантное женское пальто, идеально подходящее для демисезонного периода весной и осенью. Изделие выполнено из натуральной шерсти, с добавлением вискозы и полиэстера, такое сочетание материалов делает его приятным и практичным для повседневного ношения.
+Зауженный к низу крой придаёт современный и утончённый вид, а качественный подклад обеспечивает дополнительный комфорт.
+Модель идёт с английским воротником и удобной застёжкой на кнопку. Карманы в боковых швах повышают функциональность, а пояс формирует изящный силуэт, подчёркивая талию.
+Пальто оверсайз оптимальной длины подходит для любой фигуры и роста. В нём вы будете выглядеть модно и стильно, соответствуя актуальным трендам.
+Это длинное пальто — превосходный выбор для тех, кто ценит уют и изящность в одежде.</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Состав:  шерсть 75%; вискоза 15%; терилен 10%
+Цвет:  серый; средне-серый меланж; серый меланж
+Пол:  Женский
+Сезон:  Демисезон
+Вид застежки:  кнопки
+Рост модели на фото:  170 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  80-57-88
+Размер на модели:  42
+Утеплитель:  без утеплителя
+Температурный режим:  от 0 °C до +15 °C
+Материал подкладки:  вискоза 53%; полиэстер 47%
+Покрой:  свободный
+Тип карманов:  в шве
+Тип рукава:  длинные
+Опции капюшона:  без капюшона
+Опции опушки:  без опушки
+Особенности модели:  двубортная; дышащий материал; воздухопроницаемость
+Уход за вещами:  стирка запрещена; химическая чистка разрешена; Рекомендуется отпаривание
+Комплектация:  пальто - 1шт; пояс - 1шт; Вешалка - 1шт
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>https://basket-19.wbbasket.ru/vol3076/part307618/307618866/images/big/1.webp, https://basket-19.wbbasket.ru/vol3076/part307618/307618866/images/big/2.webp, https://basket-19.wbbasket.ru/vol3076/part307618/307618866/images/big/3.webp, https://basket-19.wbbasket.ru/vol3076/part307618/307618866/images/big/4.webp, https://basket-19.wbbasket.ru/vol3076/part307618/307618866/images/big/5.webp, https://basket-19.wbbasket.ru/vol3076/part307618/307618866/images/big/6.webp, https://basket-19.wbbasket.ru/vol3076/part307618/307618866/images/big/7.webp, https://basket-19.wbbasket.ru/vol3076/part307618/307618866/images/big/8.webp, https://basket-19.wbbasket.ru/vol3076/part307618/307618866/images/big/9.webp, https://basket-19.wbbasket.ru/vol3076/part307618/307618866/images/big/10.webp, https://basket-19.wbbasket.ru/vol3076/part307618/307618866/images/big/11.webp, https://basket-19.wbbasket.ru/vol3076/part307618/307618866/images/big/12.webp, https://basket-19.wbbasket.ru/vol3076/part307618/307618866/images/big/13.webp, https://basket-19.wbbasket.ru/vol3076/part307618/307618866/images/big/14.webp, https://basket-19.wbbasket.ru/vol3076/part307618/307618866/images/big/15.webp, https://basket-19.wbbasket.ru/vol3076/part307618/307618866/images/big/16.webp, https://basket-19.wbbasket.ru/vol3076/part307618/307618866/images/big/17.webp, https://basket-19.wbbasket.ru/vol3076/part307618/307618866/images/big/18.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/563430980/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>563430980</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Пальто демисезонное классическое</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>12639</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Мужские костюмы  СПЕКТР</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/237700</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>48-176, 48-182, 50-176, 50-182, 52-176, 52-182, 54-176, 54-182, 56-176, 56-182</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Откройте для себя стиль и комфорт с великолепной линейкой верхней одежды, созданной специально для мужчин. Представляем вашему вниманию разнообразие моделей пальто мужское на все случаи жизни. Демисезонные варианты идеально подойдут как для весны, так и для осени (осеннее). Вы найдете здесь укороченные и длинные изделия, среди которых легко выбрать то, что подходит именно вам. Мужской гардероб сложно представить без классического пальто на зиму зимнее. Оно не только добавляет тепла в снежную погоду, но и преображает образ, придавая ему элегантности и изысканности. Наши модели могут похвастаться такими особенностями, как двубортный крой и использование надежной фурнитуры: пуговицы или молнии. Например, модели с капюшоном оказываются практичными в ненастную погоду. Вы ищете современный и молодежный стиль? Короткое утепленное оверсайз полупальто или удлиненные фасоны идеально подчеркнут вашу индивидуальность, как и большие размеры. Молодежная категория порадует удобством, подчеркивающим смелость и уверенность своего обладателя. Наша коллекция славится не только дизайном, но и разнообразием материалов - от шерстяного до драпового полотна. Эти ткани создают идеальное сочетание легкости и утепления в холодное время года. Добавление меха к некоторым моделям драп обеспечит особое чувство уюта. Кто предпочитает более лаконичные решения, существуют пальто в классическом стиле: приталенные силуэты предлагают выразительность даже в спокойных тонах — серый или бежевый, коричневый идеально подойдут под любую составляющую вашего ансамбля. Если ваш выбор пал на клетку -знайте это беспроигрышный вариант! Такой узор всегда будет актуальным вне зависимости от времени года или модного сезона. Особое внимание уделено теплым моделям с фактурной конструкцией из натуральной шерсти: они обеспечат хороший уровень защиты от холода благодаря своим уникальным свойствам удерживать тепло. Черные модели демократичны в своем использовании — настоящее олицетворение универсальности доступного стиля.</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Состав:  шерсть 35 %; вискоза 45 %; пэ 17 %; лайкра 3 %
+Цвет:  серый; серый меланж; светло-серый
+Сезон:  демисезон
+Вид застежки:  пуговицы
+Рост модели на фото:  175 см
+Размер на модели:  50
+Утеплитель:  синтепон
+Температурный режим:  от +5 °C до -10 °C
+Материал подкладки:  полиэстер
+Покрой:  приталенный
+Тип карманов:  прорезные
+Тип рукава:  длинные
+Опции капюшона:  без капюшона
+Опции опушки:  без опушки
+Мех опушки/отделки:  без меха
+Декоративные элементы:  карманы
+Особенности модели:  на каждый день; пальто френч мужское
+Конструктивные элементы:  отложной ворот
+Пол:  Мужской
+Уход за вещами:  деликатная химическая чистка
+Комплектация:  Пальто мужское 1 шт
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>https://basket-29.wbbasket.ru/vol5634/part563430/563430980/images/big/1.webp, https://basket-29.wbbasket.ru/vol5634/part563430/563430980/images/big/2.webp, https://basket-29.wbbasket.ru/vol5634/part563430/563430980/images/big/3.webp, https://basket-29.wbbasket.ru/vol5634/part563430/563430980/images/big/4.webp, https://basket-29.wbbasket.ru/vol5634/part563430/563430980/images/big/5.webp, https://basket-29.wbbasket.ru/vol5634/part563430/563430980/images/big/6.webp, https://basket-29.wbbasket.ru/vol5634/part563430/563430980/images/big/7.webp, https://basket-29.wbbasket.ru/vol5634/part563430/563430980/images/big/8.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/226696220/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>226696220</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Пальто длинное демисезонное шерсть</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>5062</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Professional Manufakture</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/46086</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>42, 44, 46, 48, 50</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Пальто женское на осень от бренда Professional Manufakture. Пальто халат с идеальной посадкой подчеркивает ваши достоинства, глубокие накладные  карманы делают его удобным и практичным. ЗАСТЕЖКА ПУГОВИЦЫ. Это не просто одежда для одного сезона, это демисезонное пальто на осень, зиму и весну, которое готово защитить вас от любых погодных капризов: будь то снеговая завеса, осенний дождь или ветреная пурга C. Благодаря высокому качеству утепленного материала с добавлением натуральной шерсти, вы будете ощущать тепло и уют в любую погоду. Длина моделей – чуть ниже колена миди, что делает это осеннее пальто универсальным решением для всех женщин, девушек и девочек подростков, независимо от роста. Оно подходит как для повседневных прогулок по городу, в офис на работу, в школу, так и для вечерних мероприятий, где вы будете сиять своим стильным образом. Каждая деталь этого весеннего пальто из драпа продумана до мельчайших нюансов. Качественная фурнитура в виде пуговиц будет долго служить в носке. Двубортный воротник подчеркивают линию шеи. Тщательная ручная работа и безукоризненная посадка гарантируют, что этот элемент верхней одежды станет незаменимой частью вашего гардероба на долгие годы.  Уважаемые покупатели прощу вас, когда возврашаете товар сложите и аккуратно положите в пакет. Уважайте себя и чужой труд. Не теряйте ремень пожалуйста. </t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Состав:  70%шерсть 30%полиэстер
+Цвет:  бежевый; зеленый
+Сезон:  демисезон
+Вид застежки:  пуговицы; пояс
+Рост модели на фото:  175 см
+Размер на модели:  46
+Длина изделия по спинке:  120 см
+Температурный режим:  от +10 °C до -1 °C
+Материал подкладки:  полиэстер; вискоза
+Покрой:  прямой
+Тип карманов:  накладные
+Тип рукава:  длинные
+Опции капюшона:  без капюшона
+Опции опушки:  без опушки
+Декоративные элементы:  Английский воротник
+Особенности модели:  Элегантность
+Конструктивные элементы:  на запах
+Пол:  Женский
+Уход за вещами:  деликатная химическая чистка
+Комплектация:  пальто; пояс
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>https://basket-15.wbbasket.ru/vol2266/part226696/226696220/images/big/1.webp, https://basket-15.wbbasket.ru/vol2266/part226696/226696220/images/big/2.webp, https://basket-15.wbbasket.ru/vol2266/part226696/226696220/images/big/3.webp, https://basket-15.wbbasket.ru/vol2266/part226696/226696220/images/big/4.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/246473031/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>246473031</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>пальто зимнее твидовое с мехом натуральным на ватине</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>14882</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Элегант</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/40236</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>164-112-122, 164-96-106, 164-100-110, 164-104-114, 164-108-118, 164-116-126, 164-120-130, 164-124-134</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>80</v>
+      </c>
+      <c r="J25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Представляем вам наше утепленное женское зимнее пальто без капюшона. Великолепное сочетание стиля и комфорта! Воротник отложной из натурального меха придает пальто изысканность и элегантность. Изготовленное из твидовой ткани, оно подчеркнет вашу индивидуальность и добавит нотку модного шика в ваш повседневный или праздничный образ.
+Силуэт трапеция ласкает фигуру и создает женственные линии. Утепленное шерстяным ватином, наше пальто обеспечит вам непревзойденное тепло и комфорт в холодные зимние дни. Рукав длинный полуреглан придает пальто свободный и стильный вид.
+Для вашего удобства, пальто доступно в больших размерах и рассчитано на рост 164 см и выше. Используя только высококачественные материалы, мы создали шерстяное пальто, легкое и уютное, не ограничивающее движение.
+Наше пальто - это не только тепло и комфорт, но и модный акцент в вашем гардеробе. Качественный пошив гарантирует долговечность и удовлетворение вашего вкуса. Не упустите возможность ощутить настоящий комфорт и элегантность с нашим женским зимним пальто!</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Состав:  шерсть 60%; полиэстер 40%
+Цвет:  коричневый
+Пол:  Женский
+Сезон:  Зима
+Вид застежки:  пуговицы
+Рост модели на фото:  170 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  90-75-96
+Размер на модели:  48
+Утеплитель:  ватин
+Плотность синтетического утеплителя:  250 г/кв.м
+Температурный режим:  от -5 до -15
+Материал подкладки:  полиэстер
+Покрой:  трапеция
+Тип карманов:  в шве
+Тип рукава:  длинные
+Опции капюшона:  без капюшона
+Опции опушки:  без опушки
+Особенности модели:  дышащий материал
+Уход за вещами:  деликатная химическая чистка; отбеливание запрещено
+Комплектация:  пальто-1 шт
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>https://basket-16.wbbasket.ru/vol2464/part246473/246473031/images/big/1.webp, https://basket-16.wbbasket.ru/vol2464/part246473/246473031/images/big/2.webp, https://basket-16.wbbasket.ru/vol2464/part246473/246473031/images/big/3.webp, https://basket-16.wbbasket.ru/vol2464/part246473/246473031/images/big/4.webp, https://basket-16.wbbasket.ru/vol2464/part246473/246473031/images/big/5.webp, https://basket-16.wbbasket.ru/vol2464/part246473/246473031/images/big/6.webp, https://basket-16.wbbasket.ru/vol2464/part246473/246473031/images/big/7.webp, https://basket-16.wbbasket.ru/vol2464/part246473/246473031/images/big/8.webp, https://basket-16.wbbasket.ru/vol2464/part246473/246473031/images/big/9.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/250798523/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>250798523</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Пальто демисезонное длинное оверсайз</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>3411</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>LadiesGard</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/1196458</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>42, 44, 46, 48</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>93</v>
+      </c>
+      <c r="J26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Пальто женское демисезонное длинное оверсайз – базовый предмет гардероба и тренд сезона осень-зима 2024-2025. Удлиненная драповая модель на запах с двубортным дизайном подчеркнет элегантность, а прямой свободный oversize крой подойдет девушкам, девочкам подросткам в школу и полным plus size. Кашемировое с английским воротником на любую фигуру и рост, высоким и невысоким. Оно легкое и приятное на ощупь, оснащено пуговицами и поясом для дополнительного комфорта и поддержания формы, по желанию вы сможете создать приталенный силуэт. Универсальное широкое шерстяное осеннее пальтишко со спущенными большими реглан плечами обеспечивают свободу движений. Оверсайз крой создаст неповторимый образ в корейском стиле y2k. Красивый разрез со спины must-have для каждой модницы! Вместительные карманы с клапаном добавляют удобство и практичность. Верхняя одежда для вечерних прогулок в межсезонье, на весну осень. Классическое теплое серое зимнее пальто выполнено из высококачественной шерсти с подкладом из полиэстера, не тяжелое и комфортное в повседневной носке. Идеально для создания многослойных образов на каждый день - от офисного до спортивного и молодежного городского casual и тематической фотосессии как в пинтерест (Pinterest).</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Состав:  шерсть 55%; акрил 40%; полиэстер 5%
+Цвет:  серый; серый меланж; натуральный серый
+Сезон:  демисезон
+Размер на модели:  42
+Рост модели на фото:  168 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  80-60-90
+Утеплитель:  нет
+Температурный режим:  от -5 °C до +10 °C
+Материал подкладки:  полиэстер 100%
+Страна производства:  Россия
+Вид застежки:  пуговицы; пояс
+Особенности модели:  двубортное пальто из шерсти; износостойкость; с широкими плечами
+Опции капюшона:  без капюшона
+Опции опушки:  без опушки
+Декоративные элементы:  шлица; пояс; oversize
+Тип карманов:  с клапаном; врезной; листочка
+Конструктивные элементы:  шлевки
+Пол:  Женский
+Тип рукава:  длинные
+Комплектация:  Пальто женское - 1 шт., пояс - 1 шт.
+Покрой:  прямой
+Уход за вещами:  деликатная химическая чистка; стирка запрещена</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>https://basket-16.wbbasket.ru/vol2507/part250798/250798523/images/big/1.webp, https://basket-16.wbbasket.ru/vol2507/part250798/250798523/images/big/2.webp, https://basket-16.wbbasket.ru/vol2507/part250798/250798523/images/big/3.webp, https://basket-16.wbbasket.ru/vol2507/part250798/250798523/images/big/4.webp, https://basket-16.wbbasket.ru/vol2507/part250798/250798523/images/big/5.webp, https://basket-16.wbbasket.ru/vol2507/part250798/250798523/images/big/6.webp, https://basket-16.wbbasket.ru/vol2507/part250798/250798523/images/big/7.webp, https://basket-16.wbbasket.ru/vol2507/part250798/250798523/images/big/8.webp, https://basket-16.wbbasket.ru/vol2507/part250798/250798523/images/big/9.webp, https://basket-16.wbbasket.ru/vol2507/part250798/250798523/images/big/10.webp, https://basket-16.wbbasket.ru/vol2507/part250798/250798523/images/big/11.webp, https://basket-16.wbbasket.ru/vol2507/part250798/250798523/images/big/12.webp, https://basket-16.wbbasket.ru/vol2507/part250798/250798523/images/big/13.webp, https://basket-16.wbbasket.ru/vol2507/part250798/250798523/images/big/14.webp, https://basket-16.wbbasket.ru/vol2507/part250798/250798523/images/big/15.webp, https://basket-16.wbbasket.ru/vol2507/part250798/250798523/images/big/16.webp, https://basket-16.wbbasket.ru/vol2507/part250798/250798523/images/big/17.webp, https://basket-16.wbbasket.ru/vol2507/part250798/250798523/images/big/18.webp, https://basket-16.wbbasket.ru/vol2507/part250798/250798523/images/big/19.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/486838690/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>486838690</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Пальто оверсайз демисезонное шерстяное</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>7676</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>MA Style</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/1301294</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>42, 44, 46, 48</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>23</v>
+      </c>
+      <c r="J27" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Бренд MA Style представляет вам свою новую коллекцию - женское демисезонное пальто для весны. Это идеальное сочетание стиля, комфорта и функциональности, которое сделает ваш образ модным и неповторимым. Пальто - это неотъемлемая часть гардероба каждой стильной женщины. Ведь оно обеспечивает не только тепло и комфорт в холодные весенние дни, но и придает вашему образу неповторимый шарм. Наше выполнено из высококачественных материалов, чтобы удовлетворить даже самые взыскательные вкусы. Одной из особенностей является его универсальность. Оно подойдет как для весны, так и для осени благодаря своей средней длине и драповому фасону. Вы можете носить его как самостоятельную верхнюю одежду или с теплым свитером или кардиганом. Наши дизайнеры уделили особое внимание деталям, чтобы создать пальто, сочетающее в себе элегантность и практичность. Подкладка из полиэстера обеспечивает дополнительный комфорт и защиту от ветра, а натуральные материалы, такие как шерсть и вискоза, придают ему нежность и приятный на ощупь текстурный эффект. Сочетание оверсайз фасона, легкого материала и утепленной шерстяной подкладки создает идеальный баланс между комфортом и элегантностью. Доступно в большом размере и подходит для различных типов фигур - от стройных до полных, чтобы каждая женщина могла найти свой идеальный вариант. Выберите из нашей коллекции насещенный бордовый цвет, который подойдет к любому образу, или отважитесь на эксперименты с модными оттенками осенней палитры, такими как мокко. Добавьте наше женское пальто демисезон в свой гардероб и наслаждайтесь комфортом и стилем в любое время года. Это идеальный выбор для женщин, ценящих классику и моду. Не упускайте шанс приобрести наше оверсайз легкое, молодежное, утепленное, шерстяное пальто с большим размером прямо сейчас и завершить свой образ идеальным стилем. </t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>киргизия</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Состав:  шерсть; хлопок; вискоза; полиэстер
+Цвет:  бордовый; темно-бордовый; бургунди
+Сезон:  демисезон
+Вид застежки:  пуговицы; пояс
+Рост модели на фото:  166 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  83-59-88
+Размер на модели:  46
+Утеплитель:  без утеплителя
+Температурный режим:  от +10 °C до -5 °C
+Материал подкладки:  полиэстер
+Покрой:  прямой
+Тип карманов:  прорезные
+Тип рукава:  длинные
+Опции капюшона:  без капюшона
+Опции опушки:  без опушки
+Декоративные элементы:  погоны на плечах; кокетка; пояс
+Особенности модели:  ветрозащита; двубортная
+Конструктивные элементы:  спущенный рукав
+Пол:  Женский
+Уход за вещами:  деликатная химическая чистка
+Комплектация:  демисезонное женское пальто, пояс
+Страна производства:  Киргизия</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>https://basket-26.wbbasket.ru/vol4868/part486838/486838690/images/big/1.webp, https://basket-26.wbbasket.ru/vol4868/part486838/486838690/images/big/2.webp, https://basket-26.wbbasket.ru/vol4868/part486838/486838690/images/big/3.webp, https://basket-26.wbbasket.ru/vol4868/part486838/486838690/images/big/4.webp, https://basket-26.wbbasket.ru/vol4868/part486838/486838690/images/big/5.webp, https://basket-26.wbbasket.ru/vol4868/part486838/486838690/images/big/6.webp, https://basket-26.wbbasket.ru/vol4868/part486838/486838690/images/big/7.webp, https://basket-26.wbbasket.ru/vol4868/part486838/486838690/images/big/8.webp, https://basket-26.wbbasket.ru/vol4868/part486838/486838690/images/big/9.webp, https://basket-26.wbbasket.ru/vol4868/part486838/486838690/images/big/10.webp, https://basket-26.wbbasket.ru/vol4868/part486838/486838690/images/big/11.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/204971561/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>204971561</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Пальто весеннее шерсть альпака и овечья оверсайз еврозима</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>42120</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>KROYYORK</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/25326</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>46, 48, 52, 54, 56</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>5</v>
+      </c>
+      <c r="J28" t="n">
+        <v>4</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Элегантное пальто женское демисезонное от российского бренда KROYYORK.  
+Благодаря ворсистой структуре ткани оно смотрится как натуральная шуба из стриженной норки или пальто из кашемира. Верхняя одежда из шерсти альпака с добавлением натуральной овечьей шерсти оверсайз с подкладкой из вискозы, которая не электризуется и приятна к телу. Пальто женское модное с цельнокроеным рукавом из материала premium качества не мнется.
+Пальто весеннее для женщин больших размеров с  превосходным качеством швов дополняют английский воротник, удобные  карманы в шве, застежка на роговые пуговицы.
+Однобортное легкое осеннее пальто длинной 105 см хорошо сохраняет тепло, при этом на ощупь пальто довольно мягкое, материал износостойкий надолго сохраняет форму и безупречный вид. В зависимости от погодных условий, его можно использовать как зимнее.</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Состав:  шерсть сури альпака 75%; натуральная шерсть 25%
+Цвет:  светло-бежевый; молочный; ванильный; белый; бежевый
+Сезон:  демисезон
+Вид застежки:  пуговицы
+Рост модели на фото:  175 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  84-59-91
+Утеплитель:  без утеплителя
+Температурный режим:  от +10°С до -10°С
+Материал подкладки:  вискоза
+Покрой:  трапеция
+Тип карманов:  в шве
+Тип рукава:  длинные
+Опции капюшона:  без капюшона
+Опции опушки:  без опушки
+Декоративные элементы:  пуговицы
+Особенности модели:  двубортная
+Конструктивные элементы:  oversize
+Пол:  Женский
+Уход за вещами:  деликатная химическая чистка; допускается отпаривание
+Комплектация:  пальто женское
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>https://basket-14.wbbasket.ru/vol2049/part204971/204971561/images/big/1.webp, https://basket-14.wbbasket.ru/vol2049/part204971/204971561/images/big/2.webp, https://basket-14.wbbasket.ru/vol2049/part204971/204971561/images/big/3.webp, https://basket-14.wbbasket.ru/vol2049/part204971/204971561/images/big/4.webp, https://basket-14.wbbasket.ru/vol2049/part204971/204971561/images/big/5.webp, https://basket-14.wbbasket.ru/vol2049/part204971/204971561/images/big/6.webp, https://basket-14.wbbasket.ru/vol2049/part204971/204971561/images/big/7.webp, https://basket-14.wbbasket.ru/vol2049/part204971/204971561/images/big/8.webp, https://basket-14.wbbasket.ru/vol2049/part204971/204971561/images/big/9.webp, https://basket-14.wbbasket.ru/vol2049/part204971/204971561/images/big/10.webp, https://basket-14.wbbasket.ru/vol2049/part204971/204971561/images/big/11.webp, https://basket-14.wbbasket.ru/vol2049/part204971/204971561/images/big/12.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/263567540/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>263567540</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Пальто весна-осень длинное</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>6136</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>No name' just quality</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/4220656</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>S-M, L-XL</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>125</v>
+      </c>
+      <c r="J29" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Шерстяное пальто женское – стильная верхняя одежда для женщин.  
+Это демисезонное женское пальто из натуральной овечьей шерсти – идеальный выбор для осени и весны. Теплое, но при этом легкое, оно создаст красивый и модный образ в любую погоду.  
+Выполненное в классике или молодежном стиле, это длинное пальто с капюшоном, капором или эффектным воротником апаш станет универсальной вещью в гардеробе. Дизайнерская проработка деталей делает его необычным и стильным, подходящим как для офисной одежды, так и для повседневных луков.  
+Неважно, осеннее или весеннее настроение за окном – это пальто согреет в зиму и добавит элегантности в межсезонье. Верхняя одежда для женщин, которая сочетает комфорт и модную эстетику!</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>китай</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Состав:  шерсть; Овечья Шерсть
+Цвет:  белый; бежевый; молочный; ванильно-бежевый
+Сезон:  демисезон
+Вид застежки:  пояс; запах
+Утеплитель:  без утеплителя
+Температурный режим:  от -5 °C до +10 °C
+Материал подкладки:  без подкладки
+Покрой:  свободный
+Тип карманов:  в шве
+Тип рукава:  длинные
+Опции капюшона:  без капюшона
+Опции опушки:  без опушки
+Декоративные элементы:  пояс; воротник апаш
+Особенности модели:  с запахом; двубортная; ультралегкая
+Конструктивные элементы:  пояс
+Пол:  Женский
+Уход за вещами:  Сухая химическая чистка
+Комплектация:  пальто; вешалка; Кофр для одежды
+Страна производства:  Китай</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>https://basket-17.wbbasket.ru/vol2635/part263567/263567540/images/big/1.webp, https://basket-17.wbbasket.ru/vol2635/part263567/263567540/images/big/2.webp, https://basket-17.wbbasket.ru/vol2635/part263567/263567540/images/big/3.webp, https://basket-17.wbbasket.ru/vol2635/part263567/263567540/images/big/4.webp, https://basket-17.wbbasket.ru/vol2635/part263567/263567540/images/big/5.webp, https://basket-17.wbbasket.ru/vol2635/part263567/263567540/images/big/6.webp, https://basket-17.wbbasket.ru/vol2635/part263567/263567540/images/big/7.webp, https://basket-17.wbbasket.ru/vol2635/part263567/263567540/images/big/8.webp, https://basket-17.wbbasket.ru/vol2635/part263567/263567540/images/big/9.webp, https://basket-17.wbbasket.ru/vol2635/part263567/263567540/images/big/10.webp, https://basket-17.wbbasket.ru/vol2635/part263567/263567540/images/big/11.webp, https://basket-17.wbbasket.ru/vol2635/part263567/263567540/images/big/12.webp, https://basket-17.wbbasket.ru/vol2635/part263567/263567540/images/big/13.webp, https://basket-17.wbbasket.ru/vol2635/part263567/263567540/images/big/14.webp, https://basket-17.wbbasket.ru/vol2635/part263567/263567540/images/big/15.webp, https://basket-17.wbbasket.ru/vol2635/part263567/263567540/images/big/16.webp, https://basket-17.wbbasket.ru/vol2635/part263567/263567540/images/big/17.webp, https://basket-17.wbbasket.ru/vol2635/part263567/263567540/images/big/18.webp, https://basket-17.wbbasket.ru/vol2635/part263567/263567540/images/big/19.webp, https://basket-17.wbbasket.ru/vol2635/part263567/263567540/images/big/20.webp, https://basket-17.wbbasket.ru/vol2635/part263567/263567540/images/big/21.webp, https://basket-17.wbbasket.ru/vol2635/part263567/263567540/images/big/22.webp, https://basket-17.wbbasket.ru/vol2635/part263567/263567540/images/big/23.webp, https://basket-17.wbbasket.ru/vol2635/part263567/263567540/images/big/24.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/710115682/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>710115682</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Пальто шерстяное весна-осень</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>4365</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>YUNXIANG</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/250078284</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>M, S</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>8</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Женское пальто из шерсти — ваша идеальная пара на осень и зиму!
+Этот элегантный фасон выполнен из премиальной шерстяной ткани (69% шерсть). Натуральный состав не только обеспечивает исключительную теплоизоляцию и комфорт даже в холодную погоду, но и отличается долговечностью.
+Современный дизайн соответствует последним трендам и делает пальто универсальным предметом гардероба. Оно идеально подойдет для повседневной носки, прогулок и деловых встреч.
+Благодаря лаконичному стилю, пальто легко сочетается с любой обувью и аксессуарами, позволяя создавать безупречные образы для любого случая.
+Подарите себе уверенность в стиле и тепло!</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Состав:  69% шерсть
+Цвет:  розовый
+Сезон:  демисезон
+Рост модели на фото:  168 см
+Температурный режим:  от -5 °C до +10 °C
+Материал подкладки:  без подклада
+Покрой:  прямой
+Тип рукава:  длинные
+Опции капюшона:  несъемный капюшон
+Пол:  Женский</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>https://basket-34.wbbasket.ru/vol7101/part710115/710115682/images/big/1.webp, https://basket-34.wbbasket.ru/vol7101/part710115/710115682/images/big/2.webp, https://basket-34.wbbasket.ru/vol7101/part710115/710115682/images/big/3.webp, https://basket-34.wbbasket.ru/vol7101/part710115/710115682/images/big/4.webp, https://basket-34.wbbasket.ru/vol7101/part710115/710115682/images/big/5.webp, https://basket-34.wbbasket.ru/vol7101/part710115/710115682/images/big/6.webp, https://basket-34.wbbasket.ru/vol7101/part710115/710115682/images/big/7.webp, https://basket-34.wbbasket.ru/vol7101/part710115/710115682/images/big/8.webp, https://basket-34.wbbasket.ru/vol7101/part710115/710115682/images/big/9.webp, https://basket-34.wbbasket.ru/vol7101/part710115/710115682/images/big/10.webp, https://basket-34.wbbasket.ru/vol7101/part710115/710115682/images/big/11.webp, https://basket-34.wbbasket.ru/vol7101/part710115/710115682/images/big/12.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/26800674/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>26800674</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Пальто демисезонное большие размеры</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>9336</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Primadonna</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/47927</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>46, 48, 50, 52, 54, 56, 58, 60</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" t="n">
+        <v>7</v>
+      </c>
+      <c r="J31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Женское пальто бренда PDONNA выполнено из натуральной шерсти, полуприталенного силуэта. Пальто имеет застёжку - кнопки, воротник- отложной, карманы прорезные по линии шва. Эта модель подчеркнёт Вашу фигуру и создаст элегантный образ. Пальто прекрасно сочетается как с классическими брюками и юбкой, так и с повседневным стилем. При заказе обязательно сверьтесь с нашей таблицей размеров.</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Состав:  полиэстер; шерсть; текстиль
+Цвет:  шоколадный
+Сезон:  демисезон
+Вид застежки:  кнопки
+Утеплитель:  полиэстер
+Температурный режим:  +5 до +15
+Материал подкладки:  полиэстер
+Покрой:  приталенный
+Тип карманов:  прорезные
+Тип рукава:  длинные
+Опции капюшона:  без капюшона
+Опции опушки:  без опушки
+Декоративные элементы:  без элементов
+Особенности модели:  износостойкость
+Конструктивные элементы:  воротник
+Пол:  Женский
+Уход за вещами:  деликатная химическая чистка
+Комплектация:  пальто женское -1 шт
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>https://basket-02.wbbasket.ru/vol268/part26800/26800674/images/big/1.webp, https://basket-02.wbbasket.ru/vol268/part26800/26800674/images/big/2.webp, https://basket-02.wbbasket.ru/vol268/part26800/26800674/images/big/3.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/4896157/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>4896157</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Пальто мужское зимнее из премиальной шерсти</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>17380</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>BAZI FASHION GROUP</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/29914</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>54/182, 50-176, 48/182, 52/182, 56/182, 56-176, 48-176, 50/182, 52-176, 54/176, 46-176, 46/182, 58/176, 58/182, 60/176, 60/182</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>11</v>
+      </c>
+      <c r="J32" t="n">
+        <v>5</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Длинное мужское пальто Laconi – воплощение элегантности и комфорта для современного мужчины, ценящего безупречный стиль и высокое качество. Это изделие создано для тех, кто выбирает классику с изюминкой и стремится к длительному использованию вещей премиум-класса.
+Пальто выполнено из 100% шерсти – натурального материала, который обеспечивает идеальный баланс тепла и воздухопроницаемости. Благодаря этому материалу, изделие остается комфортным как в прохладные осенние дни, так и в холодные зимние месяцы. Элегантная шлица сзади добавляет свободы движений, делая пальто удобным для повседневной носки.
+Подкладка из чистой вискозы создает дополнительный комфорт, облегчая процесс надевания и снимания изделия. Утеплитель Termofinn Plus – инновационный гипоаллергенный материал, который эффективно сохраняет тепло, не утяжеляя силуэт. Однобортный крой подчеркивает строгий стиль, а наличие внешних карманов делает модель максимально практичной. Внутренний карман позволяет безопасно хранить документы или смартфон.
+Для любителей трендового oversize-силуэта рекомендуется выбирать размер на один больше стандартного. Прямой классический крой, разработанный по итальянским лекалам, гарантирует идеальную посадку и подчеркивает мужественные черты владельца. Широкая размерная сетка охватывает как стандартные, так и большие размеры, что делает пальто доступным для каждого.
+Laconi – бренд с более чем 10-летней историей, специализирующийся на производстве кашемировых пальто премиум-класса. Каждая деталь тщательно продумана: от выбора фурнитуры до создания уникальных тканей высочайшего качества. Такое пальто станет настоящей инвестицией в гардероб, прослужив долгие годы при правильном уходе.
+Это изделие идеально подходит как для ежедневной носки, так и для особых случаев. Оно станет отличным подарком на Новый год или 23 февраля, подчеркивая статус и хороший вкус своего обладателя. Пальто Laconi – это сочетание традиций и современных технологий, воплощенное в каждой детали.</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Состав:  шерсть; 100% шерсть от Lanficio De Ballis, Италия; обработка технология NANO TEC REVOLUTION
+Цвет:  темно-синий; темно-синий джинсовый
+Пол:  Мужской
+Сезон:  демисезон
+Вид застежки:  пуговицы
+Рост модели на фото:  189 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  102-88-99
+Размер на модели:  52
+Утеплитель:  термофин
+Плотность синтетического утеплителя:  160 г/кв.м
+Температурный режим:  от -5°C до +15°С
+Материал подкладки:  вискоза
+Покрой:  полуприлегающий
+Тип карманов:  с клапаном; прорезные
+Тип рукава:  длинные
+Опции капюшона:  без капюшона
+Опции опушки:  без опушки
+Декоративные элементы:  пуговицы; нашивки
+Особенности модели:  много карманов; со шлицей; отделочная строчка
+Уход за вещами:  деликатная химическая чистка
+Комплектация:  пальто; вешалка
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>https://basket-01.wbbasket.ru/vol48/part4896/4896157/images/big/1.webp, https://basket-01.wbbasket.ru/vol48/part4896/4896157/images/big/2.webp, https://basket-01.wbbasket.ru/vol48/part4896/4896157/images/big/3.webp, https://basket-01.wbbasket.ru/vol48/part4896/4896157/images/big/4.webp, https://basket-01.wbbasket.ru/vol48/part4896/4896157/images/big/5.webp, https://basket-01.wbbasket.ru/vol48/part4896/4896157/images/big/6.webp, https://basket-01.wbbasket.ru/vol48/part4896/4896157/images/big/7.webp, https://basket-01.wbbasket.ru/vol48/part4896/4896157/images/big/8.webp, https://basket-01.wbbasket.ru/vol48/part4896/4896157/images/big/9.webp, https://basket-01.wbbasket.ru/vol48/part4896/4896157/images/big/10.webp, https://basket-01.wbbasket.ru/vol48/part4896/4896157/images/big/11.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/15483592/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>15483592</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Пальто классическое из шерсти-кашемира премиум бренда</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>27444</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>BAZI FASHION GROUP</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/45521</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>48-176, 50-176, 52-176, 54-176, 56-176, 58-176, 60-176, 48-188, 54-170, 60-188</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>5</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Это очень универсальное неформальное пальто, которое прекрасно гармонирует с большинством джинсов, чиносов, свитеров и кардиганов. Изделие получилось очень легким и при этом теплым. Мастера марки BOLINI позаботились продумать мельчайшие детали начиная от пуговиц покрашенных под ткань, заканчивая подкладкой и других элементов. Все детали изделия, обработаны вручную по технологии, передаваемой из поколения в поколение. Это пальто из осенне-зимней коллекции одинаково хорошо рифмуется как с формальным костюмом, так и с вещами в стиле Smart Casual. Это пальто сделанное из шерсти исключительного качества, выделит Вас из толпы подчеркивая безупречный вкус. Пальто от BOLINI главный "Must Have" среди актуальных моделей верхней одежды. С приближением холодов рекомендуем присмотреть себе пальто классического кроя. Зимнее мужское пальто а так же наше удлинённое пальто от Bolini оптимальной длины ниже бедра - настоящий тренд сезона, выполненный из HI QALITY WOOL материала на основе натуральной шерсти. Благодаря премиальной итальянской шерсти от Lanificio De Fabio которая изготавливает в ручную 100% Премиальная шерсть покрашенная из натуральных природных красителей, ткань выглядит еще более красивой, не выцветет и не теряет форму, проста в уходе и почти не мнётся. В геноме бренда Bolini можно уловить отголоски любви к природе и натуральным материалам, из которых с заботой сделаны все изделия, так как именно натуральные материалы органично и бережно окутывают жизнь человека на протяжении веков.  Цветовая гамма построена на базовых оттенках черное мужское пальто, мужское длинное пальто на зиму что позволит войти в привычный гардероб делового мужчины. Компания Bolini является одним из лидеров в мужской модной одежде премиум сегменте, что подтверждает отзывы благодарных покупателей и почитателей марки. Компания рекомендует любителям посвободней брать на размер больше так как итальянские лекала подразумевают приталенность. Лучшее сочетание цены и качества на Валберес.</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Состав:  Кашемир; высокая крутка шерсти по технологииFabio-Wool tech; Премиальная шерсть с кашемиром от LANIFICIO de FABIO
+Цвет:  серый; серый гранит; серый металлик; серый мрамор; серый шелк
+Пол:  Мужской
+Сезон:  круглогодичный
+Вид застежки:  Пальто мужское классическое удлиненное на пуговицах молнии модное зимнее приталенное
+Рост модели на фото:  185 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  Классическое деловое пальто из шерсти стильное на выход полупальто тренч
+Размер на модели:  52
+Утеплитель:  термофин пальто мужское теплое зимнее бежевое черное синее модное пуховик осень
+Плотность синтетического утеплителя:  100 г/кв.м
+Температурный режим:  Пальто на осень зиму весну всесезонная демисезонная теплое зимнее утепленное
+Материал подкладки:  вискоза пальто мужское оверсайз пальто мужское длинное кашемир и шелк
+Покрой:  классическое мужское пальто зимнее осеннее стеганое полуприталенное синее черное италия
+Тип карманов:  молодежный трендовый повседневный теплый зимний осенний шерсть 100% темный
+Тип рукава:  пальто мужское оверсайз демисезонное
+Опции капюшона:  Пальто мужское демисезонное с капюшоном и без длинное casual на зиму теплое
+Опции опушки:  отстегивается классическое пальто с мехом на зиму весну осень черное bolini bazioni
+Декоративные элементы:  пальто мужское классическое шерстяное теплое на зиму демисезонное с капюшоном
+Особенности модели:  пальто зимнее мужское приталенное свободное черное серое bolini базиони кэжуал
+Уход за вещами:  деликатная химическая чистка пальто мужское классическое длинное пальто зима весна осень
+Комплектация:  пальто; вешалка; пакет; чехол
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>https://basket-02.wbbasket.ru/vol154/part15483/15483592/images/big/1.webp, https://basket-02.wbbasket.ru/vol154/part15483/15483592/images/big/2.webp, https://basket-02.wbbasket.ru/vol154/part15483/15483592/images/big/3.webp, https://basket-02.wbbasket.ru/vol154/part15483/15483592/images/big/4.webp, https://basket-02.wbbasket.ru/vol154/part15483/15483592/images/big/5.webp, https://basket-02.wbbasket.ru/vol154/part15483/15483592/images/big/6.webp, https://basket-02.wbbasket.ru/vol154/part15483/15483592/images/big/7.webp, https://basket-02.wbbasket.ru/vol154/part15483/15483592/images/big/8.webp, https://basket-02.wbbasket.ru/vol154/part15483/15483592/images/big/9.webp, https://basket-02.wbbasket.ru/vol154/part15483/15483592/images/big/10.webp, https://basket-02.wbbasket.ru/vol154/part15483/15483592/images/big/11.webp, https://basket-02.wbbasket.ru/vol154/part15483/15483592/images/big/12.webp, https://basket-02.wbbasket.ru/vol154/part15483/15483592/images/big/13.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/4932670/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>4932670</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Пальто классическое зимнее из премиальной 100% шерсти твид</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11312</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>BAZI FASHION GROUP</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/29914</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>50-176, 56-176, 48-176, 52-176, 54-176, 48-182, 52-182, 54-182, 50-182, 58-176, 58-182, 56-182, 60-176, 62-176</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>15</v>
+      </c>
+      <c r="J34" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>ДЛЯ ТЕХ, КТО ЦЕНИТ И ПОНИМАЕТ УНИКАЛЬНОЕ КАЧЕСТВО И МАСТЕРСТВО ТЕХНОЛОГОВ И ДИЗАЙНЕРОВ МАРКИ ABSOLUTEX. Это очень универсальное неформальное пальто, которое прекрасно гармонирует с большинством джинсов, чиносов, свитеров и кардиганов. Изделие получилось очень легким и при этом теплым. Мастера марки ABSOLUTEX позаботились продумать мельчайшие детали начиная от пуговиц, покрашенных под ткань, заканчивая подкладкой и других элементов. Все детали изделия, обработаны вручную по технологии, передаваемой из поколения в поколение. Это пальто из осенне-зимней коллекции одинаково хорошо рифмуется как с формальным костюмом, так и с вещами в стиле SMART CASUAL. Это пальто, сделанное из шерсти исключительного качества, выделит Вас из толпы подчеркивая безупречный вкус. Пальто - главный "Must Have" среди актуальных моделей верхней одежды. С приближением холодов рекомендуем присмотреть себе пальто классического кроя. Зимнее мужское пальто, а также наше удлинённое пальто от ABSOLUTEX оптимальной длины- настоящий тренд сезона, выполненный из HI QALITY WOOL материала на основе натуральной шерсти. Благодаря премиальной итальянской шерсти от Lora de Castello, ткань выглядит еще более красивой, не выцветет и не теряет форму, проста в уходе и почти не мнётся. Цветовая гамма построена на базовых оттенках, сером и коричневом, черное мужское пальто, мужское длинное пальто на зиму, что позволит этому пальто легко войти в привычный гардероб делового мужчины. Компания является одним из лидеров в модной одежде. Пальто, отличается не только свободным кроем, но и лучшим качеством, ведь в нем вы будете ощущать себя комфортно, в холодную, так и в теплую погоду, на природе, в путешествии, на прогулке с друзьями. В зависимости от фасона, ткани и цвета, вы можете создать множество луков, которые будут очень разнообразны и интересны. Лучшее сочетание цены и качества проверенное годами.</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Состав:  100% шерсть от Lora De Castello, Италия; шерсть; обработка технология NANO TEC REVOLUTION; Кашемир
+Цвет:  серый; темно-серый; серый гранит
+Сезон:  демисезон
+Вид застежки:  пуговицы
+Рост модели на фото:  185 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  102-88-99
+Размер на модели:  52
+Утеплитель:  термоплюс
+Плотность синтетического утеплителя:  100 г/кв.м
+Температурный режим:  от -5°C до +15°С
+Материал подкладки:  полиэстер
+Покрой:  полуприлегающий
+Тип карманов:  прорезные
+Тип рукава:  длинные
+Опции капюшона:  без капюшона
+Опции опушки:  без опушки
+Декоративные элементы:  нашивки; пуговицы; пальто мужское на зиму теплое
+Особенности модели:  отделочная строчка; много карманов; со шлицей
+Конструктивные элементы:  классическая модель
+Пол:  Мужской
+Уход за вещами:  химическая чистка
+Комплектация:  пальто
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>https://basket-01.wbbasket.ru/vol49/part4932/4932670/images/big/1.webp, https://basket-01.wbbasket.ru/vol49/part4932/4932670/images/big/2.webp, https://basket-01.wbbasket.ru/vol49/part4932/4932670/images/big/3.webp, https://basket-01.wbbasket.ru/vol49/part4932/4932670/images/big/4.webp, https://basket-01.wbbasket.ru/vol49/part4932/4932670/images/big/5.webp, https://basket-01.wbbasket.ru/vol49/part4932/4932670/images/big/6.webp, https://basket-01.wbbasket.ru/vol49/part4932/4932670/images/big/7.webp, https://basket-01.wbbasket.ru/vol49/part4932/4932670/images/big/8.webp, https://basket-01.wbbasket.ru/vol49/part4932/4932670/images/big/9.webp, https://basket-01.wbbasket.ru/vol49/part4932/4932670/images/big/10.webp, https://basket-01.wbbasket.ru/vol49/part4932/4932670/images/big/11.webp, https://basket-01.wbbasket.ru/vol49/part4932/4932670/images/big/12.webp, https://basket-01.wbbasket.ru/vol49/part4932/4932670/images/big/13.webp, https://basket-01.wbbasket.ru/vol49/part4932/4932670/images/big/14.webp, https://basket-01.wbbasket.ru/vol49/part4932/4932670/images/big/15.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/681762108/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>681762108</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Короткое пальто шерстяное весна-осень</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>4152</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>YUNXIANG</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/250078284</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>M, S</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>8</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Женское пальто из шерсти — ваша идеальная пара на осень и зиму!
+Этот элегантный фасон выполнен из премиальной шерстяной ткани (70% шерсть). Натуральный состав не только обеспечивает исключительную теплоизоляцию и комфорт даже в холодную погоду, но и отличается долговечностью.
+Современный дизайн соответствует последним трендам и делает пальто универсальным предметом гардероба. Оно идеально подойдет для повседневной носки, прогулок и деловых встреч.
+Благодаря лаконичному стилю, пальто легко сочетается с любой обувью и аксессуарами, позволяя создавать безупречные образы для любого случая.
+Подарите себе уверенность в стиле и тепло!</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Состав:  шерсть 70%
+Цвет:  черный
+Сезон:  демисезон
+Вид застежки:  без застежки
+Рост модели на фото:  168 см
+Размер на модели:  S
+Температурный режим:  от -5 °C до +10 °C
+Материал подкладки:  без подклада
+Покрой:  оверсайз
+Тип карманов:  прорезные
+Тип рукава:  короткие
+Опции капюшона:  без капюшона
+Опции опушки:  без опушки
+Декоративные элементы:  без элементов
+Особенности модели:  унисекс
+Пол:  Женский</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>https://basket-33.wbbasket.ru/vol6817/part681762/681762108/images/big/1.webp, https://basket-33.wbbasket.ru/vol6817/part681762/681762108/images/big/2.webp, https://basket-33.wbbasket.ru/vol6817/part681762/681762108/images/big/3.webp, https://basket-33.wbbasket.ru/vol6817/part681762/681762108/images/big/4.webp, https://basket-33.wbbasket.ru/vol6817/part681762/681762108/images/big/5.webp, https://basket-33.wbbasket.ru/vol6817/part681762/681762108/images/big/6.webp, https://basket-33.wbbasket.ru/vol6817/part681762/681762108/images/big/7.webp, https://basket-33.wbbasket.ru/vol6817/part681762/681762108/images/big/8.webp, https://basket-33.wbbasket.ru/vol6817/part681762/681762108/images/big/9.webp, https://basket-33.wbbasket.ru/vol6817/part681762/681762108/images/big/10.webp, https://basket-33.wbbasket.ru/vol6817/part681762/681762108/images/big/11.webp, https://basket-33.wbbasket.ru/vol6817/part681762/681762108/images/big/12.webp, https://basket-33.wbbasket.ru/vol6817/part681762/681762108/images/big/13.webp, https://basket-33.wbbasket.ru/vol6817/part681762/681762108/images/big/14.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/257941083/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>257941083</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Пальто укороченное демисезоннее</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>18009</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Mabag eco</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/1010120</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>ONE SIZE</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>3</v>
+      </c>
+      <c r="I36" t="n">
+        <v>39</v>
+      </c>
+      <c r="J36" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Полупальто женское оверсайз от бренда MABAG ECO – это то самое трендовой пальто этой осени!
+Mabag Eco - бренд, который основывается на производстве экологичных и натуральных элементов гардероба. Mabag eco оставляет сладкое послевкусием и навсегда остаётся в сердце.
+Полупальто из шерсти в стиле оверсайз сделает ваш образ стильным и эффектным. 
+Классический стиль давно вернул в моду простой свободный крой, что сделало пальто короткое ещё более безупречным. Полупальто из шерсти будет не только греть вас на осенних прогулках, но и подчеркнёт стиль. Стилизуйте пальто тёплое с любыми элементами одежды, оно обязательно займёт место в вашем сердечке надолго! 
+Размер полупальто one size, параметры обхват груди 136 см, длина по спинке 62 см, длина рукавов от линии горловины 78 см. 
+С любовью, Mabag eco!</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Состав:  Подкл: 100% вискоза; шерсть 50%; полиэстер 30%; акрил 20%
+Цвет:  черный
+Сезон:  демисезон
+Вид застежки:  пуговицы
+Рост модели на фото:  171 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  84-64-90
+Размер на модели:  one size 42-46
+Утеплитель:  без утеплителя
+Температурный режим:  от +10 °C до -5 °C
+Материал подкладки:  вискоза 100%
+Тип карманов:  втачные
+Опции капюшона:  без капюшона
+Опции опушки:  без опушки
+Особенности модели:  свободный крой
+Пол:  Женский
+Уход за вещами:  химическая чистка
+Комплектация:  пальто укороченное женское
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>https://basket-16.wbbasket.ru/vol2579/part257941/257941083/images/big/1.webp, https://basket-16.wbbasket.ru/vol2579/part257941/257941083/images/big/2.webp, https://basket-16.wbbasket.ru/vol2579/part257941/257941083/images/big/3.webp, https://basket-16.wbbasket.ru/vol2579/part257941/257941083/images/big/4.webp, https://basket-16.wbbasket.ru/vol2579/part257941/257941083/images/big/5.webp, https://basket-16.wbbasket.ru/vol2579/part257941/257941083/images/big/6.webp, https://basket-16.wbbasket.ru/vol2579/part257941/257941083/images/big/7.webp, https://basket-16.wbbasket.ru/vol2579/part257941/257941083/images/big/8.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/26800613/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>26800613</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Пальто демисезонное большие размеры</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>8336</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Primadonna</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/47927</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>46, 48, 50, 52, 56, 60</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>2</v>
+      </c>
+      <c r="I37" t="n">
+        <v>4</v>
+      </c>
+      <c r="J37" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Женское пальто бренда PDONNA выполнено из натуральной шерсти, полуприталенного силуэта. Модель имеет застёжку -пуговицы, воротник- английский, карманы прорезные с листочкой. Пальто прекрасно сочетается как с классическими брюками и юбкой, так и с вечерним платьем . При заказе обязательно сверьтесь с нашей таблицей размеров.</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Состав:  полиэстер; шерсть; текстиль
+Цвет:  черный
+Сезон:  демисезон
+Вид застежки:  пуговицы
+Утеплитель:  полиэстер
+Температурный режим:  +5 до +15
+Материал подкладки:  полиэстер
+Покрой:  приталенный
+Тип карманов:  прорезные
+Тип рукава:  длинные
+Опции капюшона:  без капюшона
+Опции опушки:  без опушки
+Декоративные элементы:  пояс
+Особенности модели:  износостойкость
+Конструктивные элементы:  воротник
+Пол:  Женский
+Уход за вещами:  деликатная химическая чистка
+Комплектация:  Пальто женское демисезонное -1шт
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>https://basket-02.wbbasket.ru/vol268/part26800/26800613/images/big/1.webp, https://basket-02.wbbasket.ru/vol268/part26800/26800613/images/big/2.webp, https://basket-02.wbbasket.ru/vol268/part26800/26800613/images/big/3.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/544186689/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>544186689</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Пальто женское весна-осень демисезонное длинное</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>20007</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Острая Роза</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/48819</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>42, 44, 46, 48, 50, 52, 54</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Шерсть 70%. Мы шьем пальто более 25 лет в России и гарантируем качество. Пальто от OSTRAYA ROZA станет стильным и практичным дополнением вашего гардероба. Изготовленное из натуральной шерсти и вискозы, оно подарит вам тепло и комфорт в прохладную погоду. Классический  цвет легко впишется в любой образ, а лаконичный крой подчеркнет вашу элегантность. Это длинное пальто станет идеальным выбором для прогулок по городу, встреч с друзьями или деловых переговоров.
+Элегантное пальто из премиальной шерсти — ваш must-have для безупречного гардероба!
+Почему это двубортное  пальто станет вашей любимой вещью:
+• Универсальный цвет подходит к любому образу
+• Длина  создает изысканный силуэт
+• Натуральная шерсть согреет даже в сильные морозы
+• Классический крой подчеркнет вашу женственность
+Особенности, которые вы оцените:
+• Мягкая, приятная к телу шерсть высшего качества
+• Идеальная посадка по фигуре
+• Практичная длина, скрывающая все несовершенства
+• Универсальный фасон, актуальный в любом сезоне
+Для кого создано это пальто:
+• Деловых женщин, ценящих элегантность
+• Модниц, следящих за трендами
+• Тех, кто выбирает комфорт и стиль</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Состав:  шерсть; вискоза
+Цвет:  серый
+Сезон:  демисезон
+Вид застежки:  пуговицы
+Рост модели на фото:  172
+Размер на модели:  42
+Температурный режим:  от +5 °C до +15 °C
+Материал подкладки:  вискоза
+Покрой:  прямой
+Пол:  Женский
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>https://basket-28.wbbasket.ru/vol5441/part544186/544186689/images/big/1.webp, https://basket-28.wbbasket.ru/vol5441/part544186/544186689/images/big/2.webp, https://basket-28.wbbasket.ru/vol5441/part544186/544186689/images/big/3.webp, https://basket-28.wbbasket.ru/vol5441/part544186/544186689/images/big/4.webp, https://basket-28.wbbasket.ru/vol5441/part544186/544186689/images/big/5.webp, https://basket-28.wbbasket.ru/vol5441/part544186/544186689/images/big/6.webp, https://basket-28.wbbasket.ru/vol5441/part544186/544186689/images/big/7.webp, https://basket-28.wbbasket.ru/vol5441/part544186/544186689/images/big/8.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/198381803/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>198381803</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Пальто короткое</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>9229</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Filigreen</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/1418640</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>M-L, S-M</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" t="n">
+        <v>5</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Пальто женское демисезонное укороченное. Подойдет: в офис, в школу, на работу или на прогулку с друзьями. Свободный фасон и продуманный крой делают модель очень комфортной в носке. Придаст элегантности любому образу, а короткая длина подчеркнет ноги и добавить образу легкости. Оно выполнено из высококачественной шерсти с добавлением вискозы, что обеспечивает натуральную теплоизоляцию. Наше пальто - это настоящий стильный и модный предмет гардероба, который подчеркнет вашу индивидуальность. Уникальный разработанный нами дизайн - придаст неповторимость вашему образу. Уникальный крой на спине, эксклюзивная итальянская фурнитура. Мягкий материал, не деформируется при стирке. Подкладка выполнена из полиэстера. Драповая фактура материала смотрится стильно и дорого. Удобные карманы, с кожаными ставками придают образу женственности. Закажите люксовое, короткое пальто прямо сейчас и почувствуйте себя настоящей королевой. Filigreen - это профессиональный пошив и высокое качество.</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Состав:  полиэстер 90%, шерсть 10%
+Цвет:  зеленый; изумрудно-зеленый; изумрудный
+Сезон:  демисезон
+Вид застежки:  пуговицы
+Рост модели на фото:  164 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  84-60-90
+Размер на модели:  42-44
+Плотность синтетического утеплителя:  100 г/кв.м
+Температурный режим:  от +10 °C до -5 °C
+Покрой:  оверсайз
+Тип карманов:  прорезные
+Тип рукава:  длинные
+Опции капюшона:  без капюшона
+Опции опушки:  без опушки
+Декоративные элементы:  кожаные вставки
+Особенности модели:  дышащий материал
+Конструктивные элементы:  вставки
+Пол:  Женский
+Уход за вещами:  химическая чистка
+Комплектация:  Пальто - 1 шт.
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>https://basket-13.wbbasket.ru/vol1983/part198381/198381803/images/big/1.webp, https://basket-13.wbbasket.ru/vol1983/part198381/198381803/images/big/2.webp, https://basket-13.wbbasket.ru/vol1983/part198381/198381803/images/big/3.webp, https://basket-13.wbbasket.ru/vol1983/part198381/198381803/images/big/4.webp, https://basket-13.wbbasket.ru/vol1983/part198381/198381803/images/big/5.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/317871295/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>317871295</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Пальто весеннее длинное</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>6303</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>ETIKA</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/468951</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>42, 44, 46, 48, 50</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>9</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" t="n">
+        <v>5</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Стильное женское драповое пальто, которое станет настоящим хитом сезона весна-осень 2026! Это удлиненное пальто оверсайз тренд 2026 для девушек идеально подойдет для прохладных дней, обеспечивая отличный комфорт и тепло благодаря высококачественным материалам, таким как натуральная шерсть.
+Данное молодежное женское весенне-осеннее пальто станет вашим верным спутником в повседневной жизни и на особых событиях. Его универсальный дизайн позволяет комбинировать его с различными нарядами, а пояс, который позволяет подчеркнуть талию, добавляет элегантности в образ. Английский воротник придаст вашему стилю изысканность и утонченный вкус.
+Весеннее пальто на запах  для женщин до колен, что подчеркивает гармоничное сочетание стиля и практичности. Благодаря шлевкам для пояса, голубое пальто женское весна-осень длинное классика всегда будет выглядеть безупречно, а теплота шерсти защитит вас от холодной осени и прохладной весны.
+Мы предлагаем женскую одежду с большим выбором размеров, включая большие размеры, что делает эту стильную вещь доступной для всех модниц, в том числе и вещью для беременных. Эта элегантное кашемировое женское пальто прекрасно подходит для демисезонного периода, а материалы премиального качества обеспечивают устойчивость к износу.
+Станьте обладательницей женственной одежды-актуального демисезонного пальто кашемир, которое сочетает в себе тепло, уют и неповторимый шарм. Не упустите возможность обновить свой гардероб с помощью пальто весеннего классического.</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Состав:  шерсть; вискоза; полиэстер
+Цвет:  кофейный; коричневый меланж; бледно-коричневый
+Пол:  Женский
+Сезон:  Демисезон
+Вид застежки:  пояс; кнопки
+Рост модели на фото:  175 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  82-63-91
+Размер на модели:  42
+Температурный режим:  от 0 °C до +15 °C
+Материал подкладки:  поливискоза
+Покрой:  полуприлегающий
+Тип карманов:  прорезные
+Особенности модели:  со шлицей; однобортная
+Уход за вещами:  химическая чистка
+Комплектация:  плечики; пояс; пальто
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>https://basket-19.wbbasket.ru/vol3178/part317871/317871295/images/big/1.webp, https://basket-19.wbbasket.ru/vol3178/part317871/317871295/images/big/2.webp, https://basket-19.wbbasket.ru/vol3178/part317871/317871295/images/big/3.webp, https://basket-19.wbbasket.ru/vol3178/part317871/317871295/images/big/4.webp, https://basket-19.wbbasket.ru/vol3178/part317871/317871295/images/big/5.webp, https://basket-19.wbbasket.ru/vol3178/part317871/317871295/images/big/6.webp, https://basket-19.wbbasket.ru/vol3178/part317871/317871295/images/big/7.webp, https://basket-19.wbbasket.ru/vol3178/part317871/317871295/images/big/8.webp, https://basket-19.wbbasket.ru/vol3178/part317871/317871295/images/big/9.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/822687844/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>822687844</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Пальто</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>4800</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Мария</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/350185895</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" t="n">
+        <v>5</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Прекрасное зимнее пальто под любой образ и стиль. Состояние отличное, носила редко, хранится в чехле в шкафу.  Маркировка 44, но идёт на 42.  Мех натуральный, не лезет, пышный.</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Состав:  Эластан 5%; вискоза 15%; шерсть 80%
+Цвет:  синий
+Сезон:  зима
+Вид застежки:  пуговицы
+Утеплитель:  ватин
+Материал подкладки:  полиэстер
+Покрой:  прямой
+Тип карманов:  прорезные
+Тип рукава:  длинные
+Опции капюшона:  без капюшона
+Опции опушки:  съемная опушка
+Конструктивные элементы:  нет
+Пол:  Женский
+Уход за вещами:  бережная стирка при 30 градусах
+Комплектация:  пальто; пояс
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>https://basket-37.wbbasket.ru/vol8226/part822687/822687844/images/big/1.webp, https://basket-37.wbbasket.ru/vol8226/part822687/822687844/images/big/2.webp, https://basket-37.wbbasket.ru/vol8226/part822687/822687844/images/big/3.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/11626284/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>11626284</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Пальто утепленное из 100% премиальной шерсти</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>22105</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>BAZI FASHION GROUP</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/45521</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>48-176, 48-182, 50-176, 50-182, 52-176, 52-182, 54-176, 54-182, 56-176, 56-182, 58-176, 58-182, 50-188, 54-170, 58-188</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>2</v>
+      </c>
+      <c r="I42" t="n">
+        <v>5</v>
+      </c>
+      <c r="J42" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Это очень универсальное неформальное пальто, которое прекрасно гармонирует с большинством
+джинсов, чиносов, свитеров и кардиганов. Изделие получилось очень легким и при этом теплым.
+Мастера марки BAZIONI позаботились продумать мельчайшие детали начиная от пуговиц
+покрашенных под ткань, заканчивая подкладкой и других элементов. Все детали изделия,
+обработаны вручную по технологии, передаваемой из поколения в поколение. Это пальто из
+осенне-зимней коллекции одинаково хорошо рифмуется как с формальным костюмом, так и с
+вещами в стиле Smart Casual. Это пальто сделанное из шерсти исключительного качества, выделит
+Вас из толпы подчеркивая безупречный вкус. Пальто от Bazioni главный "Must Have" среди
+актуальных моделей верхней одежды. С приближением холодов рекомендуем присмотреть себе
+пальто классического кроя. Зимнее мужское пальто а так же наше удлинённое пальто от BAZIONI
+оптимальной длины ниже бедра - настоящий тренд сезона, выполненный из HI QALITY WOOL
+материала на основе натуральной шерсти. Благодаря премиальной итальянской шерсти от
+Lanificio De Ballis которая изготавливает в ручную 100% Премиальная шерсть покрашенная из
+натуральных природных красителей, ткань выглядит еще более красивой, не выцветет и не теряет
+форму, проста в уходе и почти не мнётся. В геноме бренда Bazioni можно уловить отголоски любви
+к природе и натуральным материалам, из которых с заботой сделаны все изделия, так как именно
+натуральные материалы органично и бережно окутывают жизнь человека на протяжении веков.
+Цветовая гамма построена на базовых оттенках черное мужское пальто, мужское длинное пальто
+на зиму что позволит войти в привычный гардероб делового мужчины. Компания BAZIONI является
+одним из лидеров в мужской модной одежде премиум сегменте, что подтверждает отзывы
+благодарных покупателей и почитателей марки. Компания рекомендует любителям посвободней
+брать на размер больше так как итальянские лекала подразумевают приталенность. Лучшее
+сочетание цены и качества на Валберес.</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Состав:  ПРЕМИАЛЬНАЯ ШЕРСТЬ 100% от Lanificio De Ballis; дополнительную обработка NANO tec revolution
+Цвет:  синий; темно-синий джинсовый; темно-синий
+Сезон:  зима
+Вид застежки:  Пальто мужское классическое удлиненное на пуговицах молнии модное зимнее приталенное
+Рост модели на фото:  185 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  Классическое деловое пальто из шерсти стильное на выход полупальто тренч
+Размер на модели:  50 52-54 54-56 58 пальто мужское длинное классическое большой размер Тренч кардиган
+Утеплитель:  термофин пальто мужское теплое зимнее бежевое черное синее модное пуховик осень
+Плотность синтетического утеплителя:  60 г/кв.м
+Температурный режим:  Пальто на осень зиму весну всесезонная демисезонная теплое зимнее утепленное
+Материал подкладки:  вискоза пальто мужское оверсайз пальто мужское длинное кашемир и шелк
+Покрой:  классическое мужское пальто зимнее осеннее стеганое полуприталенное синее черное италия
+Тип карманов:  молодежный трендовый повседневный теплый зимний осенний шерсть 100% темный
+Тип рукава:  длинные
+Опции капюшона:  Пальто мужское демисезонное с капюшоном и без длинное casual на зиму теплое
+Опции опушки:  отстегивается классическое пальто с мехом на зиму весну осень черное bazioni
+Декоративные элементы:  пальто мужское классическое шерстяное теплое на зиму демисезонное с капюшоном
+Особенности модели:  пальто зимнее мужское приталенное свободное черное серое базиони кэжуал
+Конструктивные элементы:  Пальто мужское утепленное с английским воротником из шерсти стильное
+Пол:  Мужской
+Уход за вещами:  деликатная химическая чистка пальто мужское классическое длинное пальто весна
+Комплектация:  пакет; вешалка; пальто
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>https://basket-01.wbbasket.ru/vol116/part11626/11626284/images/big/1.webp, https://basket-01.wbbasket.ru/vol116/part11626/11626284/images/big/2.webp, https://basket-01.wbbasket.ru/vol116/part11626/11626284/images/big/3.webp, https://basket-01.wbbasket.ru/vol116/part11626/11626284/images/big/4.webp, https://basket-01.wbbasket.ru/vol116/part11626/11626284/images/big/5.webp, https://basket-01.wbbasket.ru/vol116/part11626/11626284/images/big/6.webp, https://basket-01.wbbasket.ru/vol116/part11626/11626284/images/big/7.webp, https://basket-01.wbbasket.ru/vol116/part11626/11626284/images/big/8.webp, https://basket-01.wbbasket.ru/vol116/part11626/11626284/images/big/9.webp, https://basket-01.wbbasket.ru/vol116/part11626/11626284/images/big/10.webp, https://basket-01.wbbasket.ru/vol116/part11626/11626284/images/big/11.webp, https://basket-01.wbbasket.ru/vol116/part11626/11626284/images/big/12.webp, https://basket-01.wbbasket.ru/vol116/part11626/11626284/images/big/13.webp, https://basket-01.wbbasket.ru/vol116/part11626/11626284/images/big/14.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/620126183/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>620126183</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Полупальто Brixton Антрацит</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>55978</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Виноградова-Рагинская Анна Михайловна ИП</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/49024</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>44, 46, 48</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Зимнее полупальто из 100% объемной шерсти, Австралийского мериноса, защищает от зимних морозов, как натуральная дубленка или натуральная шуба, теплее и комфортнее эффектнее, чем пуховик самого высокого качества. То, как драпируется материал на складках - мягко и крупно, говорит о толщине и теплозащите. Чистошерстяное полупальто в такой плотности годами не теряет свой вид, не боится дождя, ветра и снега. Поверхность материала легко чистится жесткой одежной щеткой и многие сезоны сохряняет вид. Теплота RichWool сопоставима с меховым изделием, однако носить это классическое пальто уместно с начала осени и до конца весны. Вам будет комфортно и при сухом морозе, и в промозглую сырую погоду. Все модели RichWool из шерсти изготовлены в ограниченном количестве в России по авторской технологии. Подкладка эффектного дизайна из шёлка и вискозы. Боковые карманы на тёплой шерстяной подкладке. Есть внутренние карманы.
+ RichWool - уникальный российский бренд шерстяной одежды полного цикла: от изготовления полотен особой толщины, структуры и плотности из шерстяного волокна до финальной отделки готового пальто с высокой долей ручной работы.
+Изделие поставляется в фирменном чехле на фирменной вешалке. Одевайтесь теплее, берегите себя!
+полупальто женское зимнее
+пальто женское зимнее шерстяное
+пальто зимнее женское</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Состав:  шерсть
+Цвет:  темно-серый; серый; серый меланж; антрацитовый
+Сезон:  зима
+Материал подкладки:  шелк
+Вид застежки:  пуговицы
+Воротник:  классический
+Опции капюшона:  без капюшона
+Тип карманов:  потайные
+Пол:  Женский
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>https://basket-31.wbbasket.ru/vol6201/part620126/620126183/images/big/1.webp, https://basket-31.wbbasket.ru/vol6201/part620126/620126183/images/big/2.webp, https://basket-31.wbbasket.ru/vol6201/part620126/620126183/images/big/3.webp, https://basket-31.wbbasket.ru/vol6201/part620126/620126183/images/big/4.webp, https://basket-31.wbbasket.ru/vol6201/part620126/620126183/images/big/5.webp, https://basket-31.wbbasket.ru/vol6201/part620126/620126183/images/big/6.webp, https://basket-31.wbbasket.ru/vol6201/part620126/620126183/images/big/7.webp, https://basket-31.wbbasket.ru/vol6201/part620126/620126183/images/big/8.webp, https://basket-31.wbbasket.ru/vol6201/part620126/620126183/images/big/9.webp, https://basket-31.wbbasket.ru/vol6201/part620126/620126183/images/big/10.webp, https://basket-31.wbbasket.ru/vol6201/part620126/620126183/images/big/11.webp, https://basket-31.wbbasket.ru/vol6201/part620126/620126183/images/big/12.webp, https://basket-31.wbbasket.ru/vol6201/part620126/620126183/images/big/13.webp, https://basket-31.wbbasket.ru/vol6201/part620126/620126183/images/big/14.webp, https://basket-31.wbbasket.ru/vol6201/part620126/620126183/images/big/15.webp, https://basket-31.wbbasket.ru/vol6201/part620126/620126183/images/big/16.webp, https://basket-31.wbbasket.ru/vol6201/part620126/620126183/images/big/17.webp, https://basket-31.wbbasket.ru/vol6201/part620126/620126183/images/big/18.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/187010840/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>187010840</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Пальто двубортное из премиальной шерсти Limited Edition</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>30144</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>BAZI FASHION GROUP</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/45521</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>52-176, 58-176, 50-176, 56-176, 54-176</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Это очень универсальное неформальное пальто, которое прекрасно гармонирует с большинством джинсов, чиносов, свитеров и кардиганов. Изделие получилось очень легким и при этом теплым. Мастера марки BOLINI позаботились продумать мельчайшие детали начиная от пуговиц покрашенных под ткань, заканчивая подкладкой и других элементов. Все детали изделия, обработаны вручную по технологии, передаваемой из поколения в поколение. Это пальто из осенне-зимней коллекции одинаково хорошо рифмуется как с формальным костюмом, так и с вещами в стиле Smart Casual. Это пальто сделанное из шерсти исключительного качества, выделит Вас из толпы подчеркивая безупречный вкус. Пальто от BOLINI главный "Must Have" среди актуальных моделей верхней одежды. С приближением холодов рекомендуем присмотреть себе пальто классического кроя. Зимнее мужское пальто а так же наше удлинённое пальто от Bolini оптимальной длины ниже бедра - настоящий тренд сезона, выполненный из HI QALITY WOOL материала на основе натуральной шерсти. Благодаря премиальной итальянской шерсти от Lanificio De Fabio которая изготавливает в ручную 100% Премиальная шерсть покрашенная из натуральных природных красителей, ткань выглядит еще более красивой, не выцветет и не теряет форму, проста в уходе и почти не мнётся. В геноме бренда Bolini можно уловить отголоски любви к природе и натуральным материалам, из которых с заботой сделаны все изделия, так как именно натуральные материалы органично и бережно окутывают жизнь человека на протяжении веков.  Цветовая гамма построена на базовых оттенках черное мужское пальто, мужское длинное пальто на зиму что позволит войти в привычный гардероб делового мужчины. Компания Bolini является одним из лидеров в мужской модной одежде премиум сегменте, что подтверждает отзывы благодарных покупателей и почитателей марки. Компания рекомендует любителям посвободней брать на размер больше так как итальянские лекала подразумевают приталенность. Лучшее сочетание цены и качества на Валберес.</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Состав:  ПРЕМИАЛЬНАЯ ШЕРСТЬ 100% от Lanificio De Ballis
+Цвет:  синий; темно-синий джинсовый; деним; темно-синий; синий космос
+Пол:  Мужской
+Сезон:  демисезон
+Вид застежки:  Пальто мужское классическое удлиненное на пуговицах молнии модное зимнее приталенное
+Рост модели на фото:  185 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  Классическое деловое пальто из шерсти стильное на выход полупальто тренч
+Размер на модели:  50 52-54 54-56 58 пальто мужское длинное классическое большой размер Тренч кардиган
+Утеплитель:  термофин пальто мужское теплое зимнее бежевое черное синее модное пуховик осень
+Плотность синтетического утеплителя:  100 г/кв.м
+Температурный режим:  Пальто на осень зиму весну всесезонная демисезонная теплое зимнее утепленное
+Материал подкладки:  вискоза пальто мужское оверсайз пальто мужское длинное кашемир и шелк
+Покрой:  классическое мужское пальто зимнее осеннее стеганое полуприталенное синее черное италия
+Тип карманов:  молодежный трендовый повседневный теплый зимний осенний шерсть 100% темный
+Тип рукава:  пальто мужское оверсайз демисезонное
+Опции капюшона:  Пальто мужское демисезонное с капюшоном и без длинное casual на зиму теплое
+Опции опушки:  отстегивается классическое пальто с мехом на зиму весну осень черное bolini bazioni
+Декоративные элементы:  пальто мужское классическое шерстяное теплое на зиму демисезонное с капюшоном
+Особенности модели:  пальто зимнее мужское приталенное свободное черное серое bolini базиони кэжуал
+Уход за вещами:  деликатная химическая чистка пальто мужское классическое длинное пальто зима весна осень
+Комплектация:  пальто; вешалка; пакет; чехол
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>https://basket-12.wbbasket.ru/vol1870/part187010/187010840/images/big/1.webp, https://basket-12.wbbasket.ru/vol1870/part187010/187010840/images/big/2.webp, https://basket-12.wbbasket.ru/vol1870/part187010/187010840/images/big/3.webp, https://basket-12.wbbasket.ru/vol1870/part187010/187010840/images/big/4.webp, https://basket-12.wbbasket.ru/vol1870/part187010/187010840/images/big/5.webp, https://basket-12.wbbasket.ru/vol1870/part187010/187010840/images/big/6.webp, https://basket-12.wbbasket.ru/vol1870/part187010/187010840/images/big/7.webp, https://basket-12.wbbasket.ru/vol1870/part187010/187010840/images/big/8.webp, https://basket-12.wbbasket.ru/vol1870/part187010/187010840/images/big/9.webp, https://basket-12.wbbasket.ru/vol1870/part187010/187010840/images/big/10.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/654547336/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>654547336</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Пальто шерстяное весна-осень</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>4673</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>ФАНРОНГ</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/250048628</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>M, S</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Роскошное женское пальто из шерсти, шелка и кашемира — идеальная пара для холодного сезона!
+Элегантный фасон выполнен из исключительно мягкой и теплой ткани премиум-класса: 72,8% шерсть, 15,1% натуральный шелк и 12,1% шерсть кролика. Такой благородный состав сочетает превосходную теплоизоляцию шерсти, нежную легкость натурального шелка и невероятную мягкость кашемира — вам будет комфортно и тепло даже в морозную погоду.
+Натуральные материалы отличаются легкостью, долговечностью и изысканной текстурой. Это пальто — безупречное качество и забота о вашем комфорте.
+Современный дизайн соответствует последним трендам, делая пальто универсальным предметом гардероба. Оно идеально подойдет для повседневной носки, прогулок и деловых встреч.
+Благодаря лаконичному стилю, пальто легко сочетается с любой обувью и аксессуарами, позволяя создавать безупречные образы для любого случая.
+Подарите себе не только тепло, но и непревзойденное чувство стиля и роскоши!</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Состав:  72,8% шерсть; 15,1% натуральный шелк; 12,1% шерсть кролика
+Цвет:  джем
+Сезон:  демисезон
+Рост модели на фото:  168 см
+Температурный режим:  от -5 °C до +10 °C
+Материал подкладки:  без подклада
+Покрой:  прямой
+Тип рукава:  длинные
+Опции капюшона:  без капюшона
+Пол:  Женский</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>https://basket-32.wbbasket.ru/vol6545/part654547/654547336/images/big/1.webp, https://basket-32.wbbasket.ru/vol6545/part654547/654547336/images/big/2.webp, https://basket-32.wbbasket.ru/vol6545/part654547/654547336/images/big/3.webp, https://basket-32.wbbasket.ru/vol6545/part654547/654547336/images/big/4.webp, https://basket-32.wbbasket.ru/vol6545/part654547/654547336/images/big/5.webp, https://basket-32.wbbasket.ru/vol6545/part654547/654547336/images/big/6.webp, https://basket-32.wbbasket.ru/vol6545/part654547/654547336/images/big/7.webp, https://basket-32.wbbasket.ru/vol6545/part654547/654547336/images/big/8.webp, https://basket-32.wbbasket.ru/vol6545/part654547/654547336/images/big/9.webp, https://basket-32.wbbasket.ru/vol6545/part654547/654547336/images/big/10.webp, https://basket-32.wbbasket.ru/vol6545/part654547/654547336/images/big/11.webp, https://basket-32.wbbasket.ru/vol6545/part654547/654547336/images/big/12.webp, https://basket-32.wbbasket.ru/vol6545/part654547/654547336/images/big/13.webp, https://basket-32.wbbasket.ru/vol6545/part654547/654547336/images/big/14.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/60657672/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>60657672</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Пальто</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>18668</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>ООО "ФРАНТИНО"</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/110473</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>ONE SIZE</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Пальто-халат из шерсти в клетку с капюшоном. Длина рукава-55 см.</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Цвет:  коричневый
+Сезон:  демисезон
+Вид застежки:  пояс; без застежки
+Рост модели на фото:  164 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  95-70-100
+Длина изделия по спинке:  117 см
+Материал подкладки:  Вискоза - 100 %
+Покрой:  пальто оверсайз
+Тип карманов:  внутренние боковые
+Тип рукава:  втачной длинный
+Опции капюшона:  несъемный капюшон
+Декоративные элементы:  без декора
+Конструктивные элементы:  Пояс съемный
+Пол:  Женский
+Комплектация:  1 шт пальто, 1 шт пояс
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>https://basket-04.wbbasket.ru/vol606/part60657/60657672/images/big/1.webp, https://basket-04.wbbasket.ru/vol606/part60657/60657672/images/big/2.webp, https://basket-04.wbbasket.ru/vol606/part60657/60657672/images/big/3.webp, https://basket-04.wbbasket.ru/vol606/part60657/60657672/images/big/4.webp, https://basket-04.wbbasket.ru/vol606/part60657/60657672/images/big/5.webp, https://basket-04.wbbasket.ru/vol606/part60657/60657672/images/big/6.webp, https://basket-04.wbbasket.ru/vol606/part60657/60657672/images/big/7.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/874752925/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>874752925</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Пальто оверсайз модное длинное женское демисезонное осень</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Елена</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/350235617</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Пальто новое, не надевала ни разу. Бирки срезаны. Размер 54, идет в размер. </t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Состояние товара:  Идеальное
+Состав:  50% шерсти 30% вискоза, 20% полиэстер
+Цвет:  серый; натуральный серый; зернистый светло-серый; серый меланж; бело-серый
+Пол:  Женский
+Сезон:  Демисезон
+Вид застежки:  пуговицы
+Утеплитель:  без утеплителя
+Температурный режим:  от +3 до +15
+Материал подкладки:  полиэстер
+Покрой:  свободный
+Тип карманов:  накладные
+Тип рукава:  длинные
+Опции капюшона:  без капюшона
+Опции опушки:  без опушки
+Мех опушки/отделки:  без меха
+Декоративные элементы:  без элементов
+Конструктивные элементы:  свободный крой
+Уход за вещами:  допускается отпаривание; деликатная химическая чистка
+Комплектация:  пояс; пальто
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>https://basket-39.wbbasket.ru/vol8747/part874752/874752925/images/big/1.webp, https://basket-39.wbbasket.ru/vol8747/part874752/874752925/images/big/2.webp, https://basket-39.wbbasket.ru/vol8747/part874752/874752925/images/big/3.webp, https://basket-39.wbbasket.ru/vol8747/part874752/874752925/images/big/4.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/211635831/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>211635831</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Пальто овечья шерсть экомех</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>22183</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Panafics Furs</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/32128</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>48, 50, 52, 54</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" t="n">
+        <v>4</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Шуба женская зимняя искусственная с добавлением шерсти от меховой фабрики "Panafics Furs" город Пятигорск.
+"Panafics Furs" - это эксклюзивная верхняя одежда с безупречным кроем и высоким качеством. 
+Экошуба длинная женская зимняя (цвет темно-синий). Длина ниже колена. Подойдет как для высоких, так и для невысоких девушек. Шуба искусственная на крючках с английским воротником. Воротник оснащен дополнительной застежкой на случай холодной ветряной погоды. Шуба легкая. Есть глубокие теплые карманы. 
+Такая модель экошубы из экомеха позволяет создать оригинальный образ. Обладательница экошубы всегда сможет подчеркнуть свою индивидуальность.
+Пальто из  50 % шерсти и 50% ПЭ сшито из полотна, изготовленного из натуральной шерсти состриженной с овцы, специально обработанной и вплетенной в текстильную основу – с равномерной плотностью и толщиной материала по всей поверхности изделия.
+Шерстяная шуба – не только красивая, но и теплая, так как натуральная шерсть обеспечивает тепло и комфорт даже в самые холодные дни. Температурный режим до -10.
+В нашем магазине есть шубы из экомеха и натурального меха больших размеров, обратите внимание.
+Пальто из экомеха отличается высоким качеством изготовления. Это шикарный подарок женщине, маме, подруге и любимой.
+</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Состав:  шерсть; полиэстер
+Цвет:  темно-синий
+Пол:  Женский
+Сезон:  зима
+Вид застежки:  крючки
+Рост модели на фото:  170 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  85-65-95
+Размер на модели:  46
+Утеплитель:  шерсть; экомех
+Температурный режим:  от +10°С до -20°С
+Материал подкладки:  полиэстер
+Покрой:  длинный
+Тип карманов:  прорезные
+Тип рукава:  длинные
+Декоративные элементы:  кнопки
+Особенности модели:  устойчивость к истиранию
+Уход за вещами:  химическая чистка
+Комплектация:  шуба из шерсти-1 шт.
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>https://basket-14.wbbasket.ru/vol2116/part211635/211635831/images/big/1.webp, https://basket-14.wbbasket.ru/vol2116/part211635/211635831/images/big/2.webp, https://basket-14.wbbasket.ru/vol2116/part211635/211635831/images/big/3.webp, https://basket-14.wbbasket.ru/vol2116/part211635/211635831/images/big/4.webp, https://basket-14.wbbasket.ru/vol2116/part211635/211635831/images/big/5.webp, https://basket-14.wbbasket.ru/vol2116/part211635/211635831/images/big/6.webp, https://basket-14.wbbasket.ru/vol2116/part211635/211635831/images/big/7.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/167970693/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>167970693</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Шубка натуральная с мехом</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>27332</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Киса Бутик</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/542562</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>40, 42, 44, 46</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" t="n">
+        <v>2</v>
+      </c>
+      <c r="J49" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Шубка из натуральной 100% овечьей шерсти (крупные завитушки), зима, за счет новых технологий она получилась невесома легкая и очень теплая.
+Внимание!!! Девочки при заказе, измерьте грудь сантиметром и смотрим выше размерную сетку, размер который написан вверху, ниже сантиметры вашей груди.
+Длина 105см, приталенный силуэт, с кожаным пояском. Рукав втачной полной длины с кожаным хлястиком. Очень удобно в автомобили. Красивый и теплый ворот куница (под соболь) на кнопках, защитит от холода, украсит и придаст элегантности выделяя ваши аккуратные плечики, создавая силуэту красивые формы. Также есть удобные и теплые карманы. Есть большие размеры. Удобное комфортное лекало, дышащая ткань. Овечья шерсть класса ЛЮКС. Ваше тело будет дышать и не потеть в нашей верхней одежде. Не забудьте также посетить наш магазин Kisa-Butik, где Вас ждет огромный выбор плащей, курток, пуховиков, шуб и многое другое. Кликните на картинку с нашим брендом и наслаждайтесь широким ассортиментом качественной верхней одежды. Будем признательны вам, если при покупке нашего товара, вы оставите отзыв. С уважением магазин Kisa-Butik</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>китай</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Состав:  Натуральная шерсть 100%
+Цвет:  светло-коричневый
+Сезон:  демисезон
+Размер на модели:  48
+Рост модели на фото:  168 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  125х120х138
+Утеплитель:  овчина 100%
+Температурный режим:  до -25 градусов
+Материал подкладки:  полиэстер
+Страна производства:  Китай
+Вид застежки:  пуговицы
+Особенности модели:  износостойкость
+Длина изделия по спинке:  110 см
+Декоративные элементы:  отложной ворот
+Тип карманов:  в шве
+Пол:  Женский
+Тип рукава:  длинные
+Покрой:  прямой
+Уход за вещами:  деликатная химическая чистка</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>https://basket-12.wbbasket.ru/vol1679/part167970/167970693/images/big/1.webp, https://basket-12.wbbasket.ru/vol1679/part167970/167970693/images/big/2.webp, https://basket-12.wbbasket.ru/vol1679/part167970/167970693/images/big/3.webp, https://basket-12.wbbasket.ru/vol1679/part167970/167970693/images/big/4.webp, https://basket-12.wbbasket.ru/vol1679/part167970/167970693/images/big/5.webp, https://basket-12.wbbasket.ru/vol1679/part167970/167970693/images/big/6.webp, https://basket-12.wbbasket.ru/vol1679/part167970/167970693/images/big/7.webp, https://basket-12.wbbasket.ru/vol1679/part167970/167970693/images/big/8.webp, https://basket-12.wbbasket.ru/vol1679/part167970/167970693/images/big/9.webp, https://basket-12.wbbasket.ru/vol1679/part167970/167970693/images/big/10.webp, https://basket-12.wbbasket.ru/vol1679/part167970/167970693/images/big/11.webp, https://basket-12.wbbasket.ru/vol1679/part167970/167970693/images/big/12.webp, https://basket-12.wbbasket.ru/vol1679/part167970/167970693/images/big/13.webp, https://basket-12.wbbasket.ru/vol1679/part167970/167970693/images/big/14.webp, https://basket-12.wbbasket.ru/vol1679/part167970/167970693/images/big/15.webp, https://basket-12.wbbasket.ru/vol1679/part167970/167970693/images/big/16.webp, https://basket-12.wbbasket.ru/vol1679/part167970/167970693/images/big/17.webp, https://basket-12.wbbasket.ru/vol1679/part167970/167970693/images/big/18.webp, https://basket-12.wbbasket.ru/vol1679/part167970/167970693/images/big/19.webp, https://basket-12.wbbasket.ru/vol1679/part167970/167970693/images/big/20.webp, https://basket-12.wbbasket.ru/vol1679/part167970/167970693/images/big/21.webp, https://basket-12.wbbasket.ru/vol1679/part167970/167970693/images/big/22.webp, https://basket-12.wbbasket.ru/vol1679/part167970/167970693/images/big/23.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/274161874/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>274161874</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Пальто укороченное шерстяное трапеция</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>9953</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Rendez-Vous</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/528630</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>XS, S, M, L, XL, XXL, 3XL</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" t="n">
+        <v>14</v>
+      </c>
+      <c r="J50" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Бежевое полупальто женское французского бренда Maison David. Состав: 50% шерсть натуральная, 50% полиэстер. Шерсть отлично согревает, при этом позволяет телу дышать, не создавая парникового эффекта. В шерстяных вещах тепло, но не жарко. Добавление полиэстера повышает прочность и устойчивость к износу. Вещи из полушерсти практичнее и проще в уходе, чем из шерсти без добавок. Одежда из смесовой шерсти — идеальный выбор для зимы и холодного демисезона. Состав подкладки: полиэстер.
+Верхняя одежда имеет силуэт трапецию. Модель отличает английский воротник и наличие прорезных карманов. Температурный режим от плюс 5 до минус 10.
+Ухаживайте за вещью правильно, чтобы она дольше служила и радовала вас. Правила по уходу указаны на вшивном ярлычке изделия. Разрешено: химчистка, вертикальная сушка, глажка на минимальных температурах. Запрещено: стирка, отбеливание, барабанная сушка.
+Полупальто в деловом стиле — удачное решение для офисного гардероба. Это сдержанная элегантность, уверенность и профессионализм. Maison David — дом современной элегантности. Бренд отражает идею французского bon chic, bon genre: искусство быть безупречным без усилий, сочетая гармонию интеллекта и формы, а качество становится главным языком красоты. Бренд соединяет современные тенденции с классическими формами, сохраняя баланс между актуальностью и вечностью. Каждая вещь Maison David создается, чтобы жить долго — сопровождать своего владельца в реальной, настоящей жизни: в работе, в путешествиях, в личных историях. Это не просто гардероб, а состояние уравновешенности и эстетического покоя.</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>китай</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Состав:  шерсть натуральная 50%; полиэстер 50%
+Цвет:  бежевый
+Пол:  Женский
+Сезон:  демисезон
+Рост модели на фото:  175 см
+Температурный режим:  от +5 °C до -10 °C
+Покрой:  трапеция
+Тип карманов:  прорезные
+Особенности модели:  Без капюшона, теплый
+Уход за вещами:  Химическая стирка; глажка на минимальных температурах; стирка запрещена
+Комплектация:  1 шт
+Страна производства:  Китай</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>https://basket-17.wbbasket.ru/vol2741/part274161/274161874/images/big/1.webp, https://basket-17.wbbasket.ru/vol2741/part274161/274161874/images/big/2.webp, https://basket-17.wbbasket.ru/vol2741/part274161/274161874/images/big/3.webp, https://basket-17.wbbasket.ru/vol2741/part274161/274161874/images/big/4.webp, https://basket-17.wbbasket.ru/vol2741/part274161/274161874/images/big/5.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/182658371/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>182658371</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Пальто женское зимнее оверсайз теплое укороченное</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>6113</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>EURYDIKE</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/23312</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>48, 50, 52, 54, 56</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" t="n">
+        <v>29</v>
+      </c>
+      <c r="J51" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Модное и укороченное зимнее пальто из качественной ткани, на большие размеры, выгодно и приятно, выделит  Вас из общей массы, особенно холодной и морозной зимой. Молодежная модель сшита из мягкой, ворстистой, шерстяной ткани, прошедшей специальную тепловую обработку, что бы не терять форму и вид, при носке и попаданию под дождь или снег. Такая верхняя женская одежда, позволит вам  чувствовать себя максимально комфортнов и удобно в зимний и демисезонный период, холодной осенью и ранней весной.  Драповые пальто из тканей под искуственные шубы, тедди и чебурашки, являются трендом и очень практичны в носке. Производство Россия. Размеры с 48 по 56. В комплекте есть пояс, с помощью которого, можно приталить пальто и подчеркнуть фигуру. Удобный спущенный рукав, обеспечит Вам  свободу движения и позволит одевать под стильное пальто любую одежду. Утеплитель стеганный шерстепон из 100% натуральной шерсти. Аккуратный и маленький английский воротник надежно прикроет вашу шею от холода. Стильная классическая модель халат, идеально подойдет тем, кто за рулем и тем, кто не любит длинные и тяжелые утепленные пальто.  Так же модель можно одеть на свадьбы, дни рождения и другие торжественные мероприятия. Дизайнерское пальто подойдет как женщинам, так и молодым девушкам, а так же беременным, будущим и молодым мамам. Его Вы можете одевать на выход, на работу или в офис, а так же для прогулок с друзьями. Вам в нем всегда будет комфортно и уютно, а так же тепло и удобно. Короткая, классическая модель прекрасно подойдет, на любой рост, на средний, низкий и на высокий. Сейчас брендовая модель учавствует в акции, её можно приобрести по выгодной, распродажной и низкой цене. Оно станет прекрасным подарком вашим любимым женщинам в Новогодние, Рожденственские и другие праздники, а так же дни рождения. </t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Состав:  50 шерсть, 30 вискоза, 20 полиэстер
+Цвет:  светло-бежевый
+Сезон:  зима
+Размер на модели:  48
+Рост модели на фото:  168 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  96-70-94
+Утеплитель:  шерстепон
+Температурный режим:  от -15 до +10
+Плотность синтетического утеплителя:  180 г/кв.м
+Материал подкладки:  полиэстер; шерстепон
+Страна производства:  Россия
+Вид застежки:  кнопки; пуговицы
+Особенности модели:  для невысоких
+Опции капюшона:  без капюшона
+Длина изделия по спинке:  90 см
+Опции опушки:  без опушки
+Декоративные элементы:  молодежное; зима; шубка
+Тип карманов:  прорезные
+Конструктивные элементы:  оверсайз
+Пол:  Женский
+Тип рукава:  длинные
+Комплектация:  пояс; верхняя одежда; для женщин; шуба; Альпака; пальто
+Покрой:  оверсайз
+Уход за вещами:  деликатная химическая чистка; допускается отпаривание</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>https://basket-12.wbbasket.ru/vol1826/part182658/182658371/images/big/1.webp, https://basket-12.wbbasket.ru/vol1826/part182658/182658371/images/big/2.webp, https://basket-12.wbbasket.ru/vol1826/part182658/182658371/images/big/3.webp, https://basket-12.wbbasket.ru/vol1826/part182658/182658371/images/big/4.webp, https://basket-12.wbbasket.ru/vol1826/part182658/182658371/images/big/5.webp, https://basket-12.wbbasket.ru/vol1826/part182658/182658371/images/big/6.webp, https://basket-12.wbbasket.ru/vol1826/part182658/182658371/images/big/7.webp, https://basket-12.wbbasket.ru/vol1826/part182658/182658371/images/big/8.webp, https://basket-12.wbbasket.ru/vol1826/part182658/182658371/images/big/9.webp, https://basket-12.wbbasket.ru/vol1826/part182658/182658371/images/big/10.webp, https://basket-12.wbbasket.ru/vol1826/part182658/182658371/images/big/11.webp, https://basket-12.wbbasket.ru/vol1826/part182658/182658371/images/big/12.webp, https://basket-12.wbbasket.ru/vol1826/part182658/182658371/images/big/13.webp, https://basket-12.wbbasket.ru/vol1826/part182658/182658371/images/big/14.webp, https://basket-12.wbbasket.ru/vol1826/part182658/182658371/images/big/15.webp, https://basket-12.wbbasket.ru/vol1826/part182658/182658371/images/big/16.webp, https://basket-12.wbbasket.ru/vol1826/part182658/182658371/images/big/17.webp, https://basket-12.wbbasket.ru/vol1826/part182658/182658371/images/big/18.webp, https://basket-12.wbbasket.ru/vol1826/part182658/182658371/images/big/19.webp, https://basket-12.wbbasket.ru/vol1826/part182658/182658371/images/big/20.webp, https://basket-12.wbbasket.ru/vol1826/part182658/182658371/images/big/21.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/444421094/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>444421094</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Пальто весеннее длинное оверсайз</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>5415</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>the nana</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/236134</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>36-38, 40-42, 44-46, 48-50, 52-54, 56-58, 60-62, 64-66, 68-70</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" t="n">
+        <v>56</v>
+      </c>
+      <c r="J52" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Удлиненное шерстяное пальто в полоску  - стильная и практичная вещь на каждый день, как из пинтерест. Пальто выполнено из мягкой премиальной драповой ткани, приятной на ощупь. Модное и популярное пальто – халат имеет классический прямой крой, длину макси в пол, длинные рукава реглан, модный двойной английский воротник, прорезные удобные карманы по бокам, V – образный вырез, пояс, подчеркивающий силуэт. Трендовое коричневое оверсайз пальто бренда the nana выполнено в универсальном дизайне и идеально подходит для весны 2026. 
+Эта форма верхней одежды на сезон  весна-осень со спущенным плечом не сковывает движений. Комфорт при ходьбе обеспечивает шлица. Широкое пинтерест пальто прекрасно сохраняет цвет и форму на весь срок эксплуатации, благодаря дублированию специальным материалом. Ткань прошла тепловую обработку, это значит пальто не сядет и на нем не образуются катышки. Швы выполнены на современном японском оборудовании JUKI немецкими нитками Gutermann.
+ Весеннее элегантное пальто подходит для женщин и девушек любого роста и типа фигуры - высоких и невысоких, стройных и полных. Если Вы поклонник стиля оверсайз, просто закажите свой размер, так как пальто выполнено в свободном крое. Удобный пояс при желании легко сделает приталенное пальто. Если хотите классическую посадку, то берите на размер меньше. 
+Красивое пальто подойдет для носки теплой зимой и переходные периоды года – демисезон ( весна ) и еврозима. Оптимальный температурный режим для носки составляет от -5 до +15С.  Дизайнерское теплое пальто из натурального материала согреет в холодную погоду, так как изделие содержит мембранную пропитку. Трендовое пальто свободного кроя подходит для повседневных кэжуал образов в офис, так и для более нарядных. Девочки подросткового возраста могут носить универсальное пальто в школу осенью. В наличии большие размеры плюс сайз.</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>киргизия</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Состав:  шерсть 40%; вискоза 30%; полиэстер 30%
+Цвет:  шоколадный
+Пол:  Женский
+Сезон:  Демисезон
+Вид застежки:  пуговицы; пояс
+Рост модели на фото:  171 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  83-65-92
+Размер на модели:  42
+Утеплитель:  без утеплителя
+Температурный режим:  от -5°C до +15°С
+Материал подкладки:  полиэстер 50%; вискоза 50%
+Покрой:  прямой
+Тип карманов:  прорезные
+Тип рукава:  длинные
+Опции капюшона:  без капюшона
+Опции опушки:  без опушки
+Декоративные элементы:  без элементов
+Особенности модели:  двубортная
+Уход за вещами:  деликатная химическая чистка
+Комплектация:  Пальто двубортное 1шт.
+Страна производства:  Киргизия</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>https://basket-25.wbbasket.ru/vol4444/part444421/444421094/images/big/1.webp, https://basket-25.wbbasket.ru/vol4444/part444421/444421094/images/big/2.webp, https://basket-25.wbbasket.ru/vol4444/part444421/444421094/images/big/3.webp, https://basket-25.wbbasket.ru/vol4444/part444421/444421094/images/big/4.webp, https://basket-25.wbbasket.ru/vol4444/part444421/444421094/images/big/5.webp, https://basket-25.wbbasket.ru/vol4444/part444421/444421094/images/big/6.webp, https://basket-25.wbbasket.ru/vol4444/part444421/444421094/images/big/7.webp, https://basket-25.wbbasket.ru/vol4444/part444421/444421094/images/big/8.webp, https://basket-25.wbbasket.ru/vol4444/part444421/444421094/images/big/9.webp, https://basket-25.wbbasket.ru/vol4444/part444421/444421094/images/big/10.webp, https://basket-25.wbbasket.ru/vol4444/part444421/444421094/images/big/11.webp, https://basket-25.wbbasket.ru/vol4444/part444421/444421094/images/big/12.webp, https://basket-25.wbbasket.ru/vol4444/part444421/444421094/images/big/13.webp, https://basket-25.wbbasket.ru/vol4444/part444421/444421094/images/big/14.webp, https://basket-25.wbbasket.ru/vol4444/part444421/444421094/images/big/15.webp, https://basket-25.wbbasket.ru/vol4444/part444421/444421094/images/big/16.webp, https://basket-25.wbbasket.ru/vol4444/part444421/444421094/images/big/17.webp, https://basket-25.wbbasket.ru/vol4444/part444421/444421094/images/big/18.webp, https://basket-25.wbbasket.ru/vol4444/part444421/444421094/images/big/19.webp, https://basket-25.wbbasket.ru/vol4444/part444421/444421094/images/big/20.webp, https://basket-25.wbbasket.ru/vol4444/part444421/444421094/images/big/21.webp, https://basket-25.wbbasket.ru/vol4444/part444421/444421094/images/big/22.webp, https://basket-25.wbbasket.ru/vol4444/part444421/444421094/images/big/23.webp, https://basket-25.wbbasket.ru/vol4444/part444421/444421094/images/big/24.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/614845843/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>614845843</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Пальто зимнее женское</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>4190</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>SHITAIMEI</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/250069413</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>XS, S, M, L</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>40</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" t="n">
+        <v>4</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Удлиненное шерстяное пальто – стильная и практичная вещь на каждый день. Пальто выполнено из мягкой премиальной ткани, приятной на ощупь. Модное и популярное пальто – халат имеет классический прямой крой, длинные рукава реглан
+модный двойной английский воротник, прорезные удобные карманы по бокам, V – образный вырез, пояс, подчеркивающий силуэт и внутренний пояс, который не позволит пальто распахнуться на ветру. 
+Эта форма верхней одежды со спущенным плечом не сковывает движений. Комфорт при ходьбе обеспечивает шлица. 
+Широкое пальто прекрасно сохраняет цвет и форму на весь срок эксплуатации, благодаря дублированию специальным материалом. 
+Весенние пальто подойдут для женщин и девушек любого роста и типа фигуры - высоких и невысоких, стройных и полных. 
+Красивое пальто подойдет для носки теплой зимой и переходные периоды года – демисезон ( весна ). 
+Дизайнерское теплое пальто из натурального материала согреет в холодную погоду, так как изделие содержит мембранную пропитку. Оптимальный температурный режим для носки составляет от -5до +10С. Трендовое пальто свободного кроя подходит будущим мамам. 
+Удобный пояс при желании легко сделает приталенное пальто. Девочки подросткового возраста могут носить универсальное пальто в школу осенью.
+Это модное пальто может сделать ваше рождественское свидание еще более очаровательным</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>китай</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Состав:  70% шерсть; 24% полиэфирного волокна; 6% других волокон
+Цвет:  бежевый
+Сезон:  демисезон
+Вид застежки:  пуговицы
+Рост модели на фото:  171 см
+Температурный режим:  от -5°C до +10°С
+Материал подкладки:  полиэстер 50%; вискоза 30%
+Покрой:  приталенный
+Тип карманов:  с клапаном
+Тип рукава:  длинные
+Опции капюшона:  без капюшона
+Пол:  Женский
+Уход за вещами:  деликатная химическая чистка
+Страна производства:  Китай</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>https://basket-31.wbbasket.ru/vol6148/part614845/614845843/images/big/1.webp, https://basket-31.wbbasket.ru/vol6148/part614845/614845843/images/big/2.webp, https://basket-31.wbbasket.ru/vol6148/part614845/614845843/images/big/3.webp, https://basket-31.wbbasket.ru/vol6148/part614845/614845843/images/big/4.webp, https://basket-31.wbbasket.ru/vol6148/part614845/614845843/images/big/5.webp, https://basket-31.wbbasket.ru/vol6148/part614845/614845843/images/big/6.webp, https://basket-31.wbbasket.ru/vol6148/part614845/614845843/images/big/7.webp, https://basket-31.wbbasket.ru/vol6148/part614845/614845843/images/big/8.webp, https://basket-31.wbbasket.ru/vol6148/part614845/614845843/images/big/9.webp, https://basket-31.wbbasket.ru/vol6148/part614845/614845843/images/big/10.webp, https://basket-31.wbbasket.ru/vol6148/part614845/614845843/images/big/11.webp, https://basket-31.wbbasket.ru/vol6148/part614845/614845843/images/big/12.webp, https://basket-31.wbbasket.ru/vol6148/part614845/614845843/images/big/13.webp, https://basket-31.wbbasket.ru/vol6148/part614845/614845843/images/big/14.webp, https://basket-31.wbbasket.ru/vol6148/part614845/614845843/images/big/15.webp, https://basket-31.wbbasket.ru/vol6148/part614845/614845843/images/big/16.webp, https://basket-31.wbbasket.ru/vol6148/part614845/614845843/images/big/17.webp, https://basket-31.wbbasket.ru/vol6148/part614845/614845843/images/big/18.webp, https://basket-31.wbbasket.ru/vol6148/part614845/614845843/images/big/19.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/531218285/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>531218285</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Пальто - бушлат</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>19864</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>ООО СВЕТ</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/4221200</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>42, 44, 46, 48</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>2</v>
+      </c>
+      <c r="I54" t="n">
+        <v>4</v>
+      </c>
+      <c r="J54" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Стильное женское пальто из деликатной ткани с вискозой идеально подходит для сезона весна-осень. Выполнено в  цвете кэмел который легко сочетается с различными элементами гардероба. Изделие имеет укороченный фасон, что добавляет ему современности и делает его подходящим для повседневной носки и городских прогулок.
+Материал пальто обладает приятной текстурой, напоминающей мягкий драп. Это обеспечивает комфорт при носке, а высокое содержание натуральной шерсти помогает сохранять тепло в прохладную погоду. Полупальто оснащено классическим английским воротником, который подчеркивает изысканность дизайна.
+Двубортная застежка на крупные пуговицы выполняет как декоративную, так и практическую функцию. По бокам расположены удобные прорезные карманы — идеальное решение для хранения мелких вещей или согревания рук.
+Свободный крой и немного заниженная линия плеч создают эффект легкого оверсайза, позволяя комбинировать полупальто с плотными свитерами или водолазками. Благодаря такой конструкции модель подходит женщинам разных комплекций и размеров, включая большие размеры.
+Полупальто — это стильная демисезонная верхняя одежда для женщин, которая гармонично впишется в любой гардероб. Оно подойдет как для делового образа с брюками или юбкой-карандашом, так и для повседневного стиля с джинсами или платьем.
+Это короткое пальто отличается своей функциональностью: оно достаточно теплое для осенних прогулок и одновременно легкое для весенней прохлады. Отличный выбор для тех, кто ценит сочетание практичности и модного внешнего вида!</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Состав:  70% шерсти; 30% вискоза
+Цвет:  кэмел
+Пол:  Женский
+Сезон:  Демисезон
+Вид застежки:  пуговицы
+Рост модели на фото:  176 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  82-67-87
+Размер на модели:  46
+Температурный режим:  от +5 °C до +10 °C
+Материал подкладки:  45% вискоза; 55% полиэстера
+Покрой:  прямой
+Тип карманов:  прорезные
+Опции капюшона:  без капюшона
+Опции опушки:  без опушки
+Мех опушки/отделки:  без меха
+Декоративные элементы:  пуговицы
+Особенности модели:  большие размеры
+Уход за вещами:  стирка при t не более 30°C; деликантная
+Комплектация:  пальто-1 шт
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>https://basket-28.wbbasket.ru/vol5312/part531218/531218285/images/big/1.webp, https://basket-28.wbbasket.ru/vol5312/part531218/531218285/images/big/2.webp, https://basket-28.wbbasket.ru/vol5312/part531218/531218285/images/big/3.webp, https://basket-28.wbbasket.ru/vol5312/part531218/531218285/images/big/4.webp, https://basket-28.wbbasket.ru/vol5312/part531218/531218285/images/big/5.webp, https://basket-28.wbbasket.ru/vol5312/part531218/531218285/images/big/6.webp, https://basket-28.wbbasket.ru/vol5312/part531218/531218285/images/big/7.webp, https://basket-28.wbbasket.ru/vol5312/part531218/531218285/images/big/8.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/17171342/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>17171342</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Пальто демисезонное с капюшоном длинное</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10105</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>BAZI FASHION GROUP</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/45521</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>48-176, 48-182, 50-176, 50-182, 52-176, 52-182, 54-176, 54-182, 56-176, 56-182, 58-176, 58-182</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" t="n">
+        <v>31</v>
+      </c>
+      <c r="J55" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>ДЛЯ ТЕХ, КТО ЦЕНИТ И ПОНИМАЕТ УНИКАЛЬНОЕ КАЧЕСТВО И МАСТЕРСТВО ТЕХНОЛОГОВ И ДИЗАЙНЕРОВ МАРКИ ABSOLUTEX. Это очень универсальное неформальное пальто, которое прекрасно гармонирует с большинством джинсов, чиносов, свитеров и кардиганов. Изделие получилось очень легким и при этом теплым. Мастера марки ABSOLUTEX позаботились продумать мельчайшие детали начиная от пуговиц, покрашенных под ткань, заканчивая подкладкой и других элементов. Все детали изделия, обработаны вручную по технологии, передаваемой из поколения в поколение. Это пальто из осенне-зимней коллекции одинаково хорошо рифмуется как с формальным костюмом, так и с вещами в стиле SMART CASUAL. Это пальто, сделанное из шерсти исключительного качества, выделит Вас из толпы подчеркивая безупречный вкус. Пальто - главный "Must Have" среди актуальных моделей верхней одежды. С приближением холодов рекомендуем присмотреть себе пальто классического кроя. Зимнее мужское пальто, а также наше удлинённое пальто от ABSOLUTEX оптимальной длины- настоящий тренд сезона, выполненный из HI QALITY WOOL материала на основе натуральной шерсти. Благодаря премиальной итальянской шерсти от Lora de Castello, ткань выглядит еще более красивой, не выцветет и не теряет форму, проста в уходе и почти не мнётся. Цветовая гамма построена на базовых оттенках, сером и коричневом, черное мужское пальто, мужское длинное пальто на зиму, что позволит этому пальто легко войти в привычный гардероб делового мужчины. Компания является одним из лидеров в модной одежде. Пальто, отличается не только свободным кроем, но и лучшим качеством, ведь в нем вы будете ощущать себя комфортно, в холодную, так и в теплую погоду, на природе, в путешествии, на прогулке с друзьями. В зависимости от фасона, ткани и цвета, вы можете создать множество луков, которые будут очень разнообразны и интересны. ЛУЧШЕЕ СОЧЕТАНИЕ ЦЕНЫ И КАЧЕСТВО НА ВАЛДБЕРЕС.</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Состав:  Премиальная 100% шерсть от Lora de Castello
+Цвет:  черный; черный матовый
+Пол:  Мужской
+Сезон:  зима
+Вид застежки:  Мужское пальто классическое теплое на пуговицы на молнии теплое элитная шерсть
+Параметры модели на фото (ОГ-ОТ-ОБ):  Классическое деловое мужское пальто из шерсти стильное на выход утепленное
+Размер на модели:  52 пальто мужское черное синее классическое большой размер Тренч кардиган
+Утеплитель:  термофин пальто мужское теплое бежевое черное синее серое модное пуховик с мехом
+Температурный режим:  Пальто на осень зиму весну всесезонная демисезонная теплое шерстяное зимнее
+Материал подкладки:  вискоза пальто мужское зимнее оверсайз пальто мужское длинное кашемир шерсть
+Покрой:  классическое мужское пальто зимнее осеннее стеганое пуховик блейзер
+Тип карманов:  прорезные молодежный трендовый повседневный теплый зимний осенний
+Тип рукава:  Пальто мужское классическое с длинными рукавами темное светлое длинное
+Опции капюшона:  Пальто мужское демисезонное с капюшоном и без длинное casual кашемир
+Опции опушки:  классическое мужское пальто с мехом без на зиму осень весну большие размеры
+Декоративные элементы:  пальто мужское классическое шерстяное с капюшоном и без модное casual
+Особенности модели:  пальто мужское приталенное черное синие с капюшоном базиони итальянская шерсть
+Уход за вещами:  деликатная химическая чистка, пальто мужское классическое шерстяное теплое
+Комплектация:  пальто; вешалка
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>https://basket-02.wbbasket.ru/vol171/part17171/17171342/images/big/1.webp, https://basket-02.wbbasket.ru/vol171/part17171/17171342/images/big/2.webp, https://basket-02.wbbasket.ru/vol171/part17171/17171342/images/big/3.webp, https://basket-02.wbbasket.ru/vol171/part17171/17171342/images/big/4.webp, https://basket-02.wbbasket.ru/vol171/part17171/17171342/images/big/5.webp, https://basket-02.wbbasket.ru/vol171/part17171/17171342/images/big/6.webp, https://basket-02.wbbasket.ru/vol171/part17171/17171342/images/big/7.webp, https://basket-02.wbbasket.ru/vol171/part17171/17171342/images/big/8.webp, https://basket-02.wbbasket.ru/vol171/part17171/17171342/images/big/9.webp, https://basket-02.wbbasket.ru/vol171/part17171/17171342/images/big/10.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/543334996/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>543334996</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Пальто утеплённое шерстяное с воротником стойкой</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>8560</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>CORESSI</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/26796</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>42, 44, 46, 48, 50, 52, 54</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" t="n">
+        <v>464</v>
+      </c>
+      <c r="J56" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Пальто женское весна-осень CORESSI (КОРЕССИ) — стильная и практичная модель для сезона 2026 года. Базовое женское пальто легко вписывается в повседневный и деловой гардероб.
+Женское короткое пальто на весну и осень подходит для повседневной носки, офиса и городских образов. Утеплённая шерстяная демисезонная модель обеспечивает комфорт в прохладную погоду и межсезонье.
+Состав: шерсть — 57%, вискоза — 36%, полиэстер — 7%.
+Длина по спинке — 63 см. Длина рукава — 63,5 см.
+Компактная длина делает короткое пальто особенно удобным для поездок за рулём и активного ритма города. Пальто женское автоледи комфортно при движении и не сковывает посадку за рулём. Изделие выполнено из ткани с высоким содержанием натуральной шерсти. Плотная пальтовая ткань мягкая, приятная к телу и хорошо держит форму.
+Внутри используется современный утеплитель TermoFinn (термофин), созданный по технологии ультратонкого микроволокна. Он лёгкий, не деформируется, не даёт усадки, его структура помогает сохранять естественное тепло и поддерживать комфортный температурный баланс в течение дня, адаптируясь к переменчивой осенней и весенней погоде.
+Однобортный крой и кнопки формируют аккуратный силуэт, воротник-стойка защищает от ветра. Глубокие карманы с листочкой добавляют практичности и подчёркивают продуманный дизайн.
+Цвет — черный (глубокий черный): базовый оттенок, который легко сочетается с офисными и повседневными комплектами. Черное женское пальто выглядит сдержанно и современно. Укороченное пальто для женщин остаётся практичным выбором на каждый день.
+Ворсовая поверхность ткани обусловлена высоким содержанием шерсти. Уход простой: используйте липкий ролик или велюровую щётку по направлению ворса, чтобы поддерживать аккуратный вид ткани.
+Пальто отшивается в России на современном оборудовании и проходит строгий контроль качества. Классическое демисезонное пальто подходит для ранней весны и прохладной осени, а также может использоваться как вариант для еврозимы и мягкой теплой зимы.
+</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Состав:  шерсть; вискоза; полиэстер
+Цвет:  черный; глубокий черный
+Пол:  Женский
+Сезон:  демисезон
+Вид застежки:  кнопки
+Рост модели на фото:  164 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  83-60-89
+Размер на модели:  42
+Утеплитель:  термофин
+Плотность синтетического утеплителя:  100 г/кв.м
+Температурный режим:  от -5°C до +15°С
+Материал подкладки:  полиэстер
+Покрой:  прямой
+Тип карманов:  прорезные
+Тип рукава:  длинные
+Опции капюшона:  без капюшона
+Опции опушки:  без опушки
+Декоративные элементы:  застежка на кнопках; глубокие карманы с листочкой; Ворсовая ткань
+Особенности модели:  однобортная; ветрозащита; износостойкость
+Уход за вещами:  деликатная химическая чистка; допускается отпаривание
+Комплектация:  Пальто - 1 шт; упаковочная сумка чемодан
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>https://basket-28.wbbasket.ru/vol5433/part543334/543334996/images/big/1.webp, https://basket-28.wbbasket.ru/vol5433/part543334/543334996/images/big/2.webp, https://basket-28.wbbasket.ru/vol5433/part543334/543334996/images/big/3.webp, https://basket-28.wbbasket.ru/vol5433/part543334/543334996/images/big/4.webp, https://basket-28.wbbasket.ru/vol5433/part543334/543334996/images/big/5.webp, https://basket-28.wbbasket.ru/vol5433/part543334/543334996/images/big/6.webp, https://basket-28.wbbasket.ru/vol5433/part543334/543334996/images/big/7.webp, https://basket-28.wbbasket.ru/vol5433/part543334/543334996/images/big/8.webp, https://basket-28.wbbasket.ru/vol5433/part543334/543334996/images/big/9.webp, https://basket-28.wbbasket.ru/vol5433/part543334/543334996/images/big/10.webp, https://basket-28.wbbasket.ru/vol5433/part543334/543334996/images/big/11.webp, https://basket-28.wbbasket.ru/vol5433/part543334/543334996/images/big/12.webp, https://basket-28.wbbasket.ru/vol5433/part543334/543334996/images/big/13.webp, https://basket-28.wbbasket.ru/vol5433/part543334/543334996/images/big/14.webp, https://basket-28.wbbasket.ru/vol5433/part543334/543334996/images/big/15.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/256159109/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>256159109</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Пальто утепленное с мехом</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>8757</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>ABRIGO COLLECTION</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/4185520</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>42, 46</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" t="n">
+        <v>5</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Женское зимнее пальто, выполненное полуприталенным кроем, выгодно подчеркивает талию и зрительно добавляет роста. Длинное женское пальто изготовлено из качественных материалов: шерсть с добавлением вискозы и эластана с меховой опушкой, защищающих от пониженных температур до -15 С.Не рекомендуется сушить женское пальто с помощью барабанной сушки. Качественные материалы обеспечивают длительный срок носки. Разнообразие расцветок позволяет подобрать вариант под конкретный стиль. Материал устойчив к образованию катышек (особенно в области подмышек от длительной носки сумки). Подклад из полиэстера и меховой воротник надежно защищают от проникновения ветра. В ассортименте модели для полных и стройных, все зимние пальто имеют длину до колена и прямой полуприталенный крой. Женское пальто больших размеров изготовлено с учетом особенностей фигуры. Качественный пошив и натуральная шерсть обеспечивают комфорт в зимнюю погоду и надежно защищают от холода.</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Состав:  шерсть-75%; вискоза-20%; эластан-5%
+Цвет:  черный; серый
+Сезон:  зима
+Размер на модели:  44
+Рост модели на фото:  174 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  92-66-94
+Утеплитель:  шерсть
+Материал подкладки:  полиэстер
+Температурный режим:  от 0 °C до -14 °C
+Вид застежки:  пуговица
+Воротник:  классический
+Опции капюшона:  без капюшона
+Опции опушки:  съемная опушка
+Тип карманов:  прорезные
+Особенности модели:  ветрозащита
+Пол:  Женский
+Уход за вещами:  барабанная сушка запрещена
+Комплектация:  Пальто женское зимнее с поясом-1 шт
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>https://basket-16.wbbasket.ru/vol2561/part256159/256159109/images/big/1.webp, https://basket-16.wbbasket.ru/vol2561/part256159/256159109/images/big/2.webp, https://basket-16.wbbasket.ru/vol2561/part256159/256159109/images/big/3.webp, https://basket-16.wbbasket.ru/vol2561/part256159/256159109/images/big/4.webp, https://basket-16.wbbasket.ru/vol2561/part256159/256159109/images/big/5.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/19064302/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>19064302</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Пальто зимнее в клетку натуральный мех</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>19484</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>BAZI FASHION GROUP</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/29914</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>60-176, 64-176, 62-176, 58-176, 56-176, 54-176, 52-176, 50-176</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" t="n">
+        <v>11</v>
+      </c>
+      <c r="J58" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Элегантное твидовое мужское пальто BAZIONI, созданное по итальянским лекалам, идеально подходит для сезона осень-зима. Полупальто состоит из 100% шерсти, что придает ему теплозащитные свойства. Укороченное пальто оснащено центральной застежкой на молнии, закрытой планкой с пуговицами, что обеспечивает дополнительную защиту от ветра и придаёт модели строгий вид. Воротник-стойка с отстегивающимся натуральным мехом из мутона добавляет изысканности и делает эту модель универсальной – короткое пальто можно носить как с мехом, так и без него, создавая разные образы.
+Функциональность демисезонной куртки дополняется наличием боковых карманов с клапанами, а также вертикальными нагрудными карманами, что позволяет разместить необходимые мелочи или согреть руки в прохладную погоду. Декоративные элементы, такие как отрезные кокетки на полочке и спинке, а также декоративная пуговица на двухшовных рукавах, делают дизайн завершённым и стильным. Внутренняя подкладка состоит на 50% из вискозы и на 50% из полиэстера, что обеспечивает комфорт при носке, а утеплитель Термоплюс позволяет сохранять тепло даже в прохладную погоду.
+Эта модель отлично впишется в гардероб любого мужчины, дополнив его классический стиль или повседневный образ. Пальто можно носить как в повседневной жизни, так и на деловых встречах. Если выбрать пальто на один размер больше, оно станет отличным вариантом оверсайз (oversize), что придаст образу лёгкую небрежность и стильный современный акцент. Это универсальное решение как для молодого парня, так и для зрелого мужчины, который ценит высокое качество и современный дизайн.
+Мужское демисезонное пальто BAZIONI – идеальный подарок на любой праздник. Оно подчеркнет заботу о комфорте и стиле близкого человека и станет отличным подарком на Новый год или  23 февраля. </t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Состав:  ПРЕМИАЛЬНАЯ ШЕРСТЬ 100% от Lanificio De Ballis; дополнительную обработка NANO tec revolution
+Цвет:  синий; темно-синий
+Пол:  Мужской
+Сезон:  зима
+Вид застежки:  молния; кнопки
+Рост модели на фото:  185 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  102-88-99
+Размер на модели:  50-176
+Утеплитель:  термофин
+Плотность синтетического утеплителя:  150 г/кв.м
+Температурный режим:  от +10°С до -10°С
+Материал подкладки:  50% Вискоза; 50% полиэстер
+Покрой:  прямой
+Тип карманов:  молодежный трендовый повседневный теплый зимний осенний шерсть 100% темный
+Тип рукава:  длинные
+Опции капюшона:  без капюшона
+Опции опушки:  Воротник съемный
+Декоративные элементы:  пальто мужское классическое шерстяное теплое на зиму демисезонное с капюшоном
+Особенности модели:  воротник из натурального меха мутон; ветрозащита; немнущийся материал
+Уход за вещами:  химическая чистка
+Комплектация:  пальто; вешалка; пакет
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>https://basket-02.wbbasket.ru/vol190/part19064/19064302/images/big/1.webp, https://basket-02.wbbasket.ru/vol190/part19064/19064302/images/big/2.webp, https://basket-02.wbbasket.ru/vol190/part19064/19064302/images/big/3.webp, https://basket-02.wbbasket.ru/vol190/part19064/19064302/images/big/4.webp, https://basket-02.wbbasket.ru/vol190/part19064/19064302/images/big/5.webp, https://basket-02.wbbasket.ru/vol190/part19064/19064302/images/big/6.webp, https://basket-02.wbbasket.ru/vol190/part19064/19064302/images/big/7.webp, https://basket-02.wbbasket.ru/vol190/part19064/19064302/images/big/8.webp, https://basket-02.wbbasket.ru/vol190/part19064/19064302/images/big/9.webp, https://basket-02.wbbasket.ru/vol190/part19064/19064302/images/big/10.webp, https://basket-02.wbbasket.ru/vol190/part19064/19064302/images/big/11.webp, https://basket-02.wbbasket.ru/vol190/part19064/19064302/images/big/12.webp, https://basket-02.wbbasket.ru/vol190/part19064/19064302/images/big/13.webp, https://basket-02.wbbasket.ru/vol190/part19064/19064302/images/big/14.webp, https://basket-02.wbbasket.ru/vol190/part19064/19064302/images/big/15.webp, https://basket-02.wbbasket.ru/vol190/part19064/19064302/images/big/16.webp, https://basket-02.wbbasket.ru/vol190/part19064/19064302/images/big/17.webp, https://basket-02.wbbasket.ru/vol190/part19064/19064302/images/big/18.webp, https://basket-02.wbbasket.ru/vol190/part19064/19064302/images/big/19.webp, https://basket-02.wbbasket.ru/vol190/part19064/19064302/images/big/20.webp, https://basket-02.wbbasket.ru/vol190/part19064/19064302/images/big/21.webp, https://basket-02.wbbasket.ru/vol190/part19064/19064302/images/big/22.webp, https://basket-02.wbbasket.ru/vol190/part19064/19064302/images/big/23.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/139851686/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>139851686</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Пальто весеннее съемный воротник</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>25187</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>FABRIKA STYLE SEVERINA</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/166951</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>50, 52, 54, 56, 58, 60, 62, 48, 46</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>1</v>
+      </c>
+      <c r="I59" t="n">
+        <v>10</v>
+      </c>
+      <c r="J59" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Модное стеганое, комбинированное женское пальто с драповыми вставками и меховым воротником из натурального меха финского песца в универсальном и практичном цвете, от производителя fabrika style SEVERINA. Идеально подойдет для прогулки в холодную, осеннюю и зимнюю погоду. Удлиненная шерстяная верхняя одежда в стиле oversize - легкая и теплая новая вещь в вашем гардеробе, с которой вы не заходите расставаться в демисезон и евро зимой, в которой вам будет комфортно за счет утеплителя в ней нового поколения Термофин. Она станет вашим стильным классическим образом и трендом сезона 2025 года. У нее оптимальная и удобная длина, подходит женщинам любого возраста и разной комплекции за счет своего свободного, прямого кроя. Порадует девушек наличием больших размеров и широким размерным рядом. Модный двубортный крой из плотной стеганой ткани подчеркнет достоинства вашей фигуры или скроет недостатки! Отлично смотрится на всех типах фигур. Размер необходимо подбирать по большему показателю - по объему бедер или объёму груди. Английский воротник можно застегнуть в зависимости от сезона и температуры воздуха. Съемная опушка из натурального меха украсит ваш look. Реверсивная молния визуально удлинит силуэт. С таким пальто вы можете создать множество красивых вариантов для разных случаев, дополняя их аксессуарами. Подходит для женщин невысоких, среднего роста и высоких предпочитающих полную свободу движений. Теплые карманы и длинные рукава защитят ваши руки от ветра. Станет вашим любимым изделием, с которым вы не захотите расставаться.</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Состав:  полиэстер; плащевка; мех песца; с подкладкой
+Цвет:  темно-серый меланж; черный
+Пол:  Женский
+Сезон:  Демисезон
+Вид застежки:  кнопки; молния
+Рост модели на фото:  170 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  92-72-100
+Размер на модели:  46
+Утеплитель:  термофин
+Плотность синтетического утеплителя:  150 г/кв.м
+Температурный режим:  от +5 °С до -20 °С
+Материал подкладки:  полиэстер
+Покрой:  свободный
+Тип карманов:  прорезные
+Тип рукава:  длинные
+Опции капюшона:  без капюшона
+Опции опушки:  съемная опушка
+Мех опушки/отделки:  мех песца
+Декоративные элементы:  меховой воротник
+Особенности модели:  комбинированное
+Уход за вещами:  химчистка; сухая химчистка
+Комплектация:  меховой воротник - 1 шт.; Пальто - 1 шт.
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>https://basket-10.wbbasket.ru/vol1398/part139851/139851686/images/big/1.webp, https://basket-10.wbbasket.ru/vol1398/part139851/139851686/images/big/2.webp, https://basket-10.wbbasket.ru/vol1398/part139851/139851686/images/big/3.webp, https://basket-10.wbbasket.ru/vol1398/part139851/139851686/images/big/4.webp, https://basket-10.wbbasket.ru/vol1398/part139851/139851686/images/big/5.webp, https://basket-10.wbbasket.ru/vol1398/part139851/139851686/images/big/6.webp, https://basket-10.wbbasket.ru/vol1398/part139851/139851686/images/big/7.webp, https://basket-10.wbbasket.ru/vol1398/part139851/139851686/images/big/8.webp, https://basket-10.wbbasket.ru/vol1398/part139851/139851686/images/big/9.webp, https://basket-10.wbbasket.ru/vol1398/part139851/139851686/images/big/10.webp, https://basket-10.wbbasket.ru/vol1398/part139851/139851686/images/big/11.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/9377731/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>9377731</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Полупальто бушлат на зиму из премиальной 100% шерсти</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>11477</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>BAZI FASHION GROUP</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/29914</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>50-176, 52-176, 52-182, 54-176, 54-182, 56-176, 56-182, 58-176, 60-176, 50-182, 58-182, 60-182, 52-188, 58-170, 58-188</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>1</v>
+      </c>
+      <c r="I60" t="n">
+        <v>15</v>
+      </c>
+      <c r="J60" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Это очень универсальное неформальное пальто, которое прекрасно гармонирует с большинством
+джинсов, чиносов, свитеров и кардиганов. Изделие получилось очень легким и при этом теплым.
+Мастера марки BAZIONI позаботились продумать мельчайшие детали начиная от пуговиц
+покрашенных под ткань, заканчивая подкладкой и других элементов. Все детали изделия,
+обработаны вручную по технологии, передаваемой из поколения в поколение. Это пальто из
+осенне-зимней коллекции одинаково хорошо рифмуется как с формальным костюмом, так и с
+вещами в стиле Smart Casual. Это пальто сделанное из шерсти исключительного качества, выделит
+Вас из толпы подчеркивая безупречный вкус. Пальто от Bazioni главный "Must Have" среди
+актуальных моделей верхней одежды. С приближением холодов рекомендуем присмотреть себе
+пальто классического кроя. Зимнее мужское пальто а так же наше удлинённое пальто от BAZIONI
+оптимальной длины ниже бедра - настоящий тренд сезона, выполненный из HI QALITY WOOL
+материала на основе натуральной шерсти. Благодаря премиальной итальянской шерсти от
+Lanificio De Ballis которая изготавливает в ручную 100% Премиальная шерсть покрашенная из
+натуральных природных красителей, ткань выглядит еще более красивой, не выцветет и не теряет
+форму, проста в уходе и почти не мнётся. В геноме бренда Bazioni можно уловить отголоски любви
+к природе и натуральным материалам, из которых с заботой сделаны все изделия, так как именно
+натуральные материалы органично и бережно окутывают жизнь человека на протяжении веков.
+Цветовая гамма построена на базовых оттенках черное мужское пальто, мужское длинное пальто
+на зиму что позволит войти в привычный гардероб делового мужчины. Компания BAZIONI является
+одним из лидеров в мужской модной одежде премиум сегменте, что подтверждает отзывы
+благодарных покупателей и почитателей марки. Компания рекомендует любителям посвободней
+брать на размер больше так как итальянские лекала подразумевают приталенность. Лучшее
+сочетание цены и качества на Валберес.</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Состав:  ПРЕМИАЛЬНАЯ ШЕРСТЬ 100% от Lanificio De Ballis
+Цвет:  синий; темно-синий
+Сезон:  демисезон
+Размер на модели:  52 пальто мужское черное синее классическое большой размер Тренч кардиган
+Рост модели на фото:  189 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  Классическое деловое мужское пальто из шерсти стильное на выход утепленное
+Утеплитель:  термофин пальто мужское теплое бежевое черное синее серое модное пуховик с мехом
+Материал подкладки:  вискоза пальто мужское зимнее оверсайз пальто мужское длинное кашемир шерсть
+Температурный режим:  Пальто на осень зиму весну всесезонная демисезонная теплое шерстяное зимнее
+Вид застежки:  Мужское пальто классическое теплое на пуговицы на молнии теплое элитная шерсть
+Воротник:  классический открытый воротник стойка и отложной с опушкой с мехом и без модный
+Опции капюшона:  Пальто мужское демисезонное с капюшоном и без длинное casual кашемир
+Опции опушки:  классическое мужское пальто с мехом без на зиму осень весну большие размеры
+Тип карманов:  прорезные молодежный трендовый повседневный теплый зимний осенний
+Особенности модели:  пальто мужское приталенное черное синие с капюшоном базиони итальянская шерсть
+Пол:  Мужской
+Уход за вещами:  деликатная химическая чистка, пальто мужское классическое шерстяное теплое
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>https://basket-01.wbbasket.ru/vol93/part9377/9377731/images/big/1.webp, https://basket-01.wbbasket.ru/vol93/part9377/9377731/images/big/2.webp, https://basket-01.wbbasket.ru/vol93/part9377/9377731/images/big/3.webp, https://basket-01.wbbasket.ru/vol93/part9377/9377731/images/big/4.webp, https://basket-01.wbbasket.ru/vol93/part9377/9377731/images/big/5.webp, https://basket-01.wbbasket.ru/vol93/part9377/9377731/images/big/6.webp, https://basket-01.wbbasket.ru/vol93/part9377/9377731/images/big/7.webp, https://basket-01.wbbasket.ru/vol93/part9377/9377731/images/big/8.webp, https://basket-01.wbbasket.ru/vol93/part9377/9377731/images/big/9.webp, https://basket-01.wbbasket.ru/vol93/part9377/9377731/images/big/10.webp, https://basket-01.wbbasket.ru/vol93/part9377/9377731/images/big/11.webp, https://basket-01.wbbasket.ru/vol93/part9377/9377731/images/big/12.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/48846999/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>48846999</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Пальто классическое из премиальной итальянской 100% шерсти</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>22598</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>BAZI FASHION GROUP</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/29914</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>46-176, 48-176, 50-176, 52-176, 54-176, 56-176, 58-176, 60-176, 62-176</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>1</v>
+      </c>
+      <c r="I61" t="n">
+        <v>12</v>
+      </c>
+      <c r="J61" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Это очень универсальное неформальное пальто, которое прекрасно гармонирует с большинством джинсов, чиносов, свитеров и кардиганов. Изделие получилось очень легким и при этом теплым. Мастера марки BAZIONI позаботились продумать мельчайшие детали начиная от пуговиц покрашенных под ткань, заканчивая подкладкой и других элементов . Все детали изделия, обработаны вручную по технологии, передаваемой из поколения в поколение. Это пальто из осенне-зимней коллекции одинаково хорошо рифмуется как с формальным костюмом, так и с вещами в стиле SMART CASUAL. Это пальто сделанное из шерсти исключительного качества, выделит Вас из толпы подчеркивая безупречный вкус.
+Пальто - главный "Must Have" среди актуальных моделей верхней одежды. С приближением холодов рекомендуем присмотреть себе пальто классического кроя . Зимнее мужское пальто а так же наше удлинённое пальто от  BAZIONI оптимальной длины ниже бедра - настоящий тренд сезона, выполненный из HI QALITY WOOL  материала на основе натуральной шерсти. Благодаря премиальной итальянской шерсти от LANIFICIO DE BALLIS,  ткань выглядит еще более красивой, не выцветет и не теряет форму, проста в уходе и почти не мнётся. Цветовая гамма построена на базовых оттенках, сером и коричневом, черное мужское пальто , мужское длинное пальто на зиму  ,что позволит этому мужскому  пальто легко войти в привычный гардероб делового мужчины. 
+Компания BAZIONI является одним из лидеров в мужской модной одежде, что подтверждает сотни тысяч продаж и благодарных покупателей.
+ЛУЧШЕЕ СОЧЕТАНИЕ ЦЕНЫ И КАЧЕСТВО НА ВАЛДБЕРЕС .
+Пальто утепленное полуприлегающего силуэта на 3 пуговицы. Воротник - английский с лацканами. На лацкане - декоративная петля. На передних половинках пальто - один верхний нагрудный карман и два нижних кармана с клапанами. По спинке - в среднем шве - шлица. Рукава в тачные, по низу рукавов - шлица на пуговицах.</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Состав:  ПРЕМИАЛЬНАЯ ШЕРСТЬ 100% от Lanificio De Ballis; дополнительную обработка NANO tec revolution
+Цвет:  темно-коричневый; коричневый; шоколадно-коричневый; коньячный; табачный
+Сезон:  зима
+Вид застежки:  Пальто мужское классическое удлиненное на пуговицах молнии модное зимнее приталенное
+Рост модели на фото:  185 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  Классическое деловое пальто из шерсти стильное на выход полупальто тренч
+Размер на модели:  50 52-54 54-56 58 пальто мужское длинное классическое большой размер Тренч кардиган
+Утеплитель:  термофин пальто мужское теплое зимнее бежевое черное синее модное пуховик осень
+Плотность синтетического утеплителя:  80 г/кв.м
+Температурный режим:  Пальто на осень зиму весну всесезонная демисезонная теплое зимнее утепленное
+Материал подкладки:  вискоза пальто мужское оверсайз пальто мужское длинное кашемир и шелк
+Покрой:  классическое мужское пальто зимнее осеннее стеганое полуприталенное синее черное италия
+Тип карманов:  молодежный трендовый повседневный теплый зимний осенний шерсть 100% темный
+Тип рукава:  длинные
+Опции капюшона:  Пальто мужское демисезонное с капюшоном и без длинное casual на зиму теплое
+Опции опушки:  отстегивается классическое пальто с мехом на зиму весну осень черное bazioni
+Декоративные элементы:  пальто мужское классическое шерстяное теплое на зиму демисезонное с капюшоном
+Особенности модели:  пальто зимнее мужское приталенное свободное черное серое базиони кэжуал
+Конструктивные элементы:  Пальто мужское утепленное с английским воротником из шерсти стильное
+Пол:  Мужской
+Уход за вещами:  деликатная химическая чистка пальто мужское классическое длинное пальто весна
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>https://basket-04.wbbasket.ru/vol488/part48846/48846999/images/big/1.webp, https://basket-04.wbbasket.ru/vol488/part48846/48846999/images/big/2.webp, https://basket-04.wbbasket.ru/vol488/part48846/48846999/images/big/3.webp, https://basket-04.wbbasket.ru/vol488/part48846/48846999/images/big/4.webp, https://basket-04.wbbasket.ru/vol488/part48846/48846999/images/big/5.webp, https://basket-04.wbbasket.ru/vol488/part48846/48846999/images/big/6.webp, https://basket-04.wbbasket.ru/vol488/part48846/48846999/images/big/7.webp, https://basket-04.wbbasket.ru/vol488/part48846/48846999/images/big/8.webp, https://basket-04.wbbasket.ru/vol488/part48846/48846999/images/big/9.webp, https://basket-04.wbbasket.ru/vol488/part48846/48846999/images/big/10.webp, https://basket-04.wbbasket.ru/vol488/part48846/48846999/images/big/11.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/643735651/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>643735651</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Женское полупальто</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>9141</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Rendez-Vous</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/528630</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>XS/S, M/L, XL/XXL</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>1</v>
+      </c>
+      <c r="I62" t="n">
+        <v>9</v>
+      </c>
+      <c r="J62" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Серый пиджак женский французского бренда Maison David. Состав: 80% шерсть натуральная, 20% полиэстер. Шерсть отлично согревает, при этом позволяет телу дышать, не создавая парникового эффекта. В шерстяных вещах тепло, но не жарко. Добавление полиэстера делает материал более прочным и устойчивым к износу. Вещи из смесовой шерсти — идеальный выбор для зимы и холодного демисезона.
+Пиджак имеет прямой силуэт. Модель отличает отложной воротник и наличие прорезных карманов. Пиджак в стиле кэжуал — удачное дополнение повседневного гардероба. Одежда в стиле кэжуал станет частью ваших комфортных образов на каждый день для работы и отдыха.
+Maison David — дом современной элегантности. Бренд отражает идею французского bon chic, bon genre: искусство быть безупречным без усилий, сочетая гармонию интеллекта и формы, а качество становится главным языком красоты. Бренд соединяет современные тенденции с классическими формами, сохраняя баланс между актуальностью и вечностью. Каждая вещь Maison David создается, чтобы жить долго — сопровождать своего владельца в реальной, настоящей жизни: в работе, в путешествиях, в личных историях. Это не просто гардероб, а состояние уравновешенности и эстетического покоя.</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>китай</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Состав:  шерсть натуральная 80%; полиэстер 20%
+Цвет:  темно-серый
+Сезон:  демисезон
+Рост модели на фото:  175 см
+Покрой:  прямой
+Воротник:  отложной
+Тип карманов:  прорезные
+Пол:  Женский
+Комплектация:  1 шт
+Страна производства:  Китай</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>https://basket-31.wbbasket.ru/vol6437/part643735/643735651/images/big/1.webp, https://basket-31.wbbasket.ru/vol6437/part643735/643735651/images/big/2.webp, https://basket-31.wbbasket.ru/vol6437/part643735/643735651/images/big/3.webp, https://basket-31.wbbasket.ru/vol6437/part643735/643735651/images/big/4.webp, https://basket-31.wbbasket.ru/vol6437/part643735/643735651/images/big/5.webp, https://basket-31.wbbasket.ru/vol6437/part643735/643735651/images/big/6.webp, https://basket-31.wbbasket.ru/vol6437/part643735/643735651/images/big/7.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/325389335/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>325389335</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Полупальто</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>4549</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Louren Wilton</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/46920</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>46, 48, 50, 52, 54, 56</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>2</v>
+      </c>
+      <c r="I63" t="n">
+        <v>1</v>
+      </c>
+      <c r="J63" t="n">
+        <v>3</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Идеальное однобортное демисезонное женское пальто в клетку. Элегантный прямой силуэт с поясом, прорезные карманы, в сочетании с классическим английским воротником создают утонченный силуэт. Выполнено из натуральных премиум тканей с высоким содержанием шерсти, при этом мягких и легких будут приятны и долговечны в носке. С такой вещью удобно строить базовый гардероб, поскольку длина и фасон легко сочетаются не только с платьями и юбками, но также с деловыми костюмами и джинсами, спортивными костюмами. Соответствует таблице размеров. Прекрасно подойдет в качестве подарка для сестры, мамы, бабушки. Данная модель позьзуется популярностью у молодых мам.Пальто женское демисезонное. Куртка женская.Куртка демисезонная.Пальто осеннее. Пальто шерстяное.Верхняя одежда.Пальто в клетку. Пальто кашемировое. Пальто драповое женское осеннее.</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Состав:  шерсть 60%; полиэстер 20%; Вискоза 20%
+Цвет:  синий
+Сезон:  демисезон
+Размер на модели:  46
+Рост модели на фото:  180 см
+Утеплитель:  Без утеплений для полных элегантная на лето осень
+Материал подкладки:  Вискоза - 100 %
+Температурный режим:  от +15 °C до -15 °C
+Вид застежки:  пуговицы,кнопки
+Воротник:  английский воротник
+Опции капюшона:  Без капюшона пальто демисезонное
+Тип карманов:  листочка без молнии
+Пол:  Женский
+Уход за вещами:  Деликатная химическая стирка
+Комплектация:  пояс - 1 шт
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>https://basket-19.wbbasket.ru/vol3253/part325389/325389335/images/big/1.webp, https://basket-19.wbbasket.ru/vol3253/part325389/325389335/images/big/2.webp, https://basket-19.wbbasket.ru/vol3253/part325389/325389335/images/big/3.webp, https://basket-19.wbbasket.ru/vol3253/part325389/325389335/images/big/4.webp, https://basket-19.wbbasket.ru/vol3253/part325389/325389335/images/big/5.webp, https://basket-19.wbbasket.ru/vol3253/part325389/325389335/images/big/6.webp, https://basket-19.wbbasket.ru/vol3253/part325389/325389335/images/big/7.webp, https://basket-19.wbbasket.ru/vol3253/part325389/325389335/images/big/8.webp, https://basket-19.wbbasket.ru/vol3253/part325389/325389335/images/big/9.webp, https://basket-19.wbbasket.ru/vol3253/part325389/325389335/images/big/10.webp, https://basket-19.wbbasket.ru/vol3253/part325389/325389335/images/big/11.webp, https://basket-19.wbbasket.ru/vol3253/part325389/325389335/images/big/12.webp, https://basket-19.wbbasket.ru/vol3253/part325389/325389335/images/big/13.webp, https://basket-19.wbbasket.ru/vol3253/part325389/325389335/images/big/14.webp, https://basket-19.wbbasket.ru/vol3253/part325389/325389335/images/big/15.webp, https://basket-19.wbbasket.ru/vol3253/part325389/325389335/images/big/16.webp, https://basket-19.wbbasket.ru/vol3253/part325389/325389335/images/big/17.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/643735675/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>643735675</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Женское полупальто</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>8807</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Rendez-Vous</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/528630</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>XS/S, M/L, XL/XXL</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>1</v>
+      </c>
+      <c r="I64" t="n">
+        <v>5</v>
+      </c>
+      <c r="J64" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Синий пиджак женский французского бренда Maison David. Состав: 80% шерсть натуральная, 20% полиэстер. Шерсть отлично согревает, при этом позволяет телу дышать, не создавая парникового эффекта. В шерстяных вещах тепло, но не жарко. Добавление полиэстера делает материал более прочным и устойчивым к износу. Вещи из смесовой шерсти — идеальный выбор для зимы и холодного демисезона.
+Пиджак имеет прямой силуэт. Модель отличает отложной воротник и наличие прорезных карманов. Пиджак в стиле кэжуал — удачное дополнение повседневного гардероба. Одежда в стиле кэжуал станет частью ваших комфортных образов на каждый день для работы и отдыха.
+Maison David — дом современной элегантности. Бренд отражает идею французского bon chic, bon genre: искусство быть безупречным без усилий, сочетая гармонию интеллекта и формы, а качество становится главным языком красоты. Бренд соединяет современные тенденции с классическими формами, сохраняя баланс между актуальностью и вечностью. Каждая вещь Maison David создается, чтобы жить долго — сопровождать своего владельца в реальной, настоящей жизни: в работе, в путешествиях, в личных историях. Это не просто гардероб, а состояние уравновешенности и эстетического покоя.</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>китай</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Состав:  шерсть натуральная 80%; полиэстер 20%
+Цвет:  синий
+Сезон:  демисезон
+Рост модели на фото:  175 см
+Покрой:  прямой
+Воротник:  отложной
+Тип карманов:  прорезные
+Пол:  Женский
+Комплектация:  1 шт
+Страна производства:  Китай</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>https://basket-31.wbbasket.ru/vol6437/part643735/643735675/images/big/1.webp, https://basket-31.wbbasket.ru/vol6437/part643735/643735675/images/big/2.webp, https://basket-31.wbbasket.ru/vol6437/part643735/643735675/images/big/3.webp, https://basket-31.wbbasket.ru/vol6437/part643735/643735675/images/big/4.webp, https://basket-31.wbbasket.ru/vol6437/part643735/643735675/images/big/5.webp, https://basket-31.wbbasket.ru/vol6437/part643735/643735675/images/big/6.webp, https://basket-31.wbbasket.ru/vol6437/part643735/643735675/images/big/7.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/514701248/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>514701248</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Пальто шерстяное классическое прямое базовое</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>15162</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Tom Tailor - официальный интернет-магазин</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/5472</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>XXL, XL, M, S, L, XXXL</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>9</v>
+      </c>
+      <c r="I65" t="n">
+        <v>4</v>
+      </c>
+      <c r="J65" t="n">
+        <v>5</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Это пальто TOM TAILOR станет незаменимым спутником в прохладную погоду, идеально подходя для офиса, школы или повседневных прогулок. Классический крой и базовый цвет делают его универсальным элементом гардероба, который легко впишется в любой стиль. Шерстяная ткань, состоящая на 22% из натуральной шерсти, подарит вам тепло и комфорт, а благодаря добавлению полиэстера и акрила пальто сохраняет свою форму и легко стирается при бережном режиме. Прямой покрой и длина до бедра создают элегантный силуэт, а отложной воротник придает модели классический вид.  Прорезные карманы удобны для хранения мелочей, а пуговичная застежка надежно защитит от ветра. Это пальто станет вашим верным другом в любой ситуации, подчеркивая ваш безупречный вкус и чувство стиля.</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>камбоджа</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Состав:  73 % полиэстер; 22 % шерсть; 2 % акрил; 2 % полиамид; 1 % вискоза
+Цвет:  синий
+Пол:  Мужской
+Сезон:  демисезон
+Вид застежки:  пуговицы
+Рост модели на фото:  188 см
+Размер на модели:  L
+Покрой:  прямой
+Тип карманов:  прорезные
+Тип рукава:  длинные
+Опции капюшона:  без капюшона
+Опции опушки:  без опушки
+Мех опушки/отделки:  без меха
+Декоративные элементы:  без элементов
+Особенности модели:  дышащий материал; сохраняет тепло
+Уход за вещами:  бережная стирка при 30 градусах
+Комплектация:  пальто
+Страна производства:  Камбоджа</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>https://basket-27.wbbasket.ru/vol5147/part514701/514701248/images/big/1.webp, https://basket-27.wbbasket.ru/vol5147/part514701/514701248/images/big/2.webp, https://basket-27.wbbasket.ru/vol5147/part514701/514701248/images/big/3.webp, https://basket-27.wbbasket.ru/vol5147/part514701/514701248/images/big/4.webp, https://basket-27.wbbasket.ru/vol5147/part514701/514701248/images/big/5.webp, https://basket-27.wbbasket.ru/vol5147/part514701/514701248/images/big/6.webp, https://basket-27.wbbasket.ru/vol5147/part514701/514701248/images/big/7.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/328086568/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>328086568</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Пальто весеннее оверсайз длинное</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>4622</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>mm brands</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/704745</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>S, M, L, XL</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>1</v>
+      </c>
+      <c r="I66" t="n">
+        <v>1</v>
+      </c>
+      <c r="J66" t="n">
+        <v>3</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Представляем вашему вниманию пальто - халат от бренда Dana Zana - идеальный выбор для демисезонного периода осень - весна. Этот предмет верхней одежды является воплощением стиля, комфорта и качества. Базовое пальто изготовлено из высококачественных материалов: 70% полиэстер, 30% шерсть. Такой состав обеспечивает тепло и комфорт в температурном режиме от -5°C до +10°C. Это стильное и модное пальто имеет классическую палитру цветов, которые легко сочетаюся с любым образом. Особенности модели - наличие отложного английского воротника и длинный крой, который создает оверсайз эффект. Прорезные карманы, рукава - длинные, что делает это пальто универсальным и практичным. Длина рукава от шва - 60 см. Покрой свободный, подчеркивающий стиль oversize и создающий модное и трендовое сочетание. Брендовое пальто отлично подойдет для любого типа фигуры - оно представлено в больших размерах, подойдет как для полных, так и для худых, а также для беременных девушек. Натуральные нити и премиум качество материалов делают его долговечным и изысканным предметом гардероба. Спинка со средним швом и отлетной шлицей добавляет утонченности и стиля этой модели. Длинное пальто уместно как для офисного официального стиля, так и для повседневного образа. Обладая классическим и современным видом, это пальто прекрасно сочетается с любой обувью и аксессуарами. Пальто нашего бренда создано для тех, кто ценит качество и стиль. Независимо от вашего роста ( высокий или невысокий) или типа фигуры ( худые или полные), это пальто подчеркнет ваш индивидуальный стиль и придаст образу элегантности и изысканности. Не упустите возможность добавить этот трендовый предмет в свой гардероб!</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>китай</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Состав:  полиэстер; шерсть
+Цвет:  черный
+Пол:  Женский
+Сезон:  Демисезон
+Вид застежки:  пуговицы
+Рост модели на фото:  170 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  90-68-95
+Размер на модели:  44-46
+Утеплитель:  без утеплителя
+Температурный режим:  от -5 °C до +10 °C
+Материал подкладки:  без подкладки
+Покрой:  прямой
+Тип карманов:  прорезные
+Тип рукава:  длинные
+Опции капюшона:  без капюшона
+Опции опушки:  без опушки
+Декоративные элементы:  пояс
+Особенности модели:  ветрозащита; немнущийся материал; с разрезом
+Уход за вещами:  гладить на низкой температуре; деликатный отжим; отбеливание запрещено
+Комплектация:  Пальто - 1 шт.
+Страна производства:  Китай</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>https://basket-20.wbbasket.ru/vol3280/part328086/328086568/images/big/1.webp, https://basket-20.wbbasket.ru/vol3280/part328086/328086568/images/big/2.webp, https://basket-20.wbbasket.ru/vol3280/part328086/328086568/images/big/3.webp, https://basket-20.wbbasket.ru/vol3280/part328086/328086568/images/big/4.webp, https://basket-20.wbbasket.ru/vol3280/part328086/328086568/images/big/5.webp, https://basket-20.wbbasket.ru/vol3280/part328086/328086568/images/big/6.webp, https://basket-20.wbbasket.ru/vol3280/part328086/328086568/images/big/7.webp, https://basket-20.wbbasket.ru/vol3280/part328086/328086568/images/big/8.webp, https://basket-20.wbbasket.ru/vol3280/part328086/328086568/images/big/9.webp, https://basket-20.wbbasket.ru/vol3280/part328086/328086568/images/big/10.webp, https://basket-20.wbbasket.ru/vol3280/part328086/328086568/images/big/11.webp, https://basket-20.wbbasket.ru/vol3280/part328086/328086568/images/big/12.webp, https://basket-20.wbbasket.ru/vol3280/part328086/328086568/images/big/13.webp, https://basket-20.wbbasket.ru/vol3280/part328086/328086568/images/big/14.webp, https://basket-20.wbbasket.ru/vol3280/part328086/328086568/images/big/15.webp, https://basket-20.wbbasket.ru/vol3280/part328086/328086568/images/big/16.webp, https://basket-20.wbbasket.ru/vol3280/part328086/328086568/images/big/17.webp, https://basket-20.wbbasket.ru/vol3280/part328086/328086568/images/big/18.webp, https://basket-20.wbbasket.ru/vol3280/part328086/328086568/images/big/19.webp, https://basket-20.wbbasket.ru/vol3280/part328086/328086568/images/big/20.webp, https://basket-20.wbbasket.ru/vol3280/part328086/328086568/images/big/21.webp, https://basket-20.wbbasket.ru/vol3280/part328086/328086568/images/big/22.webp, https://basket-20.wbbasket.ru/vol3280/part328086/328086568/images/big/23.webp, https://basket-20.wbbasket.ru/vol3280/part328086/328086568/images/big/24.webp, https://basket-20.wbbasket.ru/vol3280/part328086/328086568/images/big/25.webp, https://basket-20.wbbasket.ru/vol3280/part328086/328086568/images/big/26.webp, https://basket-20.wbbasket.ru/vol3280/part328086/328086568/images/big/27.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/537251833/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>537251833</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Пуховик с натуральным кашемиром и мехом рыжей лисы</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>47816</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>BLIZZARD QUEEN</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/696380</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>XS, S, М</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I67" t="n">
+        <v>352</v>
+      </c>
+      <c r="J67" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Элитный короткая зимняя куртка-пуховик из коллекции бренда BLIZZARD QUEEN - это роскошный выбор для девушек, которые не готовы жертвовать стилем ради тепла. Эффектная укороченная модель с длиной по спинке 73 см и натуральным мехом рыжей лисицы - настоящий must-have демисезона и зимы 2025-2026! Красивый оверсайз (oversize) силуэт, дизайнерский крой и материалы премиум класса делают эту модную повседневную вещь люксовым и трендовым акцентом гардероба.
+Ткань верха изделия изготовлена из натуральной пряжи из шерсти ангорской козы - кашемира, которая устойчива к снегу, влаге и ветру, а ее элегантный светлый цвет придает образу дорогой характер. Пушистый, объемный воротник добавляет изюминку в общий стиль, а практичность модели подчеркивается съемной опушкой, которая трансформируется в зависимости от погоды и настроения (можно носить утепленную модель весной и осенью при температурах от 0 до -5, -10, -15 и -20°C).
+Вещь имеет мягкий наполнитель (утеплитель) гусиный пух (95%) с показателем fill power 800+ - он невероятно легкий, как облачко, не комкуется и при этом выдерживает до минус 25 градусов, обеспечивая защиту от мороза. Пух-пакет обеспечивает равномерное распределение утеплителя по всему пуховому полушубку, предотвращая образование холодных зон. 
+Молния и кнопки выполнены из прочного металла, а вместительные карманы добавляют комфорта. Это классическое удлиненное меховое пальто подойдет и девочкам подросткам, и беременным, и взрослым дамам с большими размерами - фасон универсален и подходит для очень разных параметров фигуры.</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Состав:  натуральный мех; натуральный пух; шерсть; Кашемир
+Цвет:  молочный; кремовый; бежевый; топленое молоко
+Сезон:  Зима
+Размер на модели:  XS/Рос.размер 44-46
+Рост модели на фото:  167 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  90-67-90
+Утеплитель:  натуральный гусиный пух 95%
+Характеристика пух/перо (fill power):  800 куб. дюйм на унцию
+Температурный режим:  от +15 °C до -30 °C
+Материал подкладки:  полиэстер 100%
+Покрой:  свободный
+Вид застежки:  молния; кнопки
+Опции капюшона:  несъемный капюшон
+Опции опушки:  съемная опушка
+Мех опушки/отделки:  мех натуральной лисы
+Тип карманов:  прорезные
+Декоративные элементы:  натуральный мех лисы
+Особенности модели:  ветрозащита
+Пол:  Женский
+Уход за вещами:  Деликатная химическая чистка в щадящем режиме
+Комплектация:  Пуховик оверсайз прямой - 1 шт; Съемный мех натуральной лисы - 1 шт; Брендированная сумка - 1 шт; пломба - 1 шт
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>https://basket-28.wbbasket.ru/vol5372/part537251/537251833/images/big/1.webp, https://basket-28.wbbasket.ru/vol5372/part537251/537251833/images/big/2.webp, https://basket-28.wbbasket.ru/vol5372/part537251/537251833/images/big/3.webp, https://basket-28.wbbasket.ru/vol5372/part537251/537251833/images/big/4.webp, https://basket-28.wbbasket.ru/vol5372/part537251/537251833/images/big/5.webp, https://basket-28.wbbasket.ru/vol5372/part537251/537251833/images/big/6.webp, https://basket-28.wbbasket.ru/vol5372/part537251/537251833/images/big/7.webp, https://basket-28.wbbasket.ru/vol5372/part537251/537251833/images/big/8.webp, https://basket-28.wbbasket.ru/vol5372/part537251/537251833/images/big/9.webp, https://basket-28.wbbasket.ru/vol5372/part537251/537251833/images/big/10.webp, https://basket-28.wbbasket.ru/vol5372/part537251/537251833/images/big/11.webp, https://basket-28.wbbasket.ru/vol5372/part537251/537251833/images/big/12.webp, https://basket-28.wbbasket.ru/vol5372/part537251/537251833/images/big/13.webp, https://basket-28.wbbasket.ru/vol5372/part537251/537251833/images/big/14.webp, https://basket-28.wbbasket.ru/vol5372/part537251/537251833/images/big/15.webp, https://basket-28.wbbasket.ru/vol5372/part537251/537251833/images/big/16.webp, https://basket-28.wbbasket.ru/vol5372/part537251/537251833/images/big/17.webp, https://basket-28.wbbasket.ru/vol5372/part537251/537251833/images/big/18.webp, https://basket-28.wbbasket.ru/vol5372/part537251/537251833/images/big/19.webp, https://basket-28.wbbasket.ru/vol5372/part537251/537251833/images/big/20.webp, https://basket-28.wbbasket.ru/vol5372/part537251/537251833/images/big/21.webp, https://basket-28.wbbasket.ru/vol5372/part537251/537251833/images/big/22.webp, https://basket-28.wbbasket.ru/vol5372/part537251/537251833/images/big/23.webp, https://basket-28.wbbasket.ru/vol5372/part537251/537251833/images/big/24.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/192658237/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>192658237</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Пальто из премиальной итальянской 100% шерсти теплое твид</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>22702</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>BAZI FASHION GROUP</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/45521</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>48-176, 50-176, 52-176, 54-176, 56-176, 46-176, 60-176, 58-176</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>1</v>
+      </c>
+      <c r="I68" t="n">
+        <v>6</v>
+      </c>
+      <c r="J68" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Это очень универсальное неформальное пальто, которое прекрасно гармонирует с большинством
+джинсов, чиносов, свитеров и кардиганов. Изделие получилось очень легким и при этом теплым.
+Мастера марки BAZIONI позаботились продумать мельчайшие детали начиная от пуговиц
+покрашенных под ткань, заканчивая подкладкой и других элементов. Все детали изделия,
+обработаны вручную по технологии, передаваемой из поколения в поколение. Это пальто из
+осенне-зимней коллекции одинаково хорошо рифмуется как с формальным костюмом, так и с
+вещами в стиле Smart Casual. Это пальто сделанное из шерсти исключительного качества, выделит
+Вас из толпы подчеркивая безупречный вкус. Пальто от Bazioni главный "Must Have" среди
+актуальных моделей верхней одежды. С приближением холодов рекомендуем присмотреть себе
+пальто классического кроя. Зимнее мужское пальто а так же наше удлинённое пальто от BAZIONI
+оптимальной длины ниже бедра - настоящий тренд сезона, выполненный из HI QALITY WOOL
+материала на основе натуральной шерсти. Благодаря премиальной итальянской шерсти от
+Lanificio De Ballis которая изготавливает в ручную 100% Премиальная шерсть покрашенная из
+натуральных природных красителей, ткань выглядит еще более красивой, не выцветет и не теряет
+форму, проста в уходе и почти не мнётся. В геноме бренда Bazioni можно уловить отголоски любви
+к природе и натуральным материалам, из которых с заботой сделаны все изделия, так как именно
+натуральные материалы органично и бережно окутывают жизнь человека на протяжении веков.
+Цветовая гамма построена на базовых оттенках черное мужское пальто, мужское длинное пальто
+на зиму что позволит войти в привычный гардероб делового мужчины. Компания BAZIONI является
+одним из лидеров в мужской модной одежде премиум сегменте, что подтверждает отзывы
+благодарных покупателей и почитателей марки. Компания рекомендует любителям посвободней
+брать на размер больше так как итальянские лекала подразумевают приталенность. Лучшее
+сочетание цены и качества на Валберес.</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Состав:  ПРЕМИАЛЬНАЯ ШЕРСТЬ 100% от Lanificio De Ballis; дополнительную обработка NANO tec revolution
+Цвет:  синий; темно-синий джинсовый; темно-синий; синий космос; сине-морской
+Сезон:  зима
+Вид застежки:  пуговицы
+Рост модели на фото:  185 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  102-88-99
+Размер на модели:  52
+Утеплитель:  термофин
+Плотность синтетического утеплителя:  100 г/кв.м
+Температурный режим:  от -5°C до +15°С
+Материал подкладки:  вискоза; полиэстер
+Покрой:  приталенный
+Тип карманов:  с клапаном; прорезные
+Тип рукава:  длинные
+Опции капюшона:  без капюшона
+Опции опушки:  без опушки
+Декоративные элементы:  пальто мужское классическое шерстяное теплое на зиму демисезонное с капюшоном
+Особенности модели:  пальто зимнее мужское приталенное свободное черное серое базиони кэжуал
+Конструктивные элементы:  Пальто мужское утепленное с английским воротником из шерсти стильное
+Пол:  Мужской
+Уход за вещами:  деликатная химическая чистка
+Комплектация:  пальто; вешалка; пакет
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>https://basket-13.wbbasket.ru/vol1926/part192658/192658237/images/big/1.webp, https://basket-13.wbbasket.ru/vol1926/part192658/192658237/images/big/2.webp, https://basket-13.wbbasket.ru/vol1926/part192658/192658237/images/big/3.webp, https://basket-13.wbbasket.ru/vol1926/part192658/192658237/images/big/4.webp, https://basket-13.wbbasket.ru/vol1926/part192658/192658237/images/big/5.webp, https://basket-13.wbbasket.ru/vol1926/part192658/192658237/images/big/6.webp, https://basket-13.wbbasket.ru/vol1926/part192658/192658237/images/big/7.webp, https://basket-13.wbbasket.ru/vol1926/part192658/192658237/images/big/8.webp, https://basket-13.wbbasket.ru/vol1926/part192658/192658237/images/big/9.webp, https://basket-13.wbbasket.ru/vol1926/part192658/192658237/images/big/10.webp, https://basket-13.wbbasket.ru/vol1926/part192658/192658237/images/big/11.webp, https://basket-13.wbbasket.ru/vol1926/part192658/192658237/images/big/12.webp, https://basket-13.wbbasket.ru/vol1926/part192658/192658237/images/big/13.webp, https://basket-13.wbbasket.ru/vol1926/part192658/192658237/images/big/14.webp, https://basket-13.wbbasket.ru/vol1926/part192658/192658237/images/big/15.webp, https://basket-13.wbbasket.ru/vol1926/part192658/192658237/images/big/16.webp, https://basket-13.wbbasket.ru/vol1926/part192658/192658237/images/big/17.webp, https://basket-13.wbbasket.ru/vol1926/part192658/192658237/images/big/18.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/63363114/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>63363114</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Пальто демисезонное большие размеры</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>11270</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Primadonna</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/47927</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>48, 50, 52, 54, 58, 60</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>1</v>
+      </c>
+      <c r="I69" t="n">
+        <v>5</v>
+      </c>
+      <c r="J69" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Осеннее демисезонное, универсальное пальто - это идеальная верхняя одежда на каждый день недели. Стильное удлиненное пальто прекрасно подойдет для носки осень и весной. Это пальто трендовое, стильное, легкое ,модное, имеет застежку - пуговицы. Наше пальто прекрасно подойдет для полных девушек и беременных женщин. Так, что если вы ищете, что надеть в холодный сезон в этом пальто вам будет уютно независимо от времени года! Классическая модель, и мягкая ткань пальто идеально подходит для любого случая, как верхняя женская одежда.</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Состав:  шерсть; полиэстер; текстиль; ватин; натуральный мех; Мех; мех песца; песец
+Цвет:  коричневый
+Сезон:  демисезон
+Вид застежки:  пуговицы
+Утеплитель:  полиэстер
+Плотность синтетического утеплителя:  150 г/кв.м
+Температурный режим:  от -5 до +10
+Материал подкладки:  полиэстер
+Покрой:  прямой
+Тип карманов:  в шве
+Тип рукава:  длинные
+Опции капюшона:  без капюшона
+Опции опушки:  съемная опушка
+Мех опушки/отделки:  мех песца
+Декоративные элементы:  без элементов
+Особенности модели:  износостойкость
+Конструктивные элементы:  воротник
+Пол:  Женский
+Уход за вещами:  деликатная химическая чистка
+Комплектация:  пальто женское -1 шт
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>https://basket-04.wbbasket.ru/vol633/part63363/63363114/images/big/1.webp, https://basket-04.wbbasket.ru/vol633/part63363/63363114/images/big/2.webp, https://basket-04.wbbasket.ru/vol633/part63363/63363114/images/big/3.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/178186810/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>178186810</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Пальто Тедди шуба</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>1632</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>la petit mishu</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/148333</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>128, 134, 140, 146, 152</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>1</v>
+      </c>
+      <c r="I70" t="n">
+        <v>72</v>
+      </c>
+      <c r="J70" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Представляем вам пальто Тедди для девочки, которое станет настоящей находкой для зимнего сезона. Шуба изготовлена из натуральной, высококачественной шерсти, она не только обеспечит надежную защиту от холода, но и придаст вашему ребенку изысканный и стильный образ. Обладает непревзойденными теплосберегающими свойствами, поэтому никакой холод не проникнет внутрь, и ваша дочка всегда будет оставаться в тепле. В нашем магазине Вы сможете найти одежду для девочек подросткового возраста. Все изделия  изготовлены с использованием самых современных технологий и материалов, чтобы обеспечить тепло и комфорт в холодное время года. Купив пальто в нашем магазине, Вы получите натуральную, мягкую и теплую одежду, которая станет незаменимой в Вашем гардеробе на зиму и демисезон, это настоящий шедевр дизайна и стиля, который порадует как самого маленького модника, так и его родителей. Ваш бренд La petit Mishu.</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Состав:  шерсть; полиэстер
+Цвет:  розовый; карамельный; пудровый
+Сезон:  зима
+Вид застежки:  пуговицы
+Утеплитель:  натуральный мех
+Температурный режим:  от 0 °C до -15 °C
+Материал подкладки:  хлопок; хлопковый подклад
+Покрой:  прямой
+Тип карманов:  прорезные
+Тип рукава:  длинные
+Опции капюшона:  без капюшона
+Опции опушки:  без опушки
+Декоративные элементы:  пуговицы
+Особенности модели:  натуральные материалы; дышащий материал
+Конструктивные элементы:  карман
+Пол:  Девочки
+Уход за вещами:  химическая чистка
+Комплектация:  Пальто - 1 шт
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>https://basket-12.wbbasket.ru/vol1781/part178186/178186810/images/big/1.webp, https://basket-12.wbbasket.ru/vol1781/part178186/178186810/images/big/2.webp, https://basket-12.wbbasket.ru/vol1781/part178186/178186810/images/big/3.webp, https://basket-12.wbbasket.ru/vol1781/part178186/178186810/images/big/4.webp, https://basket-12.wbbasket.ru/vol1781/part178186/178186810/images/big/5.webp, https://basket-12.wbbasket.ru/vol1781/part178186/178186810/images/big/6.webp, https://basket-12.wbbasket.ru/vol1781/part178186/178186810/images/big/7.webp, https://basket-12.wbbasket.ru/vol1781/part178186/178186810/images/big/8.webp, https://basket-12.wbbasket.ru/vol1781/part178186/178186810/images/big/9.webp, https://basket-12.wbbasket.ru/vol1781/part178186/178186810/images/big/10.webp, https://basket-12.wbbasket.ru/vol1781/part178186/178186810/images/big/11.webp, https://basket-12.wbbasket.ru/vol1781/part178186/178186810/images/big/12.webp, https://basket-12.wbbasket.ru/vol1781/part178186/178186810/images/big/13.webp, https://basket-12.wbbasket.ru/vol1781/part178186/178186810/images/big/14.webp, https://basket-12.wbbasket.ru/vol1781/part178186/178186810/images/big/15.webp, https://basket-12.wbbasket.ru/vol1781/part178186/178186810/images/big/16.webp, https://basket-12.wbbasket.ru/vol1781/part178186/178186810/images/big/17.webp, https://basket-12.wbbasket.ru/vol1781/part178186/178186810/images/big/18.webp, https://basket-12.wbbasket.ru/vol1781/part178186/178186810/images/big/19.webp, https://basket-12.wbbasket.ru/vol1781/part178186/178186810/images/big/20.webp, https://basket-12.wbbasket.ru/vol1781/part178186/178186810/images/big/21.webp, https://basket-12.wbbasket.ru/vol1781/part178186/178186810/images/big/22.webp, https://basket-12.wbbasket.ru/vol1781/part178186/178186810/images/big/23.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/852791118/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>852791118</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Однобортное шерстяное пальто с воротником-стойкой</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>18461</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Taobai</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/250042517</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>M, L</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>10</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Куртка из искусственной шерсти с высоким воротником и пуговицами
+Эта стильная куртка из искусственной шерсти станет незаменимым акцентом вашего осенне-зимнего гардероба, сочетая в себе тепло, комфорт и современный дизайн. Изготовленная из плотного, приятного на ощупь материала с эффектом натуральной шерсти, она надежно защищает от холода и ветра, при этом не сковывая движений и обеспечивая ощущение уюта в течение всего дня.
+Ключевые особенности:
+Высокий воротник: Эффектный высокий воротник не только добавляет образу завершенности, но и надежно защищает шею от прохлады.
+Застежка: Асимметричная застежка на пуговицах создает динамичный силуэт и обеспечивает удобство в использовании.
+Крой: Свободный оверсайз-крой обеспечивает максимальный комфорт, позволяет носить под куртку теплые свитера и создает модный, непринужденный силуэт.
+Практичные детали: Длинные рукава с регулируемыми манжетами обеспечивают дополнительную защиту от холода, а просторные карманы позволяют удобно разместить мелкие предметы и согреть руки.
+Качественный искусственный материал хорошо держит форму, не линяет и не электризуется, сохраняя свой роскошный вид даже после многократной носки и бережной стирки, что делает куртку долговечной и практичной в использовании.
+Универсальность этой куртки позволяет создавать разнообразные образы: дополните ее джинсами и ботильонами для повседневных городских прогулок, с платьем и колготками для создания контрастного женственного лука или с спортивными штанами для расслабленного стиля. Благодаря лаконичному дизайну, она легко вписывается в любой стиль и становится незаменимым спутником в любую погоду.
+Сочетание тепла, комфортного материала и стильного дизайна делает эту куртку из искусственной шерсти идеальным выбором для современной женщины, которая ценит уют, стиль и универсальность в холодную пору года.</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>китай</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Цвет:  черный
+Сезон:  демисезон
+Размер на модели:  42
+Рост модели на фото:  165 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  83-60-86
+Температурный режим:  от +8 °C до-+18°C
+Материал подкладки:  полиэстер
+Покрой:  минималистичный
+Вид застежки:  пуговица
+Декоративные элементы:  Пуговица
+Особенности модели:  сохранять тепло
+Пол:  Женский
+Уход за вещами:  Изысканная химчистка
+Комплектация:  пальто- 1шт
+Страна производства:  Китай</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>https://basket-38.wbbasket.ru/vol8527/part852791/852791118/images/big/1.webp, https://basket-38.wbbasket.ru/vol8527/part852791/852791118/images/big/2.webp, https://basket-38.wbbasket.ru/vol8527/part852791/852791118/images/big/3.webp, https://basket-38.wbbasket.ru/vol8527/part852791/852791118/images/big/4.webp, https://basket-38.wbbasket.ru/vol8527/part852791/852791118/images/big/5.webp, https://basket-38.wbbasket.ru/vol8527/part852791/852791118/images/big/6.webp, https://basket-38.wbbasket.ru/vol8527/part852791/852791118/images/big/7.webp, https://basket-38.wbbasket.ru/vol8527/part852791/852791118/images/big/8.webp, https://basket-38.wbbasket.ru/vol8527/part852791/852791118/images/big/9.webp, https://basket-38.wbbasket.ru/vol8527/part852791/852791118/images/big/10.webp, https://basket-38.wbbasket.ru/vol8527/part852791/852791118/images/big/11.webp, https://basket-38.wbbasket.ru/vol8527/part852791/852791118/images/big/12.webp, https://basket-38.wbbasket.ru/vol8527/part852791/852791118/images/big/13.webp, https://basket-38.wbbasket.ru/vol8527/part852791/852791118/images/big/14.webp, https://basket-38.wbbasket.ru/vol8527/part852791/852791118/images/big/15.webp, https://basket-38.wbbasket.ru/vol8527/part852791/852791118/images/big/16.webp, https://basket-38.wbbasket.ru/vol8527/part852791/852791118/images/big/17.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/122402986/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>122402986</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Женское пальто</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>5849</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Milens</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/109326</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>40, 42, 44, 46, 48, 50</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>1</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Легкая и теплая однобортная шуба/пальто классического прямого силуэта из сложно обработанной смесовой нити высокой плотности, вплетенной в текстильную основу, для улучшения тепловых характеристик и увеличения срока службы верхней одежды синтетические волокна комбинируют с натуральной шерстью. Такой состав обеспечивает не только защиту от холода и ветра, но и достаточно высокие показатели прочности, износостойкости, несминаемости. Шубы из этого материала могут быть очень красивыми и стильными, яркими и загадочными, подходящими для самых взыскательных модниц. Качественный искусственный мех легко чистится, обладает устойчивым ворсом и приятным блеском, не имеет неприятного запаха. В такой шубе комфортно, она мягко прилегает к телу, красиво смотрится. Натуральный мех после окрашивания теряет свой лоск и привлекательность, становится менее мягким и нежным. Этот материал неприхотлив в уходе, легко очищается от загрязнений, не деформируется. В отличие от натурального, эко-мех практически не пропускает влагу, держит форму, не скатываться и почти не мнется. Данное изделие сможет подойти любому типу фигуры и способно сочетаться со многими стилями, для полных. Уютная плюшевая шубка отличается прочностью и долговечностью, свойства материала позволяют использовать верхнюю одежду до 10-15 лет подряд. К тому же, такие предметы гардероба не ест моль. Температурный режим от -10 до +5 С, по тепловым характеристикам может сравниться даже с классической дохой из норки. Чебурашки выбирают те девушки, которым нравится выделяться из толпы и демонстрировать окружающим собственную индивидуальность. Эта шуба очень комфортная и легкая, ее вес практически не ощущается в процессе носки, чего нельзя сказать о натуральной шубе, которая даже при самой хорошей выделке, весит несколько килограммов и носить ее не очень удобно. В этом сезоне огромной популярностью у девушек и женщин пользуются модели в стиле оверсайз.</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Состав:  шерсть 75%; эластан 5%; вискоза 20%
+Цвет:  синий
+Сезон:  демисезон
+Размер на модели:  42
+Утеплитель:  без утеплителя
+Материал подкладки:  полиэстер
+Температурный режим:  -5+10
+Вид застежки:  пуговицы
+Воротник:  классический
+Опции капюшона:  без капюшона
+Опции опушки:  без опушки
+Тип карманов:  накладные
+Особенности модели:  однобортная
+Пол:  Женский</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>https://basket-09.wbbasket.ru/vol1224/part122402/122402986/images/big/1.webp, https://basket-09.wbbasket.ru/vol1224/part122402/122402986/images/big/2.webp, https://basket-09.wbbasket.ru/vol1224/part122402/122402986/images/big/3.webp, https://basket-09.wbbasket.ru/vol1224/part122402/122402986/images/big/4.webp, https://basket-09.wbbasket.ru/vol1224/part122402/122402986/images/big/5.webp, https://basket-09.wbbasket.ru/vol1224/part122402/122402986/images/big/6.webp, https://basket-09.wbbasket.ru/vol1224/part122402/122402986/images/big/7.webp, https://basket-09.wbbasket.ru/vol1224/part122402/122402986/images/big/8.webp, https://basket-09.wbbasket.ru/vol1224/part122402/122402986/images/big/9.webp, https://basket-09.wbbasket.ru/vol1224/part122402/122402986/images/big/10.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/712938102/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>712938102</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Женское полупальто тедди</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>7884</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Rendez-Vous</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/528630</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>XS, S, M, L, XL, XXL</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>1</v>
+      </c>
+      <c r="I73" t="n">
+        <v>2</v>
+      </c>
+      <c r="J73" t="n">
+        <v>3</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Серое полупальто женское французского бренда Maison David. Состав: 42% акрил, 30% шерсть натуральная, 28% полиэстер. Материал «тедди» мягкий и приятный на ощупь, внешне он напоминает мех букле с густыми коротким ворсом. Акрил — современный материал, который часто называют «искусственной шерстью». Как и натуральная шерсть, акрил сохраняет тепло, он легкий и эластичный. Акрил прочнее шерсти, не садится и не деформируется. Вещи со смесовым составом из акрила и шерсти мягкие, теплые и прекрасно сохраняют внешний вид. Полиэстер делает состав еще прочнее и практичнее. Состав подкладки: полиэстер, вискоза.
+Верхняя одежда имеет свободный силуэт. Модель отличает отложной воротник и наличие прорезных карманов.
+Полупальто в стиле кэжуал — удачное дополнение повседневного гардероба. Одежда в стиле кэжуал станет частью ваших комфортных образов на каждый день для работы и отдыха. Maison David — дом современной элегантности. Бренд отражает идею французского bon chic, bon genre: искусство быть безупречным без усилий, сочетая гармонию интеллекта и формы, а качество становится главным языком красоты. Бренд соединяет современные тенденции с классическими формами, сохраняя баланс между актуальностью и вечностью. Каждая вещь Maison David создается, чтобы жить долго — сопровождать своего владельца в реальной, настоящей жизни: в работе, в путешествиях, в личных историях. Это не просто гардероб, а состояние уравновешенности и эстетического покоя.</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Состав:  Акрил 42%; шерсть натуральная 30%
+Цвет:  коричнево-серый
+Сезон:  демисезон
+Рост модели на фото:  175 см
+Покрой:  свободный
+Воротник:  отложной
+Тип карманов:  прорезные
+Особенности модели:  Без капюшона, теплый
+Пол:  Женский
+Комплектация:  1 шт
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>https://basket-34.wbbasket.ru/vol7129/part712938/712938102/images/big/1.webp, https://basket-34.wbbasket.ru/vol7129/part712938/712938102/images/big/2.webp, https://basket-34.wbbasket.ru/vol7129/part712938/712938102/images/big/3.webp, https://basket-34.wbbasket.ru/vol7129/part712938/712938102/images/big/4.webp, https://basket-34.wbbasket.ru/vol7129/part712938/712938102/images/big/5.webp, https://basket-34.wbbasket.ru/vol7129/part712938/712938102/images/big/6.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/531351268/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>531351268</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Длинное пальто на полсезона</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10190</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Outdoor backpack flagship store</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/4462193</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>S, M, L</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>20</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Идеальный женский жакет 2025 года - это двубортный жакет с прямыми штанинами от Max Mara, который можно носить как женский жакет на половину сезона или как женскую куртку на половину сезона. Куртки бренда созданы для ценителей комфорта и стиля. Простой, лаконичный стиль и отсутствие дополнительных украшений делают изделие универсальным. При необходимости из удобного ремня можно легко сделать хорошо сидящий пиджак. Красивая женская куртка очень подходит для ношения в переходный период года - межсезонье, осень и теплую зиму. Невероятно легкое, удобное и теплое пальто доставит особое удовольствие своей обладательнице.
+Изготовлен из мягких тканей, приятных на ощупь: вискозы, шерсти, полиэстера. Идеальное сочетание позволяет вашему телу дышать без неприятного напряжения и скованности. Есть просторные и удобные карманы, которые идеально подходят для прогулок. Модные женские куртки на полсезона, свободные и подходящие для взрослых женщин и девушек, как высокого, так и низкого роста.</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>китай</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Цвет:  латунь
+Сезон:  демисезон
+Вид застежки:  пуговица
+Рост модели на фото:  175 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  85-60-85
+Размер на модели:  44
+Утеплитель:  натуральная кожа
+Температурный режим:  от -5 до +10
+Материал подкладки:  натуральная кожа
+Покрой:  повседневное
+Тип рукава:  длинное
+Декоративные элементы:  ярлык
+Особенности модели:  ветроустойчивый; износостойкий; антивозрастной
+Пол:  Женский
+Уход за вещами:  Только сухая чистка
+Страна производства:  Китай</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>https://basket-28.wbbasket.ru/vol5313/part531351/531351268/images/big/1.webp, https://basket-28.wbbasket.ru/vol5313/part531351/531351268/images/big/2.webp, https://basket-28.wbbasket.ru/vol5313/part531351/531351268/images/big/3.webp, https://basket-28.wbbasket.ru/vol5313/part531351/531351268/images/big/4.webp, https://basket-28.wbbasket.ru/vol5313/part531351/531351268/images/big/5.webp, https://basket-28.wbbasket.ru/vol5313/part531351/531351268/images/big/6.webp, https://basket-28.wbbasket.ru/vol5313/part531351/531351268/images/big/7.webp, https://basket-28.wbbasket.ru/vol5313/part531351/531351268/images/big/8.webp, https://basket-28.wbbasket.ru/vol5313/part531351/531351268/images/big/9.webp, https://basket-28.wbbasket.ru/vol5313/part531351/531351268/images/big/10.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/531204994/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>531204994</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Длинное пальто на полсезона</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10863</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Outdoor backpack flagship store</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/4462193</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>S, M, L, XL</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>20</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Идеальный женский жакет 2025 года - это двубортный жакет с прямыми штанинами от Max Mara, который можно носить как женский жакет на половину сезона или как женскую куртку на половину сезона. Куртки бренда созданы для ценителей комфорта и стиля. Простой, лаконичный стиль и отсутствие дополнительных украшений делают изделие универсальным. При необходимости из удобного ремня можно легко сделать хорошо сидящий пиджак. Красивая женская куртка очень подходит для ношения в переходный период года - межсезонье, осень и теплую зиму. Невероятно легкое, удобное и теплое пальто доставит особое удовольствие своей обладательнице.
+Изготовлен из мягких тканей, приятных на ощупь: вискозы, шерсти, полиэстера. Идеальное сочетание позволяет вашему телу дышать без неприятного напряжения и скованности. Есть просторные и удобные карманы, которые идеально подходят для прогулок. Модные женские куртки на полсезона, свободные и подходящие для взрослых женщин и девушек, как высокого, так и низкого роста.</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>китай</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Цвет:  хаки
+Сезон:  демисезон
+Вид застежки:  пуговица
+Рост модели на фото:  175 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  85-60-85
+Размер на модели:  44
+Утеплитель:  натуральная кожа
+Температурный режим:  от -5 до +10
+Материал подкладки:  натуральная кожа
+Покрой:  повседневное
+Тип рукава:  длинное
+Опции капюшона:  без капюшона
+Декоративные элементы:  ярлык
+Особенности модели:  ветроустойчивый; износостойкий; антивозрастной
+Пол:  Женский
+Уход за вещами:  Только сухая чистка
+Страна производства:  Китай</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>https://basket-28.wbbasket.ru/vol5312/part531204/531204994/images/big/1.webp, https://basket-28.wbbasket.ru/vol5312/part531204/531204994/images/big/2.webp, https://basket-28.wbbasket.ru/vol5312/part531204/531204994/images/big/3.webp, https://basket-28.wbbasket.ru/vol5312/part531204/531204994/images/big/4.webp, https://basket-28.wbbasket.ru/vol5312/part531204/531204994/images/big/5.webp, https://basket-28.wbbasket.ru/vol5312/part531204/531204994/images/big/6.webp, https://basket-28.wbbasket.ru/vol5312/part531204/531204994/images/big/7.webp, https://basket-28.wbbasket.ru/vol5312/part531204/531204994/images/big/8.webp, https://basket-28.wbbasket.ru/vol5312/part531204/531204994/images/big/9.webp, https://basket-28.wbbasket.ru/vol5312/part531204/531204994/images/big/10.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/6383873/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>6383873</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Пальто</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>4930</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AFFORD LUX</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/10929</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>56, 54, 52, 50, 48, 46</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>1</v>
+      </c>
+      <c r="I76" t="n">
+        <v>32</v>
+      </c>
+      <c r="J76" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Теплый зимний пуховик из плащевой ткани на "шерстепоне" (50% верблюжья шерсть, 50% синтепон) надежно защищает от ветра и влаги в холодный период. Модель удлиненная, покрой прямой, талию подчеркивает пояс. Центральная застежка на молнию прикрыта ветрозащитной планкой на кнопках, капюшон обрамлен съемным натуральным мехом кролика. Дополняют изделие два кармана на молнии, два погружных кармана и внутренние манжеты.</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>китай</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Состав:  полиэстер 100%
+Цвет:  темно-серый
+Сезон:  зима
+Утеплитель:  синтепон
+Плотность синтетического утеплителя:  300 г/кв.м
+Материал подкладки:  полиэстер
+Страна производства:  Китай
+Вид застежки:  молния
+Особенности модели:  влагонепроницаемость
+Опции капюшона:  несъемный капюшон
+Длина изделия по спинке:  100 см
+Опции опушки:  съемная опушка
+Тип карманов:  прорезные
+Конструктивные элементы:  капюшон
+Пол:  Женский
+Тип рукава:  длинные
+Комплектация:  пальто
+Покрой:  прямой
+Уход за вещами:  бережная стирка при 30 градусах</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>https://basket-01.wbbasket.ru/vol63/part6383/6383873/images/big/1.webp, https://basket-01.wbbasket.ru/vol63/part6383/6383873/images/big/2.webp, https://basket-01.wbbasket.ru/vol63/part6383/6383873/images/big/3.webp, https://basket-01.wbbasket.ru/vol63/part6383/6383873/images/big/4.webp, https://basket-01.wbbasket.ru/vol63/part6383/6383873/images/big/5.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/309495131/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>309495131</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Пальто зимнее на верблюжьей шерсти</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>8985</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>MiLa</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/74454</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>50-52, 52-54, 56-58, 58-60</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>1</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Остатки этой модели! Пальто Lancon из верблюжьей шерсти – это идеальный выбор для холодной зимы. Модель с несъемным капюшоном и опушкой из натурального кролика обеспечит максимальный комфорт и защиту от мороза, а температура комфорта до -25°C позволит вам чувствовать себя уверенно даже в самые лютые холода. Пальто выполнено из высококачественной верблюжьей шерсти, которая отличается мягкостью, теплотой и износостойкостью. Внутренние манжеты и подкладка из полиэстера дополнительно защитят от ветра и холода. Модель с длинными рукавами и врезными карманами на молнии  практична и удобна для ежедневной носки.</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>китай</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Состав:  полиэстер; мех кролика; верблюжья шерсть
+Цвет:  синий
+Сезон:  зима
+Вид застежки:  молния
+Размер на модели:  50
+Утеплитель:  верблюжья шерсть
+Температурный режим:  до -25
+Материал подкладки:  полиэстер
+Покрой:  полуприлегающий
+Тип карманов:  врезные на молнии
+Тип рукава:  длинные
+Опции капюшона:  несъемный капюшон
+Опции опушки:  несъемная опушка
+Мех опушки/отделки:  мех кролика
+Декоративные элементы:  молния
+Особенности модели:  Мех кролика; внутренние манжеты
+Пол:  Женский
+Уход за вещами:  стирка при t не более 40°C
+Комплектация:  пальто
+Страна производства:  Китай</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>https://basket-19.wbbasket.ru/vol3094/part309495/309495131/images/big/1.webp, https://basket-19.wbbasket.ru/vol3094/part309495/309495131/images/big/2.webp, https://basket-19.wbbasket.ru/vol3094/part309495/309495131/images/big/3.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/329647655/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>329647655</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Пальто весеннее оверсайз длинное</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>3935</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Fuxuan</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/4019841</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>42, 44, 46, 48, 50</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" t="n">
+        <v>1</v>
+      </c>
+      <c r="J78" t="n">
+        <v>1</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Представляем вашему вниманию пальто - халат от бренда FuXuan - идеальный выбор для демисезонного периода осень - весна. Этот предмет верхней одежды является воплощением стиля, комфорта и качества. Базовое пальто изготовлено из высококачественных материалов: 18% шерсть и 82% полиэстер. Такой состав обеспечивает тепло и комфорт в температурном режиме от -5°C до +15°C. Подкладка из 100% полиэстера придает дополнительный уровень уюта и защиты от холода и ветра. Это стильное и модное пальто имеет классический черный цвет, который легко сочетается с любым образом. Особенности модели - наличие отложного английского воротника и длинный крой, который создает оверсайз эффект. Длина изделия макси, что делает его идеальным выбором как для повседневного ношения, так и для особых случаев, также по боковым швам на уровне талии обработаны шлевки Тип карманов - прорезные, рукава - длинные, что делает это пальто универсальным и практичным. Покрой свободный, подчеркивающий стиль oversize и создающий модное и трендовое сочетание. Брендовое пальто отлично подойдет для любого типа фигуры - оно представлено в больших размерах, подойдет как для полных, так и для худых, а также для беременных девушек. Натуральные нити и премиум качество материалов делают его долговечным и изысканным предметом гардероба. Спинка со средним швом и отлетной шлицей добавляет утонченности и стиля этой модели. Длинное пальто с поясом уместно как для офисного официального стиля, так и для повседневного образа. Обладая классическим и современным видом, это пальто прекрасно сочетается с любой обувью и аксессуарами. Пальто нашего бренда создано для тех, кто ценит качество и стиль. Независимо от вашего роста ( высокий или невысокий) или типа фигуры ( худые или полные), это пальто подчеркнет ваш индивидуальный стиль и придаст образу элегантности и изысканности. Не упустите возможность добавить этот трендовый предмет в свой гардероб!</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>китай</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Состав:  18% Шерсть 82% Полиэстер
+Цвет:  темно-серый
+Сезон:  демисезон
+Размер на модели:  44
+Рост модели на фото:  170 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  90-70-100
+Температурный режим:  -5°C до +15°C
+Материал подкладки:  100% полиэстер
+Покрой:  оверсайз
+Вид застежки:  пуговицы
+Тип рукава:  длинные
+Опции капюшона:  без капюшона
+Особенности модели:  ветрозащита
+Пол:  Женский
+Комплектация:  Пальто длинное - 1шт; пояс - 1шт
+Страна производства:  Китай</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>https://basket-20.wbbasket.ru/vol3296/part329647/329647655/images/big/1.webp, https://basket-20.wbbasket.ru/vol3296/part329647/329647655/images/big/2.webp, https://basket-20.wbbasket.ru/vol3296/part329647/329647655/images/big/3.webp, https://basket-20.wbbasket.ru/vol3296/part329647/329647655/images/big/4.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/267688653/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>267688653</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Пальто из шерсти и кашемира</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>50958</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Stella Guida</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/229333</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>36, 38, 40, 42, 44, 46</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>1</v>
+      </c>
+      <c r="I79" t="n">
+        <v>1</v>
+      </c>
+      <c r="J79" t="n">
+        <v>1</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Пальто удобного кроя из высококачественной смеси шерсти и кашемира с элегантной двусторонней отделкой. 
+Пальто без воротника имеет планку на пуговицах, два кармана-лока с клапанами и два боковых кармана с клапанами.
+Размер и посадка: На размер меньше, рекомендуем заказывать на размер больше.</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>германия</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Состав:  85 % натуральная шерсть, 10 % полиамид, 5 % кашемир
+Цвет:  серо-голубой
+Сезон:  демисезон
+Вид застежки:  пуговицы
+Рост модели на фото:  178 см
+Размер на модели:  38
+Утеплитель:  без утеплителя
+Температурный режим:  +15-0
+Материал подкладки:  56 % вискоза, 44 % полиэстер
+Тип карманов:  накладные; С клапанами
+Пол:  Женский
+Уход за вещами:  химчистка
+Комплектация:  Пальто 1 шт,Чехол 1 шт,Вешалка 1 шт,Коробка 1 шт
+Страна производства:  Германия</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>https://basket-17.wbbasket.ru/vol2676/part267688/267688653/images/big/1.webp, https://basket-17.wbbasket.ru/vol2676/part267688/267688653/images/big/2.webp, https://basket-17.wbbasket.ru/vol2676/part267688/267688653/images/big/3.webp, https://basket-17.wbbasket.ru/vol2676/part267688/267688653/images/big/4.webp, https://basket-17.wbbasket.ru/vol2676/part267688/267688653/images/big/5.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/187507743/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>187507743</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Пальто осеннее детское</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>3317</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>ПОЛЮС-КЛУБ</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/25723</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>128, 134, 140, 146, 152</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>1</v>
+      </c>
+      <c r="I80" t="n">
+        <v>2</v>
+      </c>
+      <c r="J80" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Пальто  демисезонное "Наташа" для девочек. Демисезонное драповое тонкое полупальто из нежного кашемира для девочки подростка школьного возраста, для невысокой стройной девушки, позволяет применять его как в повседневной носке в гимназию или колледж, на тренировку, так и на выход с друзьями или в гости. Подростковое средней длины свободного оверсайз кроя, так полюбившегося юным красавицам, с воротником, втачным рукавом и удобными вместительными карманами. Его можно носить со школьной формой на учебу или на прогулку. Легкое, но теплое  пальто-пиджак в широчайшей палитре расцветок от лирично пастельных до насыщенно сочных, на четырех декоративных пуговицах позволит начинающим модницам смело создавать различные образы в разных стилях. Высококачественная подкладочная ткань из гладкого прочного полиэстера, полностью дублированный специальным укрепляющим тканным полотном верх обеспечивают удобство надевания и долговечность изделия. Такая верхняя одежда не сминается, не образует заметный пиллинг и надежно защищает в ненастье. Полушерстяной жакет прекрасный вариант для прохладных осенних и весенних дней от +5 до +15. Для более низких температур воздуха и ветреной дождливой погоды выбирайте утепленную верхнюю одежду для детей и подростков. Ваш ребенок всегда будет чувствовать себя нарядно и комфортно!  Пальтишко отлично подайдет для полненьких модниц модельного типа украшено яркими аксессуарами. В составе натуральные материалы кашемир, шерсть и хлопок, а подклад из полиэстера. Пальто детское мягкое, бархатистое, очень приятное на ощупь. Наше пальто драповое можно стирать в машинке, при 30 градусах, с пальто ничего не произойдет, не деформируется, не сядет, специально в химчистки относить не нужно, мы продумали все детали для того чтобы вам было удобно ухаживать за вещами, а вашим детям тепло и комфортно в наших пальто. Российское производство, стильная модель, сертифицированная ткань - все это характеризует наши кашемировое пальто " Наташа " Приятных Вам покупок.</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Состав:  Кашемир; шерсть; хлопок; полиэстер
+Цвет:  бежевый
+Сезон:  демисезон
+Вид застежки:  пуговицы
+Рост модели на фото:  140 см
+Размер на модели:  146
+Температурный режим:  от +5 °C до +15 °C
+Материал подкладки:  полиэстер
+Опции капюшона:  без капюшона
+Опции опушки:  без опушки
+Особенности модели:  для полненьких
+Пол:  Девочки
+Уход за вещами:  стирка при t не более 30°C
+Комплектация:  Пальто кашемировое 1 шт
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>https://basket-12.wbbasket.ru/vol1875/part187507/187507743/images/big/1.webp, https://basket-12.wbbasket.ru/vol1875/part187507/187507743/images/big/2.webp, https://basket-12.wbbasket.ru/vol1875/part187507/187507743/images/big/3.webp, https://basket-12.wbbasket.ru/vol1875/part187507/187507743/images/big/4.webp, https://basket-12.wbbasket.ru/vol1875/part187507/187507743/images/big/5.webp, https://basket-12.wbbasket.ru/vol1875/part187507/187507743/images/big/6.webp, https://basket-12.wbbasket.ru/vol1875/part187507/187507743/images/big/7.webp, https://basket-12.wbbasket.ru/vol1875/part187507/187507743/images/big/8.webp, https://basket-12.wbbasket.ru/vol1875/part187507/187507743/images/big/9.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/14754397/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>14754397</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Пуховое пальто с натуральным мехом</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10826</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>WOWMYKID</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/78101</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>122, 128, 134, 140, 146, 152, 158, 164</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>2</v>
+      </c>
+      <c r="I81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J81" t="n">
+        <v>2</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Пуховое пальто. Модель декорирована вставками из искусственной замши и пальтового драпа. Внутренний воротник выполнен из вельвета, что обеспечивает дополнительный комфорт при носке. Подкладка - из хлопковой фланели и политаффеты. Капюшон и мех - съемные. Есть внутренняя кулиса по талии. Рукав - с ветрозащитной манжетой. Металлические молнии модного оттенка состаренной меди служат отличным "ювелирным" акцентом.</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>китай</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Цвет:  темно-серый
+Сезон:  зима
+Утеплитель:  пух
+Температурный режим:  от -15 °C до -25 °C
+Страна производства:  Китай
+Вид застежки:  молния
+Пол:  Детский
+Комплектация:  пуховик</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>https://basket-02.wbbasket.ru/vol147/part14754/14754397/images/big/1.webp, https://basket-02.wbbasket.ru/vol147/part14754/14754397/images/big/2.webp, https://basket-02.wbbasket.ru/vol147/part14754/14754397/images/big/3.webp, https://basket-02.wbbasket.ru/vol147/part14754/14754397/images/big/4.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/255920255/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>255920255</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Укороченное пальто тедди оверсайз</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>6855</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Rendez-Vous</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/528630</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>XS, S, M, L, XL</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>1</v>
+      </c>
+      <c r="I82" t="n">
+        <v>1</v>
+      </c>
+      <c r="J82" t="n">
+        <v>2</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Бежевое полупальто женское французского бренда Maison David. Состав: 50% акрил, 32% полиэстер, 18% шерсть натуральная. Материал «тедди» мягкий и приятный на ощупь, внешне он напоминает мех букле с густыми коротким ворсом. Акрил — современный материал, который часто называют «искусственной шерстью». Как и натуральная шерсть, акрил сохраняет тепло, он легкий и эластичный. Акрил прочнее шерсти, не садится и не деформируется. Вещи со смесовым составом из акрила и шерсти мягкие, теплые и прекрасно сохраняют внешний вид. Полиэстер делает состав еще прочнее и практичнее. Состав подкладки: полиэстер, вискоза.
+Верхняя одежда имеет силуэт оверсайз. Модель отличает отложной воротник и наличие прорезных карманов. Температурный режим от плюс 5 до минус 10.
+Ухаживайте за вещью правильно, чтобы она дольше служила и радовала вас. Правила по уходу указаны на вшивном ярлычке изделия. Разрешено: химчистка. Запрещено: стирка, отбеливание, глажка, барабанная сушка.
+Полупальто в деловом стиле — удачное решение для офисного гардероба. Это сдержанная элегантность, уверенность и профессионализм. Maison David — дом современной элегантности. Бренд отражает идею французского bon chic, bon genre: искусство быть безупречным без усилий, сочетая гармонию интеллекта и формы, а качество становится главным языком красоты. Бренд соединяет современные тенденции с классическими формами, сохраняя баланс между актуальностью и вечностью. Каждая вещь Maison David создается, чтобы жить долго — сопровождать своего владельца в реальной, настоящей жизни: в работе, в путешествиях, в личных историях. Это не просто гардероб, а состояние уравновешенности и эстетического покоя.</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Состав:  акрил 50%; полиэстер 32%
+Пол:  Женский
+Сезон:  демисезон
+Рост модели на фото:  175 см
+Температурный режим:  от +5 °C до -10 °C
+Покрой:  оверсайз
+Тип карманов:  прорезные
+Особенности модели:  Без капюшона, теплый
+Уход за вещами:  Химическая стирка; стирка запрещена; отбеливание запрещено
+Комплектация:  1 шт
+Страна производства:  Россия</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>https://basket-16.wbbasket.ru/vol2559/part255920/255920255/images/big/1.webp, https://basket-16.wbbasket.ru/vol2559/part255920/255920255/images/big/2.webp, https://basket-16.wbbasket.ru/vol2559/part255920/255920255/images/big/3.webp, https://basket-16.wbbasket.ru/vol2559/part255920/255920255/images/big/4.webp, https://basket-16.wbbasket.ru/vol2559/part255920/255920255/images/big/5.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/726643378/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>726643378</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Осенняя и зимняя верхняя одежда - Caramel</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>25510</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Цинцин товарный магазин</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/250040757</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>S, M</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>9</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Осенне-зимняя новинка: куртка «Дикое очарование» из Барна. Искусно изготовлена из шерстяной замши и натурального меха, обладает мягкой и плотной текстурой, отличными теплоизоляционными свойствами. Дизайн объединяет естественный стиль дикой природы с четким кроем и выразительным силуэтом, сочетая чувство моды и практичность. Усиленная внутренняя структура адаптирована для холодного сезона, сохраняя как тепло, так и элегантность. Классическая цветовая палитра «мела» — сдержанная и теплая, легко поднимает качество всего образа. Подходит для различных ситуаций: повседневные поездки на работу, отдых и прогулки. Практичная верхняя одежда для осенне-зимнего гардероба, сочетающая функциональность и эстетическую ценность.</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>https://basket-34.wbbasket.ru/vol7266/part726643/726643378/images/big/1.webp, https://basket-34.wbbasket.ru/vol7266/part726643/726643378/images/big/2.webp, https://basket-34.wbbasket.ru/vol7266/part726643/726643378/images/big/3.webp, https://basket-34.wbbasket.ru/vol7266/part726643/726643378/images/big/4.webp, https://basket-34.wbbasket.ru/vol7266/part726643/726643378/images/big/5.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/528485096/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>528485096</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Пальто</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>7338</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Магазин брендовых товаров со скидкой</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/250033656</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>S, M, L</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>43</v>
+      </c>
+      <c r="I84" t="n">
+        <v>1</v>
+      </c>
+      <c r="J84" t="n">
+        <v>1</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Пальто женское в стиле Английского джентельмена: Элегантное Пальто зимнее женское на 2025 Осень-Зима
+Описание товара 
+Представляем вам must-have сезона — классическое двубортное Пальто женское в британском стиле. Эта модель идеально сочетает в себе неподвластный времени дизайн, исключительное тепло и универсальность, являясь идеальным выбором для холодных месяцев.
+Премиальное качество и тепло: Наша уникальная смесовая ткань (50% Шерсть, 30% Полиэстер, 20% Нейлон) обеспечивает максимальное тепло и долговечность. Шерсть дарит исключительную терморегуляцию, а современные материалы добавляют прочность, устойчивость к ветру и влаге, делая это Пальто зимнее женское вашим надежным спутником в любую погоду.
+Вечная классика Англии: Утонченный пиджачный воротник и характерные двубортные пуговицы создают неизменно актуальный силуэт, полный величия и стиля. Удлиненный крой и свободный фасон (oversized) подчеркивают вашу индивидуальность, позволяя с комфортом носить объемные свитера underneath. Классическая полоска или клетка добавляют образу аристократичный шарм.
+Универсальность на все сезоны: Это не просто Пальто зимнее женское, но и идеальное Пальто женское весна-осень. Благодаря сбалансированному утеплению, оно комфортно для носки в промозглую осень, морозную зиму и прохладную весну. Его элегантность уместна как в офисе, так и на вечерней прогулке.
+Характеристики :
+Модель: Пальто женское двубортное, длинное
+Состав: 50% Шерсть, 30% Полиэстер, 20% Нейлон
+Утепление: Среднее (идеально для межсезонья и зимы)
+Покрой: Свободный (Oversized)
+Воротник: Пиджачный
+Застежка: Двубортная, на пуговицах
+Узор: Классическая клетка / полоска (в зависимости от варианта)</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Цвет:  коричневый
+Сезон:  зима
+Вид застежки:  Пояс
+Утеплитель:  натуральная кожа
+Температурный режим:  -15° до 20°
+Материал подкладки:  полиэстер
+Покрой:  повседневное
+Пол:  Женский</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>https://basket-28.wbbasket.ru/vol5284/part528485/528485096/images/big/1.webp, https://basket-28.wbbasket.ru/vol5284/part528485/528485096/images/big/2.webp, https://basket-28.wbbasket.ru/vol5284/part528485/528485096/images/big/3.webp, https://basket-28.wbbasket.ru/vol5284/part528485/528485096/images/big/4.webp, https://basket-28.wbbasket.ru/vol5284/part528485/528485096/images/big/5.webp, https://basket-28.wbbasket.ru/vol5284/part528485/528485096/images/big/6.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/531342582/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>531342582</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Длинное пальто на полсезона</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>9937</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Outdoor backpack flagship store</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/4462193</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>S, M, L, XL, 2XL</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>20</v>
+      </c>
+      <c r="I85" t="n">
+        <v>1</v>
+      </c>
+      <c r="J85" t="n">
+        <v>1</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Идеальный женский жакет 2025 года - это двубортный жакет с прямыми штанинами от Max Mara, который можно носить как женский жакет на половину сезона или как женскую куртку на половину сезона. Куртки бренда созданы для ценителей комфорта и стиля. Простой, лаконичный стиль и отсутствие дополнительных украшений делают изделие универсальным. При необходимости из удобного ремня можно легко сделать хорошо сидящий пиджак. Красивая женская куртка очень подходит для ношения в переходный период года - межсезонье, осень и теплую зиму. Невероятно легкое, удобное и теплое пальто доставит особое удовольствие своей обладательнице.
+Изготовлен из мягких тканей, приятных на ощупь: вискозы, шерсти, полиэстера. Идеальное сочетание позволяет вашему телу дышать без неприятного напряжения и скованности. Есть просторные и удобные карманы, которые идеально подходят для прогулок. Модные женские куртки на полсезона, свободные и подходящие для взрослых женщин и девушек, как высокого, так и низкого роста.</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>китай</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>Цвет:  рыжий
+Сезон:  демисезон
+Вид застежки:  пуговица
+Рост модели на фото:  175 см
+Параметры модели на фото (ОГ-ОТ-ОБ):  85-60-85
+Размер на модели:  44
+Утеплитель:  натуральная кожа
+Температурный режим:  от -5 до +10
+Материал подкладки:  натуральная кожа
+Покрой:  повседневное
+Тип рукава:  длинное
+Декоративные элементы:  ярлык
+Особенности модели:  ветроустойчивый; износостойкий; антивозрастной
+Пол:  Женский
+Уход за вещами:  Только сухая чистка
+Страна производства:  Китай</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>https://basket-28.wbbasket.ru/vol5313/part531342/531342582/images/big/1.webp, https://basket-28.wbbasket.ru/vol5313/part531342/531342582/images/big/2.webp, https://basket-28.wbbasket.ru/vol5313/part531342/531342582/images/big/3.webp, https://basket-28.wbbasket.ru/vol5313/part531342/531342582/images/big/4.webp, https://basket-28.wbbasket.ru/vol5313/part531342/531342582/images/big/5.webp, https://basket-28.wbbasket.ru/vol5313/part531342/531342582/images/big/6.webp, https://basket-28.wbbasket.ru/vol5313/part531342/531342582/images/big/7.webp, https://basket-28.wbbasket.ru/vol5313/part531342/531342582/images/big/8.webp, https://basket-28.wbbasket.ru/vol5313/part531342/531342582/images/big/9.webp, https://basket-28.wbbasket.ru/vol5313/part531342/531342582/images/big/10.webp, https://basket-28.wbbasket.ru/vol5313/part531342/531342582/images/big/11.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/583393444/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>583393444</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Пальто，Верх из овчины стеганая куртка</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10557</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>广州瑾岑商贸有限公司</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/250022985</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>L/45-55KG, XL/55-62.5KG, 2XL/62.5-70KG, 3XL/70-80Kg, 4XL/80-90Kg, 5XL/90-100Kg</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>43</v>
+      </c>
+      <c r="I86" t="n">
+        <v>1</v>
+      </c>
+      <c r="J86" t="n">
+        <v>3</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Мужской утепленный костюм со съемной подкладкой из норкового плюша выше колена рассчитан на то, чтобы выдерживать экстремально низкие температуры -30℃.Когда роскошь шерсти американской норки была объединена с ветрозащитной курткой военного образца, эта теплоизоляционная куртка изменила стандарт защиты от зимних холодов.Подборка высококачественного меха американской норки, богатый бархатистый низ, тонкий бархат, натуральный яркий блеск.Подкладка из искусственного меха золотистой норки обеспечивает отличную теплоизоляцию, а плотность шерсти в 3 раза выше, чем у обычных тканей. Это позволяет эффективно поддерживать температуру тела на уровне -30°C и выдерживать сильные морозы. Он изготовлен из композитной ткани на 83% из нейлона + 17% из спандекса, которая обладает отличными ветрозащитными и водонепроницаемыми свойствами.Модель длиной выше колена обеспечивает защиту всего тела, эффективно защищая его от холодного ветра, проникающего под подол, и по-настоящему "защищает от дождя и солнечного света".- Чтобы легко справляться с различными погодными условиями.Рукава с меховой отделкой: сохраняют тепло во всех направлениях, и ваши руки больше не мерзнут; длина до колен: эффективно защищает бедра и колени от холодного воздуха; интегрированная структура меха: как внутри, так и снаружи, двойная теплоотдача; уровень морозостойкости: сохраняет тепло в экстремально холодных условиях при температуре -30 ℃; ветрозащитный характеристики: ткань военного класса, не боится ветреной погоды; воздухопроницаемость: сохраняет тепло, обеспечивает умеренную вентиляцию и предотвращает удушающую жару."Поскольку существует множество накопителей тепла и отопительных приборов, холод больше не представляет угрозы.Этот костюм от Parker - не только зимний костюм, но и ваш верный помощник в борьбе с холодом.Каждое изделие изготовлено из отборной американской норки и предназначено для обеспечения максимального тепла.</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>вьетнам</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Состав:  95% шерсть, 5% полиэстер
+Цвет:  темно-бурый
+Сезон:  зима
+Вид застежки:  Пуговицы, молнии
+Утеплитель:  шерстяной
+Температурный режим:  -30
+Материал подкладки:  шерстяной
+Покрой:  Мода повседневная, деловая
+Тип карманов:  косой карман
+Тип рукава:  длинные рукава
+Мех опушки/отделки:  меховой воротник
+Декоративные элементы:  Меховой воротник, застежка-молния
+Пол:  Мужской
+Комплектация:  Шерстяной топ
+Страна производства:  Вьетнам</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>https://basket-30.wbbasket.ru/vol5833/part583393/583393444/images/big/1.webp, https://basket-30.wbbasket.ru/vol5833/part583393/583393444/images/big/2.webp, https://basket-30.wbbasket.ru/vol5833/part583393/583393444/images/big/3.webp, https://basket-30.wbbasket.ru/vol5833/part583393/583393444/images/big/4.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/746418024/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>746418024</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Пальто，Верх из овчины стеганая куртка</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>20873</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Торговая Площадка Восток</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/250081381</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>L/45-55KG, XL/55-62.5KG, 2XL/62.5-70KG, 3XL/70-80Kg, 4XL/80-90Kg, 5XL/90-100Kg</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>10</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Мужской утепленный костюм со съемной подкладкой из норкового плюша выше колена рассчитан на то, чтобы выдерживать экстремально низкие температуры -30℃.Когда роскошь шерсти американской норки была объединена с ветрозащитной курткой военного образца, эта теплоизоляционная куртка изменила стандарт защиты от зимних холодов.Подборка высококачественного меха американской норки, богатый бархатистый низ, тонкий бархат, натуральный яркий блеск.Подкладка из искусственного меха золотистой норки обеспечивает отличную теплоизоляцию, а плотность шерсти в 3 раза выше, чем у обычных тканей. Это позволяет эффективно поддерживать температуру тела на уровне -30°C и выдерживать сильные морозы. Он изготовлен из композитной ткани на 83% из нейлона + 17% из спандекса, которая обладает отличными ветрозащитными и водонепроницаемыми свойствами.Модель длиной выше колена обеспечивает защиту всего тела, эффективно защищая его от холодного ветра, проникающего под подол, и по-настоящему "защищает от дождя и солнечного света".- Чтобы легко справляться с различными погодными условиями.Рукава с меховой отделкой: сохраняют тепло во всех направлениях, и ваши руки больше не мерзнут; длина до колен: эффективно защищает бедра и колени от холодного воздуха; интегрированная структура меха: как внутри, так и снаружи, двойная теплоотдача; уровень морозостойкости: сохраняет тепло в экстремально холодных условиях при температуре -30 ℃; ветрозащитный характеристики: ткань военного класса, не боится ветреной погоды; воздухопроницаемость: сохраняет тепло, обеспечивает умеренную вентиляцию и предотвращает удушающую жару."Поскольку существует множество накопителей тепла и отопительных приборов, холод больше не представляет угрозы.Этот костюм от Parker - не только зимний костюм, но и ваш верный помощник в борьбе с холодом.Каждое изделие изготовлено из отборной американской норки и предназначено для обеспечения максимального тепла.</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>вьетнам</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Состав:  95% шерсть, 5% полиэстер
+Цвет:  глубокий черный
+Сезон:  зима
+Вид застежки:  Пуговицы, молнии
+Утеплитель:  шерстяной
+Температурный режим:  -30
+Материал подкладки:  шерстяной
+Покрой:  Мода повседневная, деловая
+Тип карманов:  Косой карман
+Тип рукава:  длинные рукава
+Декоративные элементы:  Меховой воротник, застежка-молния
+Пол:  Мужской
+Комплектация:  Шерстяной топ
+Страна производства:  Вьетнам</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>https://basket-35.wbbasket.ru/vol7464/part746418/746418024/images/big/1.webp, https://basket-35.wbbasket.ru/vol7464/part746418/746418024/images/big/2.webp, https://basket-35.wbbasket.ru/vol7464/part746418/746418024/images/big/3.webp, https://basket-35.wbbasket.ru/vol7464/part746418/746418024/images/big/4.webp, https://basket-35.wbbasket.ru/vol7464/part746418/746418024/images/big/5.webp, https://basket-35.wbbasket.ru/vol7464/part746418/746418024/images/big/6.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/608471220/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>608471220</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Пальто MOOCIE</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>15231</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>good product</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/250066741</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>S, M, L, XL, 2XL, 3XL, 4XL, 5XL, 6XL</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>43</v>
+      </c>
+      <c r="I88" t="n">
+        <v>1</v>
+      </c>
+      <c r="J88" t="n">
+        <v>5</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Пальто-парка с капюшоном , с кокетками и накладными карманами, застежка на молнию и потайные кнопки. Отделочные строчки, пуговицы, закрепки контрастные. Длина изделия по спинке для размера 50/176 - 81см. Классическое короткое утепленное пальто прямого кроя имеет стильные черные пуговицы и воротник (ворот), который можно сделать стойкой – популярное решение среди подростков. Шерстяное теплое пальто с подкладом из натуральных волокон прекрасно подойдет в качестве верхней вещи на зиму, осень или весну как для мужчин, парня – подростка и даже мальчика, в нем можно отправиться в школу. Элегантное подростковое строгое пальто идеально впишется как в официальный офисный или школьный, так и в неформальный романтичный образ. Однотонное, мягкое, молодежное пальто – плащ может выступать, как удлиненная, так и укороченная верхняя одежда, в зависимости от вашего роста и силуэта.и на невысоких молодых людей, как полных, так и стройных. Черный, синий, коричневый в клетку, бежевый (песочный, рыжий, желтый, оранжевый, горчичный, кэмел) пальтовые цвета - настоящие бестселлеры в мире моды. В нашем пальто по колено с утеплением вы будете выглядеть модно. В нем можно пойти на свадебное торжество, свидание и даже вечеринку на открытом воздухе. Легкое свободное ворсистое пальто дополнит ваш look и подчеркнет стиль, при том не будет сковывать движения. Весеннее – осеннее пальто до колена с утеплителем легко спрячет под собой длинный двубортный пиджак. Наденьте под подрастковое зимнее oversize пальто дизайнерский черно-синий или темно-серый костюм , рукав которого будет виден из-под пальто. Под ним также будет аккуратно смотреться школьная форма, что очень важно для подростка. Приталенное пуховое, меховое (мех), твидовое (твид), вязанное, трикотажное, кашемировое (кашимир), текстильное, драповое (драп), тканевое, стеганое palto не идет ни в какое сравнение с нашим смесовым составом и прямым силуэтом。</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Цвет:  темно-голубой
+Размер:  S
+Рос. размер:  42
+Вид застежки:  молния, пуговицы
+Утеплитель:  Хитофайбер
+Температурный режим:  от 15 до 5
+Материал подкладки:  полиэфирное волокно
+Покрой:  прямой
+Тип рукава:  длинный
+Декоративные элементы:  Воротник, Капюшон, Карманы, Манжеты</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>https://basket-30.wbbasket.ru/vol6084/part608471/608471220/images/big/1.webp, https://basket-30.wbbasket.ru/vol6084/part608471/608471220/images/big/2.webp, https://basket-30.wbbasket.ru/vol6084/part608471/608471220/images/big/3.webp, https://basket-30.wbbasket.ru/vol6084/part608471/608471220/images/big/4.webp, https://basket-30.wbbasket.ru/vol6084/part608471/608471220/images/big/5.webp, https://basket-30.wbbasket.ru/vol6084/part608471/608471220/images/big/6.webp, https://basket-30.wbbasket.ru/vol6084/part608471/608471220/images/big/7.webp, https://basket-30.wbbasket.ru/vol6084/part608471/608471220/images/big/8.webp, https://basket-30.wbbasket.ru/vol6084/part608471/608471220/images/big/9.webp, https://basket-30.wbbasket.ru/vol6084/part608471/608471220/images/big/10.webp, https://basket-30.wbbasket.ru/vol6084/part608471/608471220/images/big/11.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/817586223/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>817586223</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>осенняя зимнее куртка пальто</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>15315</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Гарант Цены и Качества</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/250087198</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>42, 44, 46, 48, 50, 52</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>5</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Стильная женская осенняя зимнее куртка пальто — отличное решение для создания модного образа в прохладное время года. Верхняя одежда сочетает в себе трендовые элементы, такие как удлиненная стеганая фактура и капюшон с мехом, которые не только придают стильный вид, но и помогают оставаться в тепле даже в холодную погоду. Утепленное изделие дарит комфорт и защищает от ветра во время прогулок по городу или выезда на природу.
+Модель выполнена из современных материалов с легкой плюшевой подкладкой, благодаря чему она остается легкая и приятная к телу. Стеганое полотно хорошо сохраняет тепло, позволяя выходить на улицу даже зимой без опасения замерзнуть. Курточка подходит для женщин разных возрастов и отлично сидит на фигуре за счет фасона оверсайз flare, который соответствует актуальным тенденциям 2025 года. Большие размеры изделия делают его универсальным выбором для женщин с разными параметрами.
+Демисезонная куртка пальто подходит для весна-осень, а утепленная структура позволяет использовать ее даже зимой. Это стильное решение для тех, кто ценит моду и комфорт одновременно. Классика всегда актуальна: драповое серое исполнение гармонирует с любыми вещами гардероба, легко сочетается со спортивной или повседневной одеждой, создавая законченный осенний или зимний образ.
+Капюшоном удобно пользоваться во время непогоды — он защищает голову от ветра и дождя. Высокий воротник стойкой обеспечивает дополнительную защиту шеи от холода. В изделии предусмотрены функциональные детали: удобные карманы для мелочей и надежные застежки, чтобы все необходимое было всегда под рукой.
+·Мы продолжим поставлять на полки новые продукты. «Astrid Official Store» — наш единственный официальный магазин в WB. Пожалуйста, выберите продавца «Astrid Official Store» при размещении заказа.
+Кликнув на логотип Astrid Official Store, Вы можете ознакомиться со всеми моделями нашего обширного ассортимента верхней одежды.</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>китай</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Цвет:  натуральный кремовый
+Сезон:  Зима
+Утеплитель:  Биологический бархат
+Температурный режим:  -25℃~10℃
+Материал подкладки:  полиэфирное волокно
+Покрой:  Непринужденное тепло
+Вид застежки:  Застежка-молния; пуговица
+Декоративные элементы:  планка на молнии; карман
+Пол:  Женский
+Страна производства:  Китай</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>https://basket-37.wbbasket.ru/vol8175/part817586/817586223/images/big/1.webp, https://basket-37.wbbasket.ru/vol8175/part817586/817586223/images/big/2.webp, https://basket-37.wbbasket.ru/vol8175/part817586/817586223/images/big/3.webp, https://basket-37.wbbasket.ru/vol8175/part817586/817586223/images/big/4.webp, https://basket-37.wbbasket.ru/vol8175/part817586/817586223/images/big/5.webp, https://basket-37.wbbasket.ru/vol8175/part817586/817586223/images/big/6.webp, https://basket-37.wbbasket.ru/vol8175/part817586/817586223/images/big/7.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/750211340/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>750211340</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Пальто，Верх из овчины стеганая куртка</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>20476</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Торговая Площадка Восток</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/250081381</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>L/45-55KG, XL/55-62.5KG, 2XL/62.5-70KG, 3XL/70-80Kg, 4XL/80-90Kg, 5XL/90-100Kg</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>10</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Мужской утепленный костюм со съемной подкладкой из норкового плюша выше колена рассчитан на то, чтобы выдерживать экстремально низкие температуры -30℃.Когда роскошь шерсти американской норки была объединена с ветрозащитной курткой военного образца, эта теплоизоляционная куртка изменила стандарт защиты от зимних холодов.Подборка высококачественного меха американской норки, богатый бархатистый низ, тонкий бархат, натуральный яркий блеск.Подкладка из искусственного меха золотистой норки обеспечивает отличную теплоизоляцию, а плотность шерсти в 3 раза выше, чем у обычных тканей. Это позволяет эффективно поддерживать температуру тела на уровне -30°C и выдерживать сильные морозы. Он изготовлен из композитной ткани на 83% из нейлона + 17% из спандекса, которая обладает отличными ветрозащитными и водонепроницаемыми свойствами.Модель длиной выше колена обеспечивает защиту всего тела, эффективно защищая его от холодного ветра, проникающего под подол, и по-настоящему "защищает от дождя и солнечного света".- Чтобы легко справляться с различными погодными условиями.Рукава с меховой отделкой: сохраняют тепло во всех направлениях, и ваши руки больше не мерзнут; длина до колен: эффективно защищает бедра и колени от холодного воздуха; интегрированная структура меха: как внутри, так и снаружи, двойная теплоотдача; уровень морозостойкости: сохраняет тепло в экстремально холодных условиях при температуре -30 ℃; ветрозащитный характеристики: ткань военного класса, не боится ветреной погоды; воздухопроницаемость: сохраняет тепло, обеспечивает умеренную вентиляцию и предотвращает удушающую жару."Поскольку существует множество накопителей тепла и отопительных приборов, холод больше не представляет угрозы.Этот костюм от Parker - не только зимний костюм, но и ваш верный помощник в борьбе с холодом.Каждое изделие изготовлено из отборной американской норки и предназначено для обеспечения максимального тепла.</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>вьетнам</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>Состав:  95% шерсть, 5% полиэстер
+Цвет:  темно-бурый
+Сезон:  зима
+Вид застежки:  Пуговицы, молнии
+Утеплитель:  шерстяной
+Температурный режим:  -30
+Материал подкладки:  шерстяной
+Покрой:  Мода повседневная, деловая
+Тип карманов:  Косой карман
+Тип рукава:  длинные рукава
+Декоративные элементы:  Меховой воротник, застежка-молния
+Пол:  Мужской
+Комплектация:  Шерстяной топ
+Страна производства:  Вьетнам</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>https://basket-35.wbbasket.ru/vol7502/part750211/750211340/images/big/1.webp, https://basket-35.wbbasket.ru/vol7502/part750211/750211340/images/big/2.webp, https://basket-35.wbbasket.ru/vol7502/part750211/750211340/images/big/3.webp, https://basket-35.wbbasket.ru/vol7502/part750211/750211340/images/big/4.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/877101984/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>877101984</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Шуба искусственная SYJWY шерстяное пальто</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>4287</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Step &amp; Spell</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/250104280</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>S/45-60kr, M/50-70kr</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>22</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Эта утолщенная шуба из искусственной норки средней длины с капюшоном — стильный предмет верхней одежды с меховым узором. Изготовленная из искусственного меха, эта шуба обеспечивает мягкость, комфорт и изысканный, элегантный вид. Ее мягкий абрикосовый цвет дополняет тон кожи и подчеркивает женственный образ. Эта верхняя одежда подходит для весны, осени и зимы, предлагая отличное тепло. Рукава реглан подчеркивают линию плеч и создают удобную, естественную посадку. Основной материал — искусственный мех, предлагающий роскошное ощущение меха без грубости натурального меха. Эта шуба доступна в размерах S и M и разработана специально для женщин. Воротник-капюшон добавляет стильный штрих, обеспечивая ветронепроницаемое тепло. Рукава три четверти, открывающие часть запястья, создают изысканный и утонченный образ. Общий стиль более зрелый, демонстрирующий очарование и уверенность зрелой женщины. Эта утолщенная шуба из искусственной норки средней длины с капюшоном — идеальный выбор для женщин, которые ценят и моду, и тепло.</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Цвет:  оранжевый
+Материал подкладки:  махровая ткань
+Покрой:  оверсайз
+Вид застежки:  без застежки, завязки
+Уход за вещами:  не смешивайте Мыть холодной водой</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>https://basket-39.wbbasket.ru/vol8771/part877101/877101984/images/big/1.webp, https://basket-39.wbbasket.ru/vol8771/part877101/877101984/images/big/2.webp, https://basket-39.wbbasket.ru/vol8771/part877101/877101984/images/big/3.webp, https://basket-39.wbbasket.ru/vol8771/part877101/877101984/images/big/4.webp, https://basket-39.wbbasket.ru/vol8771/part877101/877101984/images/big/5.webp, https://basket-39.wbbasket.ru/vol8771/part877101/877101984/images/big/6.webp, https://basket-39.wbbasket.ru/vol8771/part877101/877101984/images/big/7.webp, https://basket-39.wbbasket.ru/vol8771/part877101/877101984/images/big/8.webp, https://basket-39.wbbasket.ru/vol8771/part877101/877101984/images/big/9.webp, https://basket-39.wbbasket.ru/vol8771/part877101/877101984/images/big/10.webp, https://basket-39.wbbasket.ru/vol8771/part877101/877101984/images/big/11.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/583393443/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>583393443</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Пальто，Верх из овчины стеганая куртка</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10948</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>广州瑾岑商贸有限公司</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/250022985</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>L/45-55KG, XL/55-62.5KG, 2XL/62.5-70KG, 3XL/70-80Kg, 4XL/80-90Kg, 5XL/90-100Kg</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>43</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Мужской утепленный костюм со съемной подкладкой из норкового плюша выше колена рассчитан на то, чтобы выдерживать экстремально низкие температуры -30℃.Когда роскошь шерсти американской норки была объединена с ветрозащитной курткой военного образца, эта теплоизоляционная куртка изменила стандарт защиты от зимних холодов.Подборка высококачественного меха американской норки, богатый бархатистый низ, тонкий бархат, натуральный яркий блеск.Подкладка из искусственного меха золотистой норки обеспечивает отличную теплоизоляцию, а плотность шерсти в 3 раза выше, чем у обычных тканей. Это позволяет эффективно поддерживать температуру тела на уровне -30°C и выдерживать сильные морозы. Он изготовлен из композитной ткани на 83% из нейлона + 17% из спандекса, которая обладает отличными ветрозащитными и водонепроницаемыми свойствами.Модель длиной выше колена обеспечивает защиту всего тела, эффективно защищая его от холодного ветра, проникающего под подол, и по-настоящему "защищает от дождя и солнечного света".- Чтобы легко справляться с различными погодными условиями.Рукава с меховой отделкой: сохраняют тепло во всех направлениях, и ваши руки больше не мерзнут; длина до колен: эффективно защищает бедра и колени от холодного воздуха; интегрированная структура меха: как внутри, так и снаружи, двойная теплоотдача; уровень морозостойкости: сохраняет тепло в экстремально холодных условиях при температуре -30 ℃; ветрозащитный характеристики: ткань военного класса, не боится ветреной погоды; воздухопроницаемость: сохраняет тепло, обеспечивает умеренную вентиляцию и предотвращает удушающую жару."Поскольку существует множество накопителей тепла и отопительных приборов, холод больше не представляет угрозы.Этот костюм от Parker - не только зимний костюм, но и ваш верный помощник в борьбе с холодом.Каждое изделие изготовлено из отборной американской норки и предназначено для обеспечения максимального тепла.</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>вьетнам</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Состав:  95% шерсть, 5% полиэстер
+Цвет:  глубокий черный
+Сезон:  зима
+Вид застежки:  Пуговицы, молнии
+Утеплитель:  шерстяной
+Температурный режим:  -30
+Материал подкладки:  шерстяной
+Покрой:  Мода повседневная, деловая
+Тип карманов:  косой карман
+Тип рукава:  длинные рукава
+Мех опушки/отделки:  меховой воротник
+Декоративные элементы:  Меховой воротник, застежка-молния
+Пол:  Мужской
+Комплектация:  Шерстяной топ
+Страна производства:  Вьетнам</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>https://basket-30.wbbasket.ru/vol5833/part583393/583393443/images/big/1.webp, https://basket-30.wbbasket.ru/vol5833/part583393/583393443/images/big/2.webp, https://basket-30.wbbasket.ru/vol5833/part583393/583393443/images/big/3.webp, https://basket-30.wbbasket.ru/vol5833/part583393/583393443/images/big/4.webp, https://basket-30.wbbasket.ru/vol5833/part583393/583393443/images/big/5.webp, https://basket-30.wbbasket.ru/vol5833/part583393/583393443/images/big/6.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/877101986/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>877101986</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Шуба искусственная SYJWY шерстяное пальто</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>4287</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Step &amp; Spell</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/250104280</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>40 RU/S, 42 RU /M, 44 RU/L, 46 RU /XL</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>22</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Эта утолщенная шуба из искусственной норки средней длины с капюшоном — стильный предмет верхней одежды с меховым узором. Изготовленная из искусственного меха, эта шуба обеспечивает мягкость, комфорт и изысканный, элегантный вид. Ее мягкий абрикосовый цвет дополняет тон кожи и подчеркивает женственный образ. Эта верхняя одежда подходит для весны, осени и зимы, предлагая отличное тепло. Рукава реглан подчеркивают линию плеч и создают удобную, естественную посадку. Основной материал — искусственный мех, предлагающий роскошное ощущение меха без грубости натурального меха. Эта шуба доступна в размерах S и M и разработана специально для женщин. Воротник-капюшон добавляет стильный штрих, обеспечивая ветронепроницаемое тепло. Рукава три четверти, открывающие часть запястья, создают изысканный и утонченный образ. Общий стиль более зрелый, демонстрирующий очарование и уверенность зрелой женщины. Эта утолщенная шуба из искусственной норки средней длины с капюшоном — идеальный выбор для женщин, которые ценят и моду, и тепло.</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Цвет:  красный
+Материал подкладки:  махровая ткань
+Покрой:  оверсайз
+Вид застежки:  без застежки, завязки
+Уход за вещами:  не смешивайте Мыть холодной водой</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>https://basket-39.wbbasket.ru/vol8771/part877101/877101986/images/big/1.webp, https://basket-39.wbbasket.ru/vol8771/part877101/877101986/images/big/2.webp, https://basket-39.wbbasket.ru/vol8771/part877101/877101986/images/big/3.webp, https://basket-39.wbbasket.ru/vol8771/part877101/877101986/images/big/4.webp, https://basket-39.wbbasket.ru/vol8771/part877101/877101986/images/big/5.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/649179295/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>649179295</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Женское зимнее пальто искусственный норковый мех минималис</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>8409</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Jiayi</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/250066575</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>М, л, XL</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>43</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Описание продукта 
+ Погружитесь в зимнюю уютность с женским пальто из высококачественного искусственного меха — настоящая находка для холодных сезонов! Искусственная шерсть премиум-класса идеально повторяет текстуру натурального норкового и лисиного меха: мягкая, пушистая, приятная на ощупь, при этом безопасна и этична. Благодаря плотной нашивке и технологическому материалу, пальто отлично держит тепло даже при низких температурах (-20 ° C и ниже), защищая вас от мороза и ветра. 
+ Минималистский дизайн делает модель универсальной: подходит как для повседневных прогулок, так и для выходных встреч. Классическая крой подчеркивает фигуру, а аккуратные детали добавляют элегантности без лишнего декора. Разнообразие цветов (от нейтральных бежевых до стильных темных оттенков) позволяет легко сочетать пальто с джинсами, юбками или платьями — ваш гардероб получит стильное обновление. 
+ Легкая ткань подкладки обеспечивает комфортное ношение на протяжении всего дня, а прочный фурнитура гарантирует долговечность. Эта зимняя новинка сочетает в себе моду, практичность и тепло — то, что нужно для стильного и уютного переживания зимы! Закажите сейчас и ощутите все преимущества качественного искусственного меха без компромиссов.</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>Цвет:  черный
+Покрой:  Элегантный стиль сестры</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>https://basket-32.wbbasket.ru/vol6491/part649179/649179295/images/big/1.webp, https://basket-32.wbbasket.ru/vol6491/part649179/649179295/images/big/2.webp, https://basket-32.wbbasket.ru/vol6491/part649179/649179295/images/big/3.webp, https://basket-32.wbbasket.ru/vol6491/part649179/649179295/images/big/4.webp, https://basket-32.wbbasket.ru/vol6491/part649179/649179295/images/big/5.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/765030289/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>765030289</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Пальто，Верх из овчины стеганая куртка</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>18599</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Будущее Покупок</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/250088162</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>L/45-55KG, XL/55-62.5KG, 2XL/62.5-70KG, 3XL/70-80Kg, 4XL/80-90Kg, 5XL/90-100Kg</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>5</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Мужской утепленный костюм со съемной подкладкой из норкового плюша выше колена рассчитан на то, чтобы выдерживать экстремально низкие температуры -30℃.Когда роскошь шерсти американской норки была объединена с ветрозащитной курткой военного образца, эта теплоизоляционная куртка изменила стандарт защиты от зимних холодов.Подборка высококачественного меха американской норки, богатый бархатистый низ, тонкий бархат, натуральный яркий блеск.Подкладка из искусственного меха золотистой норки обеспечивает отличную теплоизоляцию, а плотность шерсти в 3 раза выше, чем у обычных тканей. Это позволяет эффективно поддерживать температуру тела на уровне -30°C и выдерживать сильные морозы. Он изготовлен из композитной ткани на 83% из нейлона + 17% из спандекса, которая обладает отличными ветрозащитными и водонепроницаемыми свойствами.Модель длиной выше колена обеспечивает защиту всего тела, эффективно защищая его от холодного ветра, проникающего под подол, и по-настоящему "защищает от дождя и солнечного света".- Чтобы легко справляться с различными погодными условиями.Рукава с меховой отделкой: сохраняют тепло во всех направлениях, и ваши руки больше не мерзнут; длина до колен: эффективно защищает бедра и колени от холодного воздуха; интегрированная структура меха: как внутри, так и снаружи, двойная теплоотдача; уровень морозостойкости: сохраняет тепло в экстремально холодных условиях при температуре -30 ℃; ветрозащитный характеристики: ткань военного класса, не боится ветреной погоды; воздухопроницаемость: сохраняет тепло, обеспечивает умеренную вентиляцию и предотвращает удушающую жару."Поскольку существует множество накопителей тепла и отопительных приборов, холод больше не представляет угрозы.Этот костюм от Parker - не только зимний костюм, но и ваш верный помощник в борьбе с холодом.Каждое изделие изготовлено из отборной американской норки и предназначено для обеспечения максимального тепла.</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>вьетнам</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>Состав:  95% шерсть, 5% полиэстер
+Цвет:  глубокий черный
+Сезон:  зима
+Вид застежки:  Пуговицы, молнии
+Утеплитель:  шерстяной
+Температурный режим:  -30
+Материал подкладки:  шерстяной
+Покрой:  Мода повседневная, деловая
+Тип карманов:  Косой карман
+Тип рукава:  длинные рукава
+Декоративные элементы:  Меховой воротник, застежка-молния
+Пол:  Мужской
+Комплектация:  Шерстяной топ
+Страна производства:  Вьетнам</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>https://basket-35.wbbasket.ru/vol7650/part765030/765030289/images/big/1.webp, https://basket-35.wbbasket.ru/vol7650/part765030/765030289/images/big/2.webp, https://basket-35.wbbasket.ru/vol7650/part765030/765030289/images/big/3.webp, https://basket-35.wbbasket.ru/vol7650/part765030/765030289/images/big/4.webp, https://basket-35.wbbasket.ru/vol7650/part765030/765030289/images/big/5.webp, https://basket-35.wbbasket.ru/vol7650/part765030/765030289/images/big/6.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/583393446/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>583393446</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Пальто，Верх из овчины стеганая куртка</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10557</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>广州瑾岑商贸有限公司</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/250022985</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>L/45-55KG, XL/55-62.5KG, 2XL/62.5-70KG, 3XL/70-80Kg, 4XL/80-90Kg, 5XL/90-100Kg</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
+        <v>43</v>
+      </c>
+      <c r="I96" t="n">
+        <v>1</v>
+      </c>
+      <c r="J96" t="n">
+        <v>5</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Мужской утепленный костюм со съемной подкладкой из норкового плюша выше колена рассчитан на то, чтобы выдерживать экстремально низкие температуры -30℃.Когда роскошь шерсти американской норки была объединена с ветрозащитной курткой военного образца, эта теплоизоляционная куртка изменила стандарт защиты от зимних холодов.Подборка высококачественного меха американской норки, богатый бархатистый низ, тонкий бархат, натуральный яркий блеск.Подкладка из искусственного меха золотистой норки обеспечивает отличную теплоизоляцию, а плотность шерсти в 3 раза выше, чем у обычных тканей. Это позволяет эффективно поддерживать температуру тела на уровне -30°C и выдерживать сильные морозы. Он изготовлен из композитной ткани на 83% из нейлона + 17% из спандекса, которая обладает отличными ветрозащитными и водонепроницаемыми свойствами.Модель длиной выше колена обеспечивает защиту всего тела, эффективно защищая его от холодного ветра, проникающего под подол, и по-настоящему "защищает от дождя и солнечного света".- Чтобы легко справляться с различными погодными условиями.Рукава с меховой отделкой: сохраняют тепло во всех направлениях, и ваши руки больше не мерзнут; длина до колен: эффективно защищает бедра и колени от холодного воздуха; интегрированная структура меха: как внутри, так и снаружи, двойная теплоотдача; уровень морозостойкости: сохраняет тепло в экстремально холодных условиях при температуре -30 ℃; ветрозащитный характеристики: ткань военного класса, не боится ветреной погоды; воздухопроницаемость: сохраняет тепло, обеспечивает умеренную вентиляцию и предотвращает удушающую жару."Поскольку существует множество накопителей тепла и отопительных приборов, холод больше не представляет угрозы.Этот костюм от Parker - не только зимний костюм, но и ваш верный помощник в борьбе с холодом.Каждое изделие изготовлено из отборной американской норки и предназначено для обеспечения максимального тепла.</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>вьетнам</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>Состав:  95% шерсть, 5% полиэстер
+Цвет:  вива маджента
+Сезон:  зима
+Вид застежки:  Пуговицы, молнии
+Утеплитель:  шерстяной
+Температурный режим:  -30
+Материал подкладки:  шерстяной
+Покрой:  Мода повседневная, деловая
+Тип карманов:  косой карман
+Тип рукава:  длинные рукава
+Мех опушки/отделки:  меховой воротник
+Декоративные элементы:  Меховой воротник, застежка-молния
+Пол:  Мужской
+Комплектация:  Шерстяной топ
+Страна производства:  Вьетнам</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>https://basket-30.wbbasket.ru/vol5833/part583393/583393446/images/big/1.webp, https://basket-30.wbbasket.ru/vol5833/part583393/583393446/images/big/2.webp, https://basket-30.wbbasket.ru/vol5833/part583393/583393446/images/big/3.webp, https://basket-30.wbbasket.ru/vol5833/part583393/583393446/images/big/4.webp, https://basket-30.wbbasket.ru/vol5833/part583393/583393446/images/big/5.webp, https://basket-30.wbbasket.ru/vol5833/part583393/583393446/images/big/6.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/662745890/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>662745890</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Дубленка искусственная</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>1696</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Fashion sneaker store</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/250005275</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>44 RU /M, 46 RU/L, 48 RU /XL</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>19</v>
+      </c>
+      <c r="I97" t="n">
+        <v>2</v>
+      </c>
+      <c r="J97" t="n">
+        <v>5</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>** Пальто из искусственной шерсти - теплое и модное, новый выбор для защиты окружающей среды** В современном стремлении к моде и защите окружающей среды пальто из искусственной шерсти стали незаменимым предметом осеннего и зимнего гардероба благодаря своей легкости и теплоте, бионической текстуре и экологичным свойствам. Будь то поездка на работу в городе или отдых на природе, он может учитывать температуру и манеру поведения, снижая зависимость от животных и воплощая элегантность и ответственность современных людей. # # # ** Основные моменты**  1. ** Бионическая технология, настоящий бархат на ощупь** Использование высокотехнологичных волокон (таких как смеси акриловых и полиэфирных волокон) идеально воспроизводит пушистость и мягкость натуральной шерсти, они легкие и не вызывают зуда, а верхняя часть тела комфортна и приятна для кожи. 2. ** Очень теплая, ветрозащитная и влагостойкая** Структура волокон удерживает воздушную прослойку, а тепло сравнимо с теплом натуральной шерсти; некоторые ткани обладают водоотталкивающими свойствами, и им нелегко впитывать воду в дождливую и снежную погоду, сохраняя их сухими и теплыми. 3. **Безвреден для окружающей среды и не требует жестокого обращения** Для снижения потребления ресурсов животноводства не требуется шерсть животных; некоторые бренды используют переработанные волокна или биоразлагаемые материалы, чтобы снизить нагрузку на окружающую среду. 4. **Простота в уходе и экономичность**     Она не мнется и износостойка, выдерживает машинную стирку, не дает усадки и деформации; цена составляет всего 1/3-1/2 от натуральной шерсти, а долговечность выше. 5. ** Разнообразный дизайн, универсальная мода**     От классических цветов camel до Morandi, они охватывают такие стили, как силуэты оверсайз и приталенный крой, которые легко сочетаются с официальной одеждой для работы или повседневным стилем.</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Цвет:  коричневый</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>https://basket-32.wbbasket.ru/vol6627/part662745/662745890/images/big/1.webp, https://basket-32.wbbasket.ru/vol6627/part662745/662745890/images/big/2.webp, https://basket-32.wbbasket.ru/vol6627/part662745/662745890/images/big/3.webp, https://basket-32.wbbasket.ru/vol6627/part662745/662745890/images/big/4.webp, https://basket-32.wbbasket.ru/vol6627/part662745/662745890/images/big/5.webp, https://basket-32.wbbasket.ru/vol6627/part662745/662745890/images/big/6.webp, https://basket-32.wbbasket.ru/vol6627/part662745/662745890/images/big/7.webp, https://basket-32.wbbasket.ru/vol6627/part662745/662745890/images/big/8.webp, https://basket-32.wbbasket.ru/vol6627/part662745/662745890/images/big/9.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/554670110/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>554670110</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Куртка</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>8157</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>恒东</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/250044881</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>M, L, XL, 2XL, 3XL</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>43</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Он подходит для осени-весны, в холодные межсезонные дни, так как содержит высококачественную натуральную шерсть, которая обеспечит длительный срок службы. Классическое красивое желто-горчичное пальто длиной ниже колена создано для такого же комфорта. Его свободный крой придаст образу неповторимости и шарма, а также позволит вам свободно двигаться. Изделие имеет прямой приталенный силуэт, пуговицы, закатанные рукава, лацкан и длинный пояс. Это драпированное утепленное однобортное пальто-кокон - отличный выбор для современных модниц. Он подходит для любого типа фигуры, добавляя образу элегантности, а сочетание свободного кроя и стильного силуэта делает пиджак оверсайз отличным выбором для разборчивых женщин. Идеальный выбор для холодного времени года. Длина миди является базовой и станет незаменимым предметом гардероба. Он найдет применение в повседневных луках, офисной одежде, спортивных костюмах и молодежных стилях. Это пальто в британском стиле может стать хорошим подарком для любимого человека. Весеннее пальто - незаменимая классика в гардеробе. У нас проводятся акции и распродажи, вы можете приобрести нашу продукцию в качестве подарков и со скидками!</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>китай</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Цвет:  темно-серый
+Сезон:  круглогодичный
+Утеплитель:  нет
+Температурный режим:  -5 °С до +15 °С
+Материал подкладки:  шерстяной
+Покрой:  свободный
+Вид застежки:  однобортный
+Тип карманов:  нет
+Опции капюшона:  нет
+Мех опушки/отделки:  Лацкан
+Декоративные элементы:  Сплошной цвет
+Уход за вещами:  химчистка
+Страна производства:  Китай</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>https://basket-29.wbbasket.ru/vol5546/part554670/554670110/images/big/1.webp, https://basket-29.wbbasket.ru/vol5546/part554670/554670110/images/big/2.webp, https://basket-29.wbbasket.ru/vol5546/part554670/554670110/images/big/3.webp, https://basket-29.wbbasket.ru/vol5546/part554670/554670110/images/big/4.webp, https://basket-29.wbbasket.ru/vol5546/part554670/554670110/images/big/5.webp, https://basket-29.wbbasket.ru/vol5546/part554670/554670110/images/big/6.webp, https://basket-29.wbbasket.ru/vol5546/part554670/554670110/images/big/7.webp, https://basket-29.wbbasket.ru/vol5546/part554670/554670110/images/big/8.webp, https://basket-29.wbbasket.ru/vol5546/part554670/554670110/images/big/9.webp, https://basket-29.wbbasket.ru/vol5546/part554670/554670110/images/big/10.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/583393447/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>583393447</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Пальто，Верх из овчины стеганая куртка</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10948</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>广州瑾岑商贸有限公司</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/250022985</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>L/45-55KG, XL/55-62.5KG, 2XL/62.5-70KG, 3XL/70-80Kg, 4XL/80-90Kg, 5XL/90-100Kg</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
+        <v>43</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Мужской утепленный костюм со съемной подкладкой из норкового плюша выше колена рассчитан на то, чтобы выдерживать экстремально низкие температуры -30℃.Когда роскошь шерсти американской норки была объединена с ветрозащитной курткой военного образца, эта теплоизоляционная куртка изменила стандарт защиты от зимних холодов.Подборка высококачественного меха американской норки, богатый бархатистый низ, тонкий бархат, натуральный яркий блеск.Подкладка из искусственного меха золотистой норки обеспечивает отличную теплоизоляцию, а плотность шерсти в 3 раза выше, чем у обычных тканей. Это позволяет эффективно поддерживать температуру тела на уровне -30°C и выдерживать сильные морозы. Он изготовлен из композитной ткани на 83% из нейлона + 17% из спандекса, которая обладает отличными ветрозащитными и водонепроницаемыми свойствами.Модель длиной выше колена обеспечивает защиту всего тела, эффективно защищая его от холодного ветра, проникающего под подол, и по-настоящему "защищает от дождя и солнечного света".- Чтобы легко справляться с различными погодными условиями.Рукава с меховой отделкой: сохраняют тепло во всех направлениях, и ваши руки больше не мерзнут; длина до колен: эффективно защищает бедра и колени от холодного воздуха; интегрированная структура меха: как внутри, так и снаружи, двойная теплоотдача; уровень морозостойкости: сохраняет тепло в экстремально холодных условиях при температуре -30 ℃; ветрозащитный характеристики: ткань военного класса, не боится ветреной погоды; воздухопроницаемость: сохраняет тепло, обеспечивает умеренную вентиляцию и предотвращает удушающую жару."Поскольку существует множество накопителей тепла и отопительных приборов, холод больше не представляет угрозы.Этот костюм от Parker - не только зимний костюм, но и ваш верный помощник в борьбе с холодом.Каждое изделие изготовлено из отборной американской норки и предназначено для обеспечения максимального тепла.</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>вьетнам</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Состав:  95% шерсть, 5% полиэстер
+Цвет:  коричневый
+Сезон:  зима
+Вид застежки:  Пуговицы, молнии
+Утеплитель:  шерстяной
+Температурный режим:  -30
+Материал подкладки:  шерстяной
+Покрой:  Мода повседневная, деловая
+Тип карманов:  косой карман
+Тип рукава:  длинные рукава
+Мех опушки/отделки:  меховой воротник
+Декоративные элементы:  Меховой воротник, застежка-молния
+Пол:  Мужской
+Комплектация:  Шерстяной топ
+Страна производства:  Вьетнам</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>https://basket-30.wbbasket.ru/vol5833/part583393/583393447/images/big/1.webp, https://basket-30.wbbasket.ru/vol5833/part583393/583393447/images/big/2.webp, https://basket-30.wbbasket.ru/vol5833/part583393/583393447/images/big/3.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/583393448/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>583393448</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Пальто，Верх из овчины стеганая куртка</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10948</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>广州瑾岑商贸有限公司</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/250022985</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>L/45-55KG, XL/55-62.5KG, 2XL/62.5-70KG, 3XL/70-80Kg, 4XL/80-90Kg, 5XL/90-100Kg</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>43</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Мужской утепленный костюм со съемной подкладкой из норкового плюша выше колена рассчитан на то, чтобы выдерживать экстремально низкие температуры -30℃.Когда роскошь шерсти американской норки была объединена с ветрозащитной курткой военного образца, эта теплоизоляционная куртка изменила стандарт защиты от зимних холодов.Подборка высококачественного меха американской норки, богатый бархатистый низ, тонкий бархат, натуральный яркий блеск.Подкладка из искусственного меха золотистой норки обеспечивает отличную теплоизоляцию, а плотность шерсти в 3 раза выше, чем у обычных тканей. Это позволяет эффективно поддерживать температуру тела на уровне -30°C и выдерживать сильные морозы. Он изготовлен из композитной ткани на 83% из нейлона + 17% из спандекса, которая обладает отличными ветрозащитными и водонепроницаемыми свойствами.Модель длиной выше колена обеспечивает защиту всего тела, эффективно защищая его от холодного ветра, проникающего под подол, и по-настоящему "защищает от дождя и солнечного света".- Чтобы легко справляться с различными погодными условиями.Рукава с меховой отделкой: сохраняют тепло во всех направлениях, и ваши руки больше не мерзнут; длина до колен: эффективно защищает бедра и колени от холодного воздуха; интегрированная структура меха: как внутри, так и снаружи, двойная теплоотдача; уровень морозостойкости: сохраняет тепло в экстремально холодных условиях при температуре -30 ℃; ветрозащитный характеристики: ткань военного класса, не боится ветреной погоды; воздухопроницаемость: сохраняет тепло, обеспечивает умеренную вентиляцию и предотвращает удушающую жару."Поскольку существует множество накопителей тепла и отопительных приборов, холод больше не представляет угрозы.Этот костюм от Parker - не только зимний костюм, но и ваш верный помощник в борьбе с холодом.Каждое изделие изготовлено из отборной американской норки и предназначено для обеспечения максимального тепла.</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>вьетнам</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>Состав:  95% шерсть, 5% полиэстер
+Цвет:  черный
+Сезон:  зима
+Вид застежки:  Пуговицы, молнии
+Утеплитель:  шерстяной
+Температурный режим:  -30
+Материал подкладки:  шерстяной
+Покрой:  Мода повседневная, деловая
+Тип карманов:  косой карман
+Тип рукава:  длинные рукава
+Мех опушки/отделки:  меховой воротник
+Декоративные элементы:  Меховой воротник, застежка-молния
+Пол:  Мужской
+Комплектация:  Шерстяной топ
+Страна производства:  Вьетнам</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>https://basket-30.wbbasket.ru/vol5833/part583393/583393448/images/big/1.webp, https://basket-30.wbbasket.ru/vol5833/part583393/583393448/images/big/2.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/catalog/695062387/detail.aspx</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>695062387</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Пальто ALEXANDER WANG</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>4971</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Fashion sneaker store</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>https://www.wildberries.ru/seller/250005275</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>44 RU/M, 46 RU /L, 48 RU /XL, 50 RU /2XL, 52 RU /3XL</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>20</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Эта джинсовка — идеальный акцент для современного гардероба: 
+ Мягкая шерстяная ткань (натуральные волокна) обеспечивает тепло и приятное ощущение на коже. 
+ Классический крой с воротником и карманами в стиле джинсовки — универсальный дизайн для разных образов. 
+ Бежевый нейтральный цвет легко сочетается с черными, серыми или светлыми брюками, свитерами и футболками. 
+ Крупные металлические пуговицы добавляют изюминку и долговечность. 
+ Свободный крой не ограничивает движения, идеален для повседневного использования (учеба, работа, прогулки). 
+ Подходит для весны, осени или тепловых зимних дней. Создает стильный, непринужденный образ для молодых мужчин.</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Цвет:  хаки
+Размер на модели:  44
+Рост модели на фото:  177 см
+Покрой:  свободный</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>https://basket-33.wbbasket.ru/vol6950/part695062/695062387/images/big/1.webp, https://basket-33.wbbasket.ru/vol6950/part695062/695062387/images/big/2.webp, https://basket-33.wbbasket.ru/vol6950/part695062/695062387/images/big/3.webp, https://basket-33.wbbasket.ru/vol6950/part695062/695062387/images/big/4.webp, https://basket-33.wbbasket.ru/vol6950/part695062/695062387/images/big/5.webp</t>
         </is>
       </c>
     </row>
